--- a/research/traditional_assets/database/data/morocco/morocco_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_real_estate_development.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cbse_rds" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.262</v>
+        <v>-0.2275</v>
       </c>
       <c r="G2">
-        <v>-0.3663192799621033</v>
+        <v>-0.0343807763401109</v>
       </c>
       <c r="H2">
-        <v>-0.3663192799621033</v>
+        <v>-0.0343807763401109</v>
       </c>
       <c r="I2">
-        <v>-0.2271435338702037</v>
+        <v>-0.003974121996303144</v>
       </c>
       <c r="J2">
-        <v>-0.2271435338702037</v>
+        <v>-0.003974121996303144</v>
       </c>
       <c r="K2">
-        <v>-80.10000000000001</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.3794410232117481</v>
+        <v>-0.044547134935305</v>
       </c>
       <c r="M2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1.863932898415657e-06</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-1.248439450686642e-05</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.863932898415657e-06</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-1.248439450686642e-05</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>98.69999999999999</v>
+        <v>41.48</v>
       </c>
       <c r="V2">
-        <v>0.1839701770736253</v>
+        <v>0.1452889667250438</v>
       </c>
       <c r="W2">
-        <v>-0.04482065509104855</v>
+        <v>-0.005811638108600335</v>
       </c>
       <c r="X2">
-        <v>0.112582519942472</v>
+        <v>0.248688972398073</v>
       </c>
       <c r="Y2">
-        <v>-0.1574031750335205</v>
+        <v>-0.2545006105066733</v>
       </c>
       <c r="Z2">
-        <v>0.09101711518429348</v>
+        <v>0.09365938108634494</v>
       </c>
       <c r="AA2">
-        <v>-0.01583592689505318</v>
+        <v>0.001274554265423339</v>
       </c>
       <c r="AB2">
-        <v>0.05213689840752528</v>
+        <v>0.09504475165129192</v>
       </c>
       <c r="AC2">
-        <v>-0.06797282530257846</v>
+        <v>-0.09377019738586859</v>
       </c>
       <c r="AD2">
-        <v>888.9</v>
+        <v>774.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>888.9</v>
+        <v>774.1</v>
       </c>
       <c r="AG2">
-        <v>790.2</v>
+        <v>732.62</v>
       </c>
       <c r="AH2">
-        <v>0.6236144240213273</v>
+        <v>0.7305587013967536</v>
       </c>
       <c r="AI2">
-        <v>0.3604769049839815</v>
+        <v>0.3535510390500115</v>
       </c>
       <c r="AJ2">
-        <v>0.595613175548353</v>
+        <v>0.7195811888578949</v>
       </c>
       <c r="AK2">
-        <v>0.3338120986819872</v>
+        <v>0.3410675878250668</v>
       </c>
       <c r="AL2">
-        <v>40.89</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>40.89</v>
+        <v>34.7</v>
       </c>
       <c r="AN2">
-        <v>-20.08223572735693</v>
+        <v>789.8979591836732</v>
       </c>
       <c r="AO2">
-        <v>-1.172658351675226</v>
+        <v>-0.01869565217391305</v>
       </c>
       <c r="AP2">
-        <v>-17.85238235094775</v>
+        <v>747.5714285714282</v>
       </c>
       <c r="AQ2">
-        <v>-1.172658351675226</v>
+        <v>-0.02478386167146975</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +718,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.247</v>
+        <v>-0.179</v>
       </c>
       <c r="G3">
-        <v>-0.1102079395085066</v>
+        <v>0.0734207389749702</v>
       </c>
       <c r="H3">
-        <v>-0.1102079395085066</v>
+        <v>0.0734207389749702</v>
       </c>
       <c r="I3">
-        <v>-0.02930056710775047</v>
+        <v>0.06257449344457687</v>
       </c>
       <c r="J3">
-        <v>-0.02930056710775047</v>
+        <v>0.06257449344457687</v>
       </c>
       <c r="K3">
-        <v>-10.4</v>
+        <v>-1.85</v>
       </c>
       <c r="L3">
-        <v>-0.1965973534971645</v>
+        <v>-0.02205005959475566</v>
       </c>
       <c r="M3">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>1.283697047496791e-05</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-9.615384615384615e-05</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>1.283697047496791e-05</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-9.615384615384615e-05</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>57.3</v>
+        <v>31.5</v>
       </c>
       <c r="V3">
-        <v>0.735558408215661</v>
+        <v>0.6969026548672566</v>
       </c>
       <c r="W3">
-        <v>-0.02317806997994206</v>
+        <v>-0.00387434554973822</v>
       </c>
       <c r="X3">
-        <v>0.1490063654869266</v>
+        <v>0.3378687712981005</v>
       </c>
       <c r="Y3">
-        <v>-0.1721844354668687</v>
+        <v>-0.3417431168478387</v>
       </c>
       <c r="Z3">
-        <v>0.0703083466241361</v>
+        <v>0.1052565550119182</v>
       </c>
       <c r="AA3">
-        <v>-0.002060074428495481</v>
+        <v>0.006586375611592021</v>
       </c>
       <c r="AB3">
-        <v>0.05285023075054693</v>
+        <v>0.09664298062960691</v>
       </c>
       <c r="AC3">
-        <v>-0.05491030517904241</v>
+        <v>-0.09005660501801489</v>
       </c>
       <c r="AD3">
-        <v>339.4</v>
+        <v>312.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>339.4</v>
+        <v>312.1</v>
       </c>
       <c r="AG3">
-        <v>282.1</v>
+        <v>280.6</v>
       </c>
       <c r="AH3">
-        <v>0.8133237479031872</v>
+        <v>0.8734956619087602</v>
       </c>
       <c r="AI3">
-        <v>0.4157275845173934</v>
+        <v>0.4052194235263568</v>
       </c>
       <c r="AJ3">
-        <v>0.783611111111111</v>
+        <v>0.8612645794966237</v>
       </c>
       <c r="AK3">
-        <v>0.3716242919246476</v>
+        <v>0.3798565046703669</v>
       </c>
       <c r="AL3">
-        <v>8.09</v>
+        <v>17.3</v>
       </c>
       <c r="AM3">
-        <v>8.09</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1290.494296577947</v>
+        <v>50.66558441558442</v>
       </c>
       <c r="AO3">
-        <v>-0.1915945611866502</v>
+        <v>0.3034682080924855</v>
       </c>
       <c r="AP3">
-        <v>-1072.623574144487</v>
+        <v>45.55194805194805</v>
       </c>
       <c r="AQ3">
-        <v>-0.1915945611866502</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="4">
@@ -850,25 +846,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.277</v>
+        <v>-0.276</v>
       </c>
       <c r="G4">
-        <v>-0.4519595448798989</v>
+        <v>-0.1026415094339623</v>
       </c>
       <c r="H4">
-        <v>-0.4519595448798989</v>
+        <v>-0.1026415094339623</v>
       </c>
       <c r="I4">
-        <v>-0.2932996207332491</v>
+        <v>-0.04611320754716981</v>
       </c>
       <c r="J4">
-        <v>-0.2932996207332491</v>
+        <v>-0.04611320754716981</v>
       </c>
       <c r="K4">
-        <v>-69.7</v>
+        <v>-7.79</v>
       </c>
       <c r="L4">
-        <v>-0.4405815423514539</v>
+        <v>-0.05879245283018868</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +888,8785 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>41.4</v>
+        <v>9.98</v>
       </c>
       <c r="V4">
-        <v>0.09027474923680767</v>
+        <v>0.04153141905950895</v>
       </c>
       <c r="W4">
-        <v>-0.06646324020215505</v>
+        <v>-0.007748930667462449</v>
       </c>
       <c r="X4">
-        <v>0.07615867439801725</v>
+        <v>0.1595091734980454</v>
       </c>
       <c r="Y4">
-        <v>-0.1426219146001723</v>
+        <v>-0.1672581041655079</v>
       </c>
       <c r="Z4">
-        <v>0.1009608511854923</v>
+        <v>0.0875512091978327</v>
       </c>
       <c r="AA4">
-        <v>-0.02961177936161088</v>
+        <v>-0.004037267080745342</v>
       </c>
       <c r="AB4">
-        <v>0.05142356606450364</v>
+        <v>0.09344652267297693</v>
       </c>
       <c r="AC4">
-        <v>-0.08103534542611451</v>
+        <v>-0.09748378975372227</v>
       </c>
       <c r="AD4">
-        <v>549.5</v>
+        <v>462</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>549.5</v>
+        <v>462</v>
       </c>
       <c r="AG4">
-        <v>508.1</v>
+        <v>452.02</v>
       </c>
       <c r="AH4">
-        <v>0.5450848130145819</v>
+        <v>0.6578385305425033</v>
       </c>
       <c r="AI4">
-        <v>0.3331312518945135</v>
+        <v>0.3255125766222786</v>
       </c>
       <c r="AJ4">
-        <v>0.5256025654287784</v>
+        <v>0.6529061705569679</v>
       </c>
       <c r="AK4">
-        <v>0.315962937628257</v>
+        <v>0.3207362415916896</v>
       </c>
       <c r="AL4">
-        <v>32.8</v>
+        <v>28.7</v>
       </c>
       <c r="AM4">
-        <v>32.8</v>
+        <v>28.7</v>
       </c>
       <c r="AN4">
-        <v>-12.48863636363636</v>
+        <v>-89.18918918918919</v>
       </c>
       <c r="AO4">
-        <v>-1.414634146341464</v>
+        <v>-0.2128919860627178</v>
       </c>
       <c r="AP4">
-        <v>-11.54772727272727</v>
+        <v>-87.26254826254826</v>
       </c>
       <c r="AQ4">
-        <v>-1.414634146341464</v>
+        <v>-0.2128919860627178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Résidences Dar Saada S.A (CBSE:RDS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CBSE:RDS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Development)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.87349566190876</v>
+      </c>
+      <c r="F2">
+        <v>0.06</v>
+      </c>
+      <c r="G2">
+        <v>45.2</v>
+      </c>
+      <c r="H2">
+        <v>379.404853315028</v>
+      </c>
+      <c r="I2">
+        <v>325.8</v>
+      </c>
+      <c r="J2">
+        <v>369.342853315028</v>
+      </c>
+      <c r="K2">
+        <v>312.1</v>
+      </c>
+      <c r="L2">
+        <v>21.438</v>
+      </c>
+      <c r="M2">
+        <v>0.0966429806296069</v>
+      </c>
+      <c r="N2">
+        <v>0.0898237112211078</v>
+      </c>
+      <c r="O2">
+        <v>0.0617073646788991</v>
+      </c>
+      <c r="P2">
+        <v>0.040572</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.337868771298101</v>
+      </c>
+      <c r="T2">
+        <v>0.0929674374692636</v>
+      </c>
+      <c r="U2">
+        <v>2.92198616590131</v>
+      </c>
+      <c r="V2">
+        <v>0.52923112714349</v>
+      </c>
+      <c r="W2">
+        <v>4.166420743126992</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>45.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.1023511934410034</v>
+      </c>
+      <c r="AC2">
+        <v>0.0894309633027523</v>
+      </c>
+      <c r="AD2">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>6.16</v>
+      </c>
+      <c r="AH2">
+        <v>0.908</v>
+      </c>
+      <c r="AI2">
+        <v>-3.33066907387547e-16</v>
+      </c>
+      <c r="AJ2">
+        <v>312.1</v>
+      </c>
+      <c r="AK2">
+        <v>312.1</v>
+      </c>
+      <c r="AL2">
+        <v>17.3</v>
+      </c>
+      <c r="AM2">
+        <v>312.1</v>
+      </c>
+      <c r="AN2">
+        <v>31.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09068240393428548</v>
+      </c>
+      <c r="C2">
+        <v>394.7299519697548</v>
+      </c>
+      <c r="D2">
+        <v>363.2299519697548</v>
+      </c>
+      <c r="E2">
+        <v>-312.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>31.5</v>
+      </c>
+      <c r="H2">
+        <v>45.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.16</v>
+      </c>
+      <c r="K2">
+        <v>0.908</v>
+      </c>
+      <c r="L2">
+        <v>5.252</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.252</v>
+      </c>
+      <c r="O2">
+        <v>1.62812</v>
+      </c>
+      <c r="P2">
+        <v>3.62388</v>
+      </c>
+      <c r="Q2">
+        <v>4.53188</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09068240393428548</v>
+      </c>
+      <c r="T2">
+        <v>0.5069057056397804</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.031533</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0904488984820892</v>
+      </c>
+      <c r="C3">
+        <v>392.7991200832789</v>
+      </c>
+      <c r="D3">
+        <v>364.8721200832789</v>
+      </c>
+      <c r="E3">
+        <v>-308.527</v>
+      </c>
+      <c r="F3">
+        <v>3.573</v>
+      </c>
+      <c r="G3">
+        <v>31.5</v>
+      </c>
+      <c r="H3">
+        <v>45.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.16</v>
+      </c>
+      <c r="K3">
+        <v>0.908</v>
+      </c>
+      <c r="L3">
+        <v>5.252</v>
+      </c>
+      <c r="M3">
+        <v>0.1632861</v>
+      </c>
+      <c r="N3">
+        <v>5.0887139</v>
+      </c>
+      <c r="O3">
+        <v>1.577501309</v>
+      </c>
+      <c r="P3">
+        <v>3.511212591</v>
+      </c>
+      <c r="Q3">
+        <v>4.419212591</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09104400856776687</v>
+      </c>
+      <c r="T3">
+        <v>0.5104386848003002</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.031533</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>32.16440346116417</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.0902153930298929</v>
+      </c>
+      <c r="C4">
+        <v>390.8832041659452</v>
+      </c>
+      <c r="D4">
+        <v>366.5292041659453</v>
+      </c>
+      <c r="E4">
+        <v>-304.954</v>
+      </c>
+      <c r="F4">
+        <v>7.146000000000001</v>
+      </c>
+      <c r="G4">
+        <v>31.5</v>
+      </c>
+      <c r="H4">
+        <v>45.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.16</v>
+      </c>
+      <c r="K4">
+        <v>0.908</v>
+      </c>
+      <c r="L4">
+        <v>5.252</v>
+      </c>
+      <c r="M4">
+        <v>0.3265722000000001</v>
+      </c>
+      <c r="N4">
+        <v>4.9254278</v>
+      </c>
+      <c r="O4">
+        <v>1.526882618</v>
+      </c>
+      <c r="P4">
+        <v>3.398545181999999</v>
+      </c>
+      <c r="Q4">
+        <v>4.306545182</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09141299288764582</v>
+      </c>
+      <c r="T4">
+        <v>0.5140437655763407</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.031533</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>16.08220173058209</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09001500757769662</v>
+      </c>
+      <c r="C5">
+        <v>388.7442978778033</v>
+      </c>
+      <c r="D5">
+        <v>367.9632978778033</v>
+      </c>
+      <c r="E5">
+        <v>-301.381</v>
+      </c>
+      <c r="F5">
+        <v>10.719</v>
+      </c>
+      <c r="G5">
+        <v>31.5</v>
+      </c>
+      <c r="H5">
+        <v>45.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.16</v>
+      </c>
+      <c r="K5">
+        <v>0.908</v>
+      </c>
+      <c r="L5">
+        <v>5.252</v>
+      </c>
+      <c r="M5">
+        <v>0.5070087</v>
+      </c>
+      <c r="N5">
+        <v>4.7449913</v>
+      </c>
+      <c r="O5">
+        <v>1.470947303</v>
+      </c>
+      <c r="P5">
+        <v>3.274043997</v>
+      </c>
+      <c r="Q5">
+        <v>4.182043997</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09178958513164599</v>
+      </c>
+      <c r="T5">
+        <v>0.5177231779147736</v>
+      </c>
+      <c r="U5">
+        <v>0.0473</v>
+      </c>
+      <c r="V5">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.032637</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>10.35879660447641</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08994986212550034</v>
+      </c>
+      <c r="C6">
+        <v>385.6399430399949</v>
+      </c>
+      <c r="D6">
+        <v>368.4319430399949</v>
+      </c>
+      <c r="E6">
+        <v>-297.808</v>
+      </c>
+      <c r="F6">
+        <v>14.292</v>
+      </c>
+      <c r="G6">
+        <v>31.5</v>
+      </c>
+      <c r="H6">
+        <v>45.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.16</v>
+      </c>
+      <c r="K6">
+        <v>0.908</v>
+      </c>
+      <c r="L6">
+        <v>5.252</v>
+      </c>
+      <c r="M6">
+        <v>0.7574760000000001</v>
+      </c>
+      <c r="N6">
+        <v>4.494523999999999</v>
+      </c>
+      <c r="O6">
+        <v>1.39330244</v>
+      </c>
+      <c r="P6">
+        <v>3.101221559999999</v>
+      </c>
+      <c r="Q6">
+        <v>4.009221559999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09217402304739619</v>
+      </c>
+      <c r="T6">
+        <v>0.5214792446769242</v>
+      </c>
+      <c r="U6">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V6">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.03657</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>6.933553010260389</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08983572667330406</v>
+      </c>
+      <c r="C7">
+        <v>382.8908981232958</v>
+      </c>
+      <c r="D7">
+        <v>369.2558981232958</v>
+      </c>
+      <c r="E7">
+        <v>-294.235</v>
+      </c>
+      <c r="F7">
+        <v>17.865</v>
+      </c>
+      <c r="G7">
+        <v>31.5</v>
+      </c>
+      <c r="H7">
+        <v>45.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.16</v>
+      </c>
+      <c r="K7">
+        <v>0.908</v>
+      </c>
+      <c r="L7">
+        <v>5.252</v>
+      </c>
+      <c r="M7">
+        <v>0.9825750000000001</v>
+      </c>
+      <c r="N7">
+        <v>4.269425</v>
+      </c>
+      <c r="O7">
+        <v>1.32352175</v>
+      </c>
+      <c r="P7">
+        <v>2.94590325</v>
+      </c>
+      <c r="Q7">
+        <v>3.85390325</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09256655439295164</v>
+      </c>
+      <c r="T7">
+        <v>0.5253143865288041</v>
+      </c>
+      <c r="U7">
+        <v>0.055</v>
+      </c>
+      <c r="V7">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.03795</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>5.345139047909829</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08982371122110777</v>
+      </c>
+      <c r="C8">
+        <v>379.4048533150276</v>
+      </c>
+      <c r="D8">
+        <v>369.3428533150276</v>
+      </c>
+      <c r="E8">
+        <v>-290.662</v>
+      </c>
+      <c r="F8">
+        <v>21.438</v>
+      </c>
+      <c r="G8">
+        <v>31.5</v>
+      </c>
+      <c r="H8">
+        <v>45.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.16</v>
+      </c>
+      <c r="K8">
+        <v>0.908</v>
+      </c>
+      <c r="L8">
+        <v>5.252</v>
+      </c>
+      <c r="M8">
+        <v>1.2605544</v>
+      </c>
+      <c r="N8">
+        <v>3.9914456</v>
+      </c>
+      <c r="O8">
+        <v>1.237348136</v>
+      </c>
+      <c r="P8">
+        <v>2.754097464</v>
+      </c>
+      <c r="Q8">
+        <v>3.662097463999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09296743746926359</v>
+      </c>
+      <c r="T8">
+        <v>0.52923112714349</v>
+      </c>
+      <c r="U8">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.040572</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>4.166420743126992</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09125517576891146</v>
+      </c>
+      <c r="C9">
+        <v>365.752748769953</v>
+      </c>
+      <c r="D9">
+        <v>359.2637487699531</v>
+      </c>
+      <c r="E9">
+        <v>-287.089</v>
+      </c>
+      <c r="F9">
+        <v>25.011</v>
+      </c>
+      <c r="G9">
+        <v>31.5</v>
+      </c>
+      <c r="H9">
+        <v>45.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.16</v>
+      </c>
+      <c r="K9">
+        <v>0.908</v>
+      </c>
+      <c r="L9">
+        <v>5.252</v>
+      </c>
+      <c r="M9">
+        <v>2.286005400000001</v>
+      </c>
+      <c r="N9">
+        <v>2.965994599999999</v>
+      </c>
+      <c r="O9">
+        <v>0.9194583259999999</v>
+      </c>
+      <c r="P9">
+        <v>2.046536273999999</v>
+      </c>
+      <c r="Q9">
+        <v>2.954536273999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09337694168700159</v>
+      </c>
+      <c r="T9">
+        <v>0.5332320987391368</v>
+      </c>
+      <c r="U9">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V9">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.063066</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>2.297457390083155</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.0913370003167152</v>
+      </c>
+      <c r="C10">
+        <v>361.6202079966283</v>
+      </c>
+      <c r="D10">
+        <v>358.7042079966283</v>
+      </c>
+      <c r="E10">
+        <v>-283.516</v>
+      </c>
+      <c r="F10">
+        <v>28.584</v>
+      </c>
+      <c r="G10">
+        <v>31.5</v>
+      </c>
+      <c r="H10">
+        <v>45.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.16</v>
+      </c>
+      <c r="K10">
+        <v>0.908</v>
+      </c>
+      <c r="L10">
+        <v>5.252</v>
+      </c>
+      <c r="M10">
+        <v>2.612577600000001</v>
+      </c>
+      <c r="N10">
+        <v>2.639422399999999</v>
+      </c>
+      <c r="O10">
+        <v>0.8182209439999999</v>
+      </c>
+      <c r="P10">
+        <v>1.821201455999999</v>
+      </c>
+      <c r="Q10">
+        <v>2.729201455999999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.0937953481703426</v>
+      </c>
+      <c r="T10">
+        <v>0.5373200479781672</v>
+      </c>
+      <c r="U10">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.063066</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>2.010275216322761</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09912515936414572</v>
+      </c>
+      <c r="C11">
+        <v>311.7374186432868</v>
+      </c>
+      <c r="D11">
+        <v>312.3944186432868</v>
+      </c>
+      <c r="E11">
+        <v>-279.943</v>
+      </c>
+      <c r="F11">
+        <v>32.157</v>
+      </c>
+      <c r="G11">
+        <v>31.5</v>
+      </c>
+      <c r="H11">
+        <v>45.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.16</v>
+      </c>
+      <c r="K11">
+        <v>0.908</v>
+      </c>
+      <c r="L11">
+        <v>5.252</v>
+      </c>
+      <c r="M11">
+        <v>6.322066199999999</v>
+      </c>
+      <c r="N11">
+        <v>-1.070066199999999</v>
+      </c>
+      <c r="O11">
+        <v>-0.3317205219999999</v>
+      </c>
+      <c r="P11">
+        <v>-0.7383456779999995</v>
+      </c>
+      <c r="Q11">
+        <v>0.1696543220000005</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09449218725548225</v>
+      </c>
+      <c r="T11">
+        <v>0.5441283621923179</v>
+      </c>
+      <c r="U11">
+        <v>0.1966</v>
+      </c>
+      <c r="V11">
+        <v>0.257529729758287</v>
+      </c>
+      <c r="W11">
+        <v>0.1459696551295208</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.8307410637364095</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1025199003966382</v>
+      </c>
+      <c r="C12">
+        <v>291.5212954637352</v>
+      </c>
+      <c r="D12">
+        <v>295.7512954637352</v>
+      </c>
+      <c r="E12">
+        <v>-276.37</v>
+      </c>
+      <c r="F12">
+        <v>35.73</v>
+      </c>
+      <c r="G12">
+        <v>31.5</v>
+      </c>
+      <c r="H12">
+        <v>45.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.16</v>
+      </c>
+      <c r="K12">
+        <v>0.908</v>
+      </c>
+      <c r="L12">
+        <v>5.252</v>
+      </c>
+      <c r="M12">
+        <v>7.639074000000001</v>
+      </c>
+      <c r="N12">
+        <v>-2.387074000000001</v>
+      </c>
+      <c r="O12">
+        <v>-0.7399929400000005</v>
+      </c>
+      <c r="P12">
+        <v>-1.647081060000001</v>
+      </c>
+      <c r="Q12">
+        <v>-0.7390810600000005</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09521847937220153</v>
+      </c>
+      <c r="T12">
+        <v>0.5512244408241505</v>
+      </c>
+      <c r="U12">
+        <v>0.2138</v>
+      </c>
+      <c r="V12">
+        <v>0.2131305443565542</v>
+      </c>
+      <c r="W12">
+        <v>0.1682326896165687</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.6875178850211425</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1042699003966383</v>
+      </c>
+      <c r="C13">
+        <v>280.0429104864255</v>
+      </c>
+      <c r="D13">
+        <v>287.8459104864255</v>
+      </c>
+      <c r="E13">
+        <v>-272.797</v>
+      </c>
+      <c r="F13">
+        <v>39.303</v>
+      </c>
+      <c r="G13">
+        <v>31.5</v>
+      </c>
+      <c r="H13">
+        <v>45.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.16</v>
+      </c>
+      <c r="K13">
+        <v>0.908</v>
+      </c>
+      <c r="L13">
+        <v>5.252</v>
+      </c>
+      <c r="M13">
+        <v>8.4029814</v>
+      </c>
+      <c r="N13">
+        <v>-3.1509814</v>
+      </c>
+      <c r="O13">
+        <v>-0.9768042340000002</v>
+      </c>
+      <c r="P13">
+        <v>-2.174177166</v>
+      </c>
+      <c r="Q13">
+        <v>-1.266177166</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09585239487076561</v>
+      </c>
+      <c r="T13">
+        <v>0.5574179738671186</v>
+      </c>
+      <c r="U13">
+        <v>0.2138</v>
+      </c>
+      <c r="V13">
+        <v>0.1937550403241402</v>
+      </c>
+      <c r="W13">
+        <v>0.1723751723786988</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.6250162591101296</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1060199003966383</v>
+      </c>
+      <c r="C14">
+        <v>268.9761424150817</v>
+      </c>
+      <c r="D14">
+        <v>280.3521424150817</v>
+      </c>
+      <c r="E14">
+        <v>-269.224</v>
+      </c>
+      <c r="F14">
+        <v>42.876</v>
+      </c>
+      <c r="G14">
+        <v>31.5</v>
+      </c>
+      <c r="H14">
+        <v>45.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.16</v>
+      </c>
+      <c r="K14">
+        <v>0.908</v>
+      </c>
+      <c r="L14">
+        <v>5.252</v>
+      </c>
+      <c r="M14">
+        <v>9.166888799999999</v>
+      </c>
+      <c r="N14">
+        <v>-3.914888799999999</v>
+      </c>
+      <c r="O14">
+        <v>-1.213615528</v>
+      </c>
+      <c r="P14">
+        <v>-2.701273271999999</v>
+      </c>
+      <c r="Q14">
+        <v>-1.793273271999999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09650071753975156</v>
+      </c>
+      <c r="T14">
+        <v>0.5637522690246993</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0.1776087869637952</v>
+      </c>
+      <c r="W14">
+        <v>0.1758272413471406</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.5729315708509523</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1077699003966383</v>
+      </c>
+      <c r="C15">
+        <v>258.2896589040876</v>
+      </c>
+      <c r="D15">
+        <v>273.2386589040876</v>
+      </c>
+      <c r="E15">
+        <v>-265.651</v>
+      </c>
+      <c r="F15">
+        <v>46.44900000000001</v>
+      </c>
+      <c r="G15">
+        <v>31.5</v>
+      </c>
+      <c r="H15">
+        <v>45.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.16</v>
+      </c>
+      <c r="K15">
+        <v>0.908</v>
+      </c>
+      <c r="L15">
+        <v>5.252</v>
+      </c>
+      <c r="M15">
+        <v>9.930796200000001</v>
+      </c>
+      <c r="N15">
+        <v>-4.678796200000002</v>
+      </c>
+      <c r="O15">
+        <v>-1.450426822000001</v>
+      </c>
+      <c r="P15">
+        <v>-3.228369378000001</v>
+      </c>
+      <c r="Q15">
+        <v>-2.320369378000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09716394417813952</v>
+      </c>
+      <c r="T15">
+        <v>0.5702321801629143</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1639465725819648</v>
+      </c>
+      <c r="W15">
+        <v>0.1787482227819759</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.528859911554725</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1131356638492455</v>
+      </c>
+      <c r="C16">
+        <v>234.9935013526824</v>
+      </c>
+      <c r="D16">
+        <v>253.5155013526823</v>
+      </c>
+      <c r="E16">
+        <v>-262.078</v>
+      </c>
+      <c r="F16">
+        <v>50.02200000000001</v>
+      </c>
+      <c r="G16">
+        <v>31.5</v>
+      </c>
+      <c r="H16">
+        <v>45.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.16</v>
+      </c>
+      <c r="K16">
+        <v>0.908</v>
+      </c>
+      <c r="L16">
+        <v>5.252</v>
+      </c>
+      <c r="M16">
+        <v>11.9452536</v>
+      </c>
+      <c r="N16">
+        <v>-6.693253600000003</v>
+      </c>
+      <c r="O16">
+        <v>-2.074908616000001</v>
+      </c>
+      <c r="P16">
+        <v>-4.618344984000002</v>
+      </c>
+      <c r="Q16">
+        <v>-3.710344984000002</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09797720335766116</v>
+      </c>
+      <c r="T16">
+        <v>0.578177951503533</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.1362984876269182</v>
+      </c>
+      <c r="W16">
+        <v>0.2062519211546919</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.439672540731994</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1151356638492455</v>
+      </c>
+      <c r="C17">
+        <v>224.7783765955479</v>
+      </c>
+      <c r="D17">
+        <v>246.873376595548</v>
+      </c>
+      <c r="E17">
+        <v>-258.505</v>
+      </c>
+      <c r="F17">
+        <v>53.595</v>
+      </c>
+      <c r="G17">
+        <v>31.5</v>
+      </c>
+      <c r="H17">
+        <v>45.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.16</v>
+      </c>
+      <c r="K17">
+        <v>0.908</v>
+      </c>
+      <c r="L17">
+        <v>5.252</v>
+      </c>
+      <c r="M17">
+        <v>12.798486</v>
+      </c>
+      <c r="N17">
+        <v>-7.546486000000001</v>
+      </c>
+      <c r="O17">
+        <v>-2.33941066</v>
+      </c>
+      <c r="P17">
+        <v>-5.20707534</v>
+      </c>
+      <c r="Q17">
+        <v>-4.29907534</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09867340575010422</v>
+      </c>
+      <c r="T17">
+        <v>0.5849800450506333</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.1272119217851237</v>
+      </c>
+      <c r="W17">
+        <v>0.2084217930777125</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.4103610380165279</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1171356638492455</v>
+      </c>
+      <c r="C18">
+        <v>214.9024140759311</v>
+      </c>
+      <c r="D18">
+        <v>240.5704140759311</v>
+      </c>
+      <c r="E18">
+        <v>-254.932</v>
+      </c>
+      <c r="F18">
+        <v>57.16800000000001</v>
+      </c>
+      <c r="G18">
+        <v>31.5</v>
+      </c>
+      <c r="H18">
+        <v>45.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.16</v>
+      </c>
+      <c r="K18">
+        <v>0.908</v>
+      </c>
+      <c r="L18">
+        <v>5.252</v>
+      </c>
+      <c r="M18">
+        <v>13.6517184</v>
+      </c>
+      <c r="N18">
+        <v>-8.399718400000001</v>
+      </c>
+      <c r="O18">
+        <v>-2.603912704000001</v>
+      </c>
+      <c r="P18">
+        <v>-5.795805696</v>
+      </c>
+      <c r="Q18">
+        <v>-4.887805696</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09938618438998642</v>
+      </c>
+      <c r="T18">
+        <v>0.5919440932059981</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.1192611766735534</v>
+      </c>
+      <c r="W18">
+        <v>0.2103204310103555</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.3847134731404949</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1191356638492455</v>
+      </c>
+      <c r="C19">
+        <v>205.3402829092957</v>
+      </c>
+      <c r="D19">
+        <v>234.5812829092957</v>
+      </c>
+      <c r="E19">
+        <v>-251.359</v>
+      </c>
+      <c r="F19">
+        <v>60.74100000000001</v>
+      </c>
+      <c r="G19">
+        <v>31.5</v>
+      </c>
+      <c r="H19">
+        <v>45.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.16</v>
+      </c>
+      <c r="K19">
+        <v>0.908</v>
+      </c>
+      <c r="L19">
+        <v>5.252</v>
+      </c>
+      <c r="M19">
+        <v>14.5049508</v>
+      </c>
+      <c r="N19">
+        <v>-9.252950800000004</v>
+      </c>
+      <c r="O19">
+        <v>-2.868414748000002</v>
+      </c>
+      <c r="P19">
+        <v>-6.384536052000002</v>
+      </c>
+      <c r="Q19">
+        <v>-5.476536052000002</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1001161384187814</v>
+      </c>
+      <c r="T19">
+        <v>0.5990759497506487</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.112245813339815</v>
+      </c>
+      <c r="W19">
+        <v>0.2119956997744522</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.3620832688381127</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1211356638492455</v>
+      </c>
+      <c r="C20">
+        <v>196.06911344196</v>
+      </c>
+      <c r="D20">
+        <v>228.88311344196</v>
+      </c>
+      <c r="E20">
+        <v>-247.786</v>
+      </c>
+      <c r="F20">
+        <v>64.31399999999999</v>
+      </c>
+      <c r="G20">
+        <v>31.5</v>
+      </c>
+      <c r="H20">
+        <v>45.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.16</v>
+      </c>
+      <c r="K20">
+        <v>0.908</v>
+      </c>
+      <c r="L20">
+        <v>5.252</v>
+      </c>
+      <c r="M20">
+        <v>15.3581832</v>
+      </c>
+      <c r="N20">
+        <v>-10.1061832</v>
+      </c>
+      <c r="O20">
+        <v>-3.132916792000001</v>
+      </c>
+      <c r="P20">
+        <v>-6.973266408</v>
+      </c>
+      <c r="Q20">
+        <v>-6.065266407999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1008638962043763</v>
+      </c>
+      <c r="T20">
+        <v>0.6063817540159004</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.1060099348209364</v>
+      </c>
+      <c r="W20">
+        <v>0.2134848275647604</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.3419675316804398</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1231356638492455</v>
+      </c>
+      <c r="C21">
+        <v>187.0682054136055</v>
+      </c>
+      <c r="D21">
+        <v>223.4552054136055</v>
+      </c>
+      <c r="E21">
+        <v>-244.213</v>
+      </c>
+      <c r="F21">
+        <v>67.887</v>
+      </c>
+      <c r="G21">
+        <v>31.5</v>
+      </c>
+      <c r="H21">
+        <v>45.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.16</v>
+      </c>
+      <c r="K21">
+        <v>0.908</v>
+      </c>
+      <c r="L21">
+        <v>5.252</v>
+      </c>
+      <c r="M21">
+        <v>16.2114156</v>
+      </c>
+      <c r="N21">
+        <v>-10.9594156</v>
+      </c>
+      <c r="O21">
+        <v>-3.397418836000002</v>
+      </c>
+      <c r="P21">
+        <v>-7.561996764000002</v>
+      </c>
+      <c r="Q21">
+        <v>-6.653996764000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1016301171451711</v>
+      </c>
+      <c r="T21">
+        <v>0.6138679485099239</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.1004304645672029</v>
+      </c>
+      <c r="W21">
+        <v>0.214817205061352</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.323969240539364</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1251356638492455</v>
+      </c>
+      <c r="C22">
+        <v>178.3187766829759</v>
+      </c>
+      <c r="D22">
+        <v>218.2787766829759</v>
+      </c>
+      <c r="E22">
+        <v>-240.64</v>
+      </c>
+      <c r="F22">
+        <v>71.46000000000001</v>
+      </c>
+      <c r="G22">
+        <v>31.5</v>
+      </c>
+      <c r="H22">
+        <v>45.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.16</v>
+      </c>
+      <c r="K22">
+        <v>0.908</v>
+      </c>
+      <c r="L22">
+        <v>5.252</v>
+      </c>
+      <c r="M22">
+        <v>17.064648</v>
+      </c>
+      <c r="N22">
+        <v>-11.812648</v>
+      </c>
+      <c r="O22">
+        <v>-3.661920880000002</v>
+      </c>
+      <c r="P22">
+        <v>-8.150727120000001</v>
+      </c>
+      <c r="Q22">
+        <v>-7.242727120000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1024154936094857</v>
+      </c>
+      <c r="T22">
+        <v>0.621541297866298</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.09540894133884274</v>
+      </c>
+      <c r="W22">
+        <v>0.2160163448082844</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3077707785123959</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1271356638492455</v>
+      </c>
+      <c r="C23">
+        <v>169.8037460880513</v>
+      </c>
+      <c r="D23">
+        <v>213.3367460880513</v>
+      </c>
+      <c r="E23">
+        <v>-237.067</v>
+      </c>
+      <c r="F23">
+        <v>75.033</v>
+      </c>
+      <c r="G23">
+        <v>31.5</v>
+      </c>
+      <c r="H23">
+        <v>45.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.16</v>
+      </c>
+      <c r="K23">
+        <v>0.908</v>
+      </c>
+      <c r="L23">
+        <v>5.252</v>
+      </c>
+      <c r="M23">
+        <v>17.9178804</v>
+      </c>
+      <c r="N23">
+        <v>-12.6658804</v>
+      </c>
+      <c r="O23">
+        <v>-3.926422924000001</v>
+      </c>
+      <c r="P23">
+        <v>-8.739457476000002</v>
+      </c>
+      <c r="Q23">
+        <v>-7.831457476000002</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1032207530222641</v>
+      </c>
+      <c r="T23">
+        <v>0.6294089092316941</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.09086565841794547</v>
+      </c>
+      <c r="W23">
+        <v>0.2171012807697946</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.2931150271546626</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1291356638492455</v>
+      </c>
+      <c r="C24">
+        <v>161.5075451506215</v>
+      </c>
+      <c r="D24">
+        <v>208.6135451506215</v>
+      </c>
+      <c r="E24">
+        <v>-233.494</v>
+      </c>
+      <c r="F24">
+        <v>78.60600000000001</v>
+      </c>
+      <c r="G24">
+        <v>31.5</v>
+      </c>
+      <c r="H24">
+        <v>45.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.16</v>
+      </c>
+      <c r="K24">
+        <v>0.908</v>
+      </c>
+      <c r="L24">
+        <v>5.252</v>
+      </c>
+      <c r="M24">
+        <v>18.7711128</v>
+      </c>
+      <c r="N24">
+        <v>-13.51911280000001</v>
+      </c>
+      <c r="O24">
+        <v>-4.190924968000003</v>
+      </c>
+      <c r="P24">
+        <v>-9.328187832000003</v>
+      </c>
+      <c r="Q24">
+        <v>-8.420187832000003</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1040466601122931</v>
+      </c>
+      <c r="T24">
+        <v>0.637478254221844</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.08673540121712975</v>
+      </c>
+      <c r="W24">
+        <v>0.2180875861893494</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.2797916168294508</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1311356638492455</v>
+      </c>
+      <c r="C25">
+        <v>153.4159542518498</v>
+      </c>
+      <c r="D25">
+        <v>204.0949542518498</v>
+      </c>
+      <c r="E25">
+        <v>-229.921</v>
+      </c>
+      <c r="F25">
+        <v>82.179</v>
+      </c>
+      <c r="G25">
+        <v>31.5</v>
+      </c>
+      <c r="H25">
+        <v>45.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.16</v>
+      </c>
+      <c r="K25">
+        <v>0.908</v>
+      </c>
+      <c r="L25">
+        <v>5.252</v>
+      </c>
+      <c r="M25">
+        <v>19.6243452</v>
+      </c>
+      <c r="N25">
+        <v>-14.3723452</v>
+      </c>
+      <c r="O25">
+        <v>-4.455427012000001</v>
+      </c>
+      <c r="P25">
+        <v>-9.916918188</v>
+      </c>
+      <c r="Q25">
+        <v>-9.008918188000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1048940193345306</v>
+      </c>
+      <c r="T25">
+        <v>0.6457571925883614</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.08296429681638499</v>
+      </c>
+      <c r="W25">
+        <v>0.2189881259202473</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.2676267639238225</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1331356638492454</v>
+      </c>
+      <c r="C26">
+        <v>145.5159596471793</v>
+      </c>
+      <c r="D26">
+        <v>199.7679596471793</v>
+      </c>
+      <c r="E26">
+        <v>-226.348</v>
+      </c>
+      <c r="F26">
+        <v>85.752</v>
+      </c>
+      <c r="G26">
+        <v>31.5</v>
+      </c>
+      <c r="H26">
+        <v>45.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.16</v>
+      </c>
+      <c r="K26">
+        <v>0.908</v>
+      </c>
+      <c r="L26">
+        <v>5.252</v>
+      </c>
+      <c r="M26">
+        <v>20.4775776</v>
+      </c>
+      <c r="N26">
+        <v>-15.2255776</v>
+      </c>
+      <c r="O26">
+        <v>-4.719929056000002</v>
+      </c>
+      <c r="P26">
+        <v>-10.505648544</v>
+      </c>
+      <c r="Q26">
+        <v>-9.597648544</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1057636774836692</v>
+      </c>
+      <c r="T26">
+        <v>0.6542539977539977</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.07950745111570229</v>
+      </c>
+      <c r="W26">
+        <v>0.2198136206735703</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.2564756487603299</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1351356638492455</v>
+      </c>
+      <c r="C27">
+        <v>137.7956282920999</v>
+      </c>
+      <c r="D27">
+        <v>195.6206282920999</v>
+      </c>
+      <c r="E27">
+        <v>-222.775</v>
+      </c>
+      <c r="F27">
+        <v>89.325</v>
+      </c>
+      <c r="G27">
+        <v>31.5</v>
+      </c>
+      <c r="H27">
+        <v>45.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.16</v>
+      </c>
+      <c r="K27">
+        <v>0.908</v>
+      </c>
+      <c r="L27">
+        <v>5.252</v>
+      </c>
+      <c r="M27">
+        <v>21.33081</v>
+      </c>
+      <c r="N27">
+        <v>-16.07881</v>
+      </c>
+      <c r="O27">
+        <v>-4.984431100000002</v>
+      </c>
+      <c r="P27">
+        <v>-11.0943789</v>
+      </c>
+      <c r="Q27">
+        <v>-10.1863789</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1066565265167848</v>
+      </c>
+      <c r="T27">
+        <v>0.6629773843907178</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.07632715307107418</v>
+      </c>
+      <c r="W27">
+        <v>0.2205730758466275</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.2462166228099166</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1371356638492455</v>
+      </c>
+      <c r="C28">
+        <v>130.2439979430538</v>
+      </c>
+      <c r="D28">
+        <v>191.6419979430538</v>
+      </c>
+      <c r="E28">
+        <v>-219.202</v>
+      </c>
+      <c r="F28">
+        <v>92.89800000000001</v>
+      </c>
+      <c r="G28">
+        <v>31.5</v>
+      </c>
+      <c r="H28">
+        <v>45.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.16</v>
+      </c>
+      <c r="K28">
+        <v>0.908</v>
+      </c>
+      <c r="L28">
+        <v>5.252</v>
+      </c>
+      <c r="M28">
+        <v>22.1840424</v>
+      </c>
+      <c r="N28">
+        <v>-16.9320424</v>
+      </c>
+      <c r="O28">
+        <v>-5.248933144000002</v>
+      </c>
+      <c r="P28">
+        <v>-11.683109256</v>
+      </c>
+      <c r="Q28">
+        <v>-10.775109256</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1075735066048494</v>
+      </c>
+      <c r="T28">
+        <v>0.6719365382338356</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.07339149333757133</v>
+      </c>
+      <c r="W28">
+        <v>0.221274111390988</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.236746752701843</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1391356638492455</v>
+      </c>
+      <c r="C29">
+        <v>122.8509804021125</v>
+      </c>
+      <c r="D29">
+        <v>187.8219804021125</v>
+      </c>
+      <c r="E29">
+        <v>-215.629</v>
+      </c>
+      <c r="F29">
+        <v>96.471</v>
+      </c>
+      <c r="G29">
+        <v>31.5</v>
+      </c>
+      <c r="H29">
+        <v>45.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.16</v>
+      </c>
+      <c r="K29">
+        <v>0.908</v>
+      </c>
+      <c r="L29">
+        <v>5.252</v>
+      </c>
+      <c r="M29">
+        <v>23.0372748</v>
+      </c>
+      <c r="N29">
+        <v>-17.7852748</v>
+      </c>
+      <c r="O29">
+        <v>-5.513435188000002</v>
+      </c>
+      <c r="P29">
+        <v>-12.271839612</v>
+      </c>
+      <c r="Q29">
+        <v>-11.363839612</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1085156094350529</v>
+      </c>
+      <c r="T29">
+        <v>0.6811411483466279</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.07067328988062425</v>
+      </c>
+      <c r="W29">
+        <v>0.2219232183765069</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2279783544536266</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1411356638492455</v>
+      </c>
+      <c r="C30">
+        <v>115.607276107297</v>
+      </c>
+      <c r="D30">
+        <v>184.151276107297</v>
+      </c>
+      <c r="E30">
+        <v>-212.056</v>
+      </c>
+      <c r="F30">
+        <v>100.044</v>
+      </c>
+      <c r="G30">
+        <v>31.5</v>
+      </c>
+      <c r="H30">
+        <v>45.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.16</v>
+      </c>
+      <c r="K30">
+        <v>0.908</v>
+      </c>
+      <c r="L30">
+        <v>5.252</v>
+      </c>
+      <c r="M30">
+        <v>23.89050720000001</v>
+      </c>
+      <c r="N30">
+        <v>-18.63850720000001</v>
+      </c>
+      <c r="O30">
+        <v>-5.777937232000003</v>
+      </c>
+      <c r="P30">
+        <v>-12.860569968</v>
+      </c>
+      <c r="Q30">
+        <v>-11.952569968</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1094838817883175</v>
+      </c>
+      <c r="T30">
+        <v>0.6906014420736645</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.06814924381345909</v>
+      </c>
+      <c r="W30">
+        <v>0.222525960577346</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.219836270365997</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1431356638492455</v>
+      </c>
+      <c r="C31">
+        <v>108.5042985461559</v>
+      </c>
+      <c r="D31">
+        <v>180.6212985461559</v>
+      </c>
+      <c r="E31">
+        <v>-208.483</v>
+      </c>
+      <c r="F31">
+        <v>103.617</v>
+      </c>
+      <c r="G31">
+        <v>31.5</v>
+      </c>
+      <c r="H31">
+        <v>45.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.16</v>
+      </c>
+      <c r="K31">
+        <v>0.908</v>
+      </c>
+      <c r="L31">
+        <v>5.252</v>
+      </c>
+      <c r="M31">
+        <v>24.7437396</v>
+      </c>
+      <c r="N31">
+        <v>-19.4917396</v>
+      </c>
+      <c r="O31">
+        <v>-6.042439276000001</v>
+      </c>
+      <c r="P31">
+        <v>-13.449300324</v>
+      </c>
+      <c r="Q31">
+        <v>-12.541300324</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1104794294191389</v>
+      </c>
+      <c r="T31">
+        <v>0.7003282229479413</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.06579926988885708</v>
+      </c>
+      <c r="W31">
+        <v>0.2230871343505409</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2122557093188937</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1451356638492455</v>
+      </c>
+      <c r="C32">
+        <v>101.5341071992861</v>
+      </c>
+      <c r="D32">
+        <v>177.2241071992861</v>
+      </c>
+      <c r="E32">
+        <v>-204.91</v>
+      </c>
+      <c r="F32">
+        <v>107.19</v>
+      </c>
+      <c r="G32">
+        <v>31.5</v>
+      </c>
+      <c r="H32">
+        <v>45.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.16</v>
+      </c>
+      <c r="K32">
+        <v>0.908</v>
+      </c>
+      <c r="L32">
+        <v>5.252</v>
+      </c>
+      <c r="M32">
+        <v>25.596972</v>
+      </c>
+      <c r="N32">
+        <v>-20.344972</v>
+      </c>
+      <c r="O32">
+        <v>-6.306941320000002</v>
+      </c>
+      <c r="P32">
+        <v>-14.03803068</v>
+      </c>
+      <c r="Q32">
+        <v>-13.13003068</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1115034212679837</v>
+      </c>
+      <c r="T32">
+        <v>0.7103329118471977</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.06360596089256183</v>
+      </c>
+      <c r="W32">
+        <v>0.2236108965388562</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.205180519008264</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1471356638492455</v>
+      </c>
+      <c r="C33">
+        <v>94.68934791148772</v>
+      </c>
+      <c r="D33">
+        <v>173.9523479114877</v>
+      </c>
+      <c r="E33">
+        <v>-201.337</v>
+      </c>
+      <c r="F33">
+        <v>110.763</v>
+      </c>
+      <c r="G33">
+        <v>31.5</v>
+      </c>
+      <c r="H33">
+        <v>45.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.16</v>
+      </c>
+      <c r="K33">
+        <v>0.908</v>
+      </c>
+      <c r="L33">
+        <v>5.252</v>
+      </c>
+      <c r="M33">
+        <v>26.4502044</v>
+      </c>
+      <c r="N33">
+        <v>-21.19820440000001</v>
+      </c>
+      <c r="O33">
+        <v>-6.571443364000003</v>
+      </c>
+      <c r="P33">
+        <v>-14.626761036</v>
+      </c>
+      <c r="Q33">
+        <v>-13.718761036</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1125570940399835</v>
+      </c>
+      <c r="T33">
+        <v>0.7206275917290411</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.06155415570247918</v>
+      </c>
+      <c r="W33">
+        <v>0.224100867618248</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.1985617925886425</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1491356638492455</v>
+      </c>
+      <c r="C34">
+        <v>87.96319974809487</v>
+      </c>
+      <c r="D34">
+        <v>170.7991997480949</v>
+      </c>
+      <c r="E34">
+        <v>-197.764</v>
+      </c>
+      <c r="F34">
+        <v>114.336</v>
+      </c>
+      <c r="G34">
+        <v>31.5</v>
+      </c>
+      <c r="H34">
+        <v>45.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.16</v>
+      </c>
+      <c r="K34">
+        <v>0.908</v>
+      </c>
+      <c r="L34">
+        <v>5.252</v>
+      </c>
+      <c r="M34">
+        <v>27.3034368</v>
+      </c>
+      <c r="N34">
+        <v>-22.0514368</v>
+      </c>
+      <c r="O34">
+        <v>-6.835945408000002</v>
+      </c>
+      <c r="P34">
+        <v>-15.215491392</v>
+      </c>
+      <c r="Q34">
+        <v>-14.307491392</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1136417571876303</v>
+      </c>
+      <c r="T34">
+        <v>0.7312250563132917</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05963058833677671</v>
+      </c>
+      <c r="W34">
+        <v>0.2245602155051777</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.1923567365702474</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1511356638492455</v>
+      </c>
+      <c r="C35">
+        <v>81.34932752825726</v>
+      </c>
+      <c r="D35">
+        <v>167.7583275282573</v>
+      </c>
+      <c r="E35">
+        <v>-194.191</v>
+      </c>
+      <c r="F35">
+        <v>117.909</v>
+      </c>
+      <c r="G35">
+        <v>31.5</v>
+      </c>
+      <c r="H35">
+        <v>45.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.16</v>
+      </c>
+      <c r="K35">
+        <v>0.908</v>
+      </c>
+      <c r="L35">
+        <v>5.252</v>
+      </c>
+      <c r="M35">
+        <v>28.1566692</v>
+      </c>
+      <c r="N35">
+        <v>-22.9046692</v>
+      </c>
+      <c r="O35">
+        <v>-7.100447452000003</v>
+      </c>
+      <c r="P35">
+        <v>-15.804221748</v>
+      </c>
+      <c r="Q35">
+        <v>-14.896221748</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1147587983396845</v>
+      </c>
+      <c r="T35">
+        <v>0.742138863123938</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.05782360081141984</v>
+      </c>
+      <c r="W35">
+        <v>0.224991724126233</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1865277445529672</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1531356638492455</v>
+      </c>
+      <c r="C36">
+        <v>74.84183934004939</v>
+      </c>
+      <c r="D36">
+        <v>164.8238393400494</v>
+      </c>
+      <c r="E36">
+        <v>-190.618</v>
+      </c>
+      <c r="F36">
+        <v>121.482</v>
+      </c>
+      <c r="G36">
+        <v>31.5</v>
+      </c>
+      <c r="H36">
+        <v>45.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.16</v>
+      </c>
+      <c r="K36">
+        <v>0.908</v>
+      </c>
+      <c r="L36">
+        <v>5.252</v>
+      </c>
+      <c r="M36">
+        <v>29.00990160000001</v>
+      </c>
+      <c r="N36">
+        <v>-23.75790160000001</v>
+      </c>
+      <c r="O36">
+        <v>-7.364949496000004</v>
+      </c>
+      <c r="P36">
+        <v>-16.392952104</v>
+      </c>
+      <c r="Q36">
+        <v>-15.484952104</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1159096892236191</v>
+      </c>
+      <c r="T36">
+        <v>0.7533833913530884</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.05612290666990749</v>
+      </c>
+      <c r="W36">
+        <v>0.2253978498872261</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1810416344190563</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1551356638492455</v>
+      </c>
+      <c r="C37">
+        <v>68.43524843788823</v>
+      </c>
+      <c r="D37">
+        <v>161.9902484378883</v>
+      </c>
+      <c r="E37">
+        <v>-187.045</v>
+      </c>
+      <c r="F37">
+        <v>125.055</v>
+      </c>
+      <c r="G37">
+        <v>31.5</v>
+      </c>
+      <c r="H37">
+        <v>45.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.16</v>
+      </c>
+      <c r="K37">
+        <v>0.908</v>
+      </c>
+      <c r="L37">
+        <v>5.252</v>
+      </c>
+      <c r="M37">
+        <v>29.86313400000001</v>
+      </c>
+      <c r="N37">
+        <v>-24.61113400000001</v>
+      </c>
+      <c r="O37">
+        <v>-7.629451540000003</v>
+      </c>
+      <c r="P37">
+        <v>-16.98168246</v>
+      </c>
+      <c r="Q37">
+        <v>-16.07368246</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1170959921347517</v>
+      </c>
+      <c r="T37">
+        <v>0.7649739050662128</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.05451939505076728</v>
+      </c>
+      <c r="W37">
+        <v>0.2257807684618768</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1758690162927976</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1571356638492455</v>
+      </c>
+      <c r="C38">
+        <v>62.12443900379819</v>
+      </c>
+      <c r="D38">
+        <v>159.2524390037982</v>
+      </c>
+      <c r="E38">
+        <v>-183.472</v>
+      </c>
+      <c r="F38">
+        <v>128.628</v>
+      </c>
+      <c r="G38">
+        <v>31.5</v>
+      </c>
+      <c r="H38">
+        <v>45.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.16</v>
+      </c>
+      <c r="K38">
+        <v>0.908</v>
+      </c>
+      <c r="L38">
+        <v>5.252</v>
+      </c>
+      <c r="M38">
+        <v>30.7163664</v>
+      </c>
+      <c r="N38">
+        <v>-25.4643664</v>
+      </c>
+      <c r="O38">
+        <v>-7.893953584000001</v>
+      </c>
+      <c r="P38">
+        <v>-17.570412816</v>
+      </c>
+      <c r="Q38">
+        <v>-16.662412816</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1183193670118572</v>
+      </c>
+      <c r="T38">
+        <v>0.7769266223328724</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.05300496741046819</v>
+      </c>
+      <c r="W38">
+        <v>0.2261424137823802</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1709837658402199</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1591356638492455</v>
+      </c>
+      <c r="C39">
+        <v>55.90463532299901</v>
+      </c>
+      <c r="D39">
+        <v>156.605635322999</v>
+      </c>
+      <c r="E39">
+        <v>-179.899</v>
+      </c>
+      <c r="F39">
+        <v>132.201</v>
+      </c>
+      <c r="G39">
+        <v>31.5</v>
+      </c>
+      <c r="H39">
+        <v>45.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.16</v>
+      </c>
+      <c r="K39">
+        <v>0.908</v>
+      </c>
+      <c r="L39">
+        <v>5.252</v>
+      </c>
+      <c r="M39">
+        <v>31.5695988</v>
+      </c>
+      <c r="N39">
+        <v>-26.3175988</v>
+      </c>
+      <c r="O39">
+        <v>-8.158455628000002</v>
+      </c>
+      <c r="P39">
+        <v>-18.159143172</v>
+      </c>
+      <c r="Q39">
+        <v>-17.251143172</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1195815791866486</v>
+      </c>
+      <c r="T39">
+        <v>0.7892587909413307</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.05157240072369878</v>
+      </c>
+      <c r="W39">
+        <v>0.2264845107071808</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1663625829796734</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1611356638492455</v>
+      </c>
+      <c r="C40">
+        <v>49.77137398308449</v>
+      </c>
+      <c r="D40">
+        <v>154.0453739830845</v>
+      </c>
+      <c r="E40">
+        <v>-176.326</v>
+      </c>
+      <c r="F40">
+        <v>135.774</v>
+      </c>
+      <c r="G40">
+        <v>31.5</v>
+      </c>
+      <c r="H40">
+        <v>45.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.16</v>
+      </c>
+      <c r="K40">
+        <v>0.908</v>
+      </c>
+      <c r="L40">
+        <v>5.252</v>
+      </c>
+      <c r="M40">
+        <v>32.4228312</v>
+      </c>
+      <c r="N40">
+        <v>-27.17083120000001</v>
+      </c>
+      <c r="O40">
+        <v>-8.422957672000003</v>
+      </c>
+      <c r="P40">
+        <v>-18.747873528</v>
+      </c>
+      <c r="Q40">
+        <v>-17.839873528</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1208845078832074</v>
+      </c>
+      <c r="T40">
+        <v>0.8019887714403844</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.05021523228360143</v>
+      </c>
+      <c r="W40">
+        <v>0.226808602530676</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.161984620269682</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1631356638492455</v>
+      </c>
+      <c r="C41">
+        <v>43.7204787563399</v>
+      </c>
+      <c r="D41">
+        <v>151.5674787563399</v>
+      </c>
+      <c r="E41">
+        <v>-172.753</v>
+      </c>
+      <c r="F41">
+        <v>139.347</v>
+      </c>
+      <c r="G41">
+        <v>31.5</v>
+      </c>
+      <c r="H41">
+        <v>45.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.16</v>
+      </c>
+      <c r="K41">
+        <v>0.908</v>
+      </c>
+      <c r="L41">
+        <v>5.252</v>
+      </c>
+      <c r="M41">
+        <v>33.2760636</v>
+      </c>
+      <c r="N41">
+        <v>-28.0240636</v>
+      </c>
+      <c r="O41">
+        <v>-8.687459716000003</v>
+      </c>
+      <c r="P41">
+        <v>-19.336603884</v>
+      </c>
+      <c r="Q41">
+        <v>-18.428603884</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1222301555534239</v>
+      </c>
+      <c r="T41">
+        <v>0.8151361283492432</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04892766222504756</v>
+      </c>
+      <c r="W41">
+        <v>0.2271160742606587</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1578311684678954</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1651356638492455</v>
+      </c>
+      <c r="C42">
+        <v>37.74803786786356</v>
+      </c>
+      <c r="D42">
+        <v>149.1680378678636</v>
+      </c>
+      <c r="E42">
+        <v>-169.18</v>
+      </c>
+      <c r="F42">
+        <v>142.92</v>
+      </c>
+      <c r="G42">
+        <v>31.5</v>
+      </c>
+      <c r="H42">
+        <v>45.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.16</v>
+      </c>
+      <c r="K42">
+        <v>0.908</v>
+      </c>
+      <c r="L42">
+        <v>5.252</v>
+      </c>
+      <c r="M42">
+        <v>34.129296</v>
+      </c>
+      <c r="N42">
+        <v>-28.877296</v>
+      </c>
+      <c r="O42">
+        <v>-8.951961760000003</v>
+      </c>
+      <c r="P42">
+        <v>-19.92533424</v>
+      </c>
+      <c r="Q42">
+        <v>-19.01733424</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.123620658145981</v>
+      </c>
+      <c r="T42">
+        <v>0.8287217304883973</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04770447066942137</v>
+      </c>
+      <c r="W42">
+        <v>0.2274081724041422</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1538853892561979</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1671356638492454</v>
+      </c>
+      <c r="C43">
+        <v>31.85038338922871</v>
+      </c>
+      <c r="D43">
+        <v>146.8433833892287</v>
+      </c>
+      <c r="E43">
+        <v>-165.607</v>
+      </c>
+      <c r="F43">
+        <v>146.493</v>
+      </c>
+      <c r="G43">
+        <v>31.5</v>
+      </c>
+      <c r="H43">
+        <v>45.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.16</v>
+      </c>
+      <c r="K43">
+        <v>0.908</v>
+      </c>
+      <c r="L43">
+        <v>5.252</v>
+      </c>
+      <c r="M43">
+        <v>34.98252840000001</v>
+      </c>
+      <c r="N43">
+        <v>-29.73052840000001</v>
+      </c>
+      <c r="O43">
+        <v>-9.216463804000004</v>
+      </c>
+      <c r="P43">
+        <v>-20.514064596</v>
+      </c>
+      <c r="Q43">
+        <v>-19.606064596</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1250582964196417</v>
+      </c>
+      <c r="T43">
+        <v>0.8427678615136243</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.04654094699455743</v>
+      </c>
+      <c r="W43">
+        <v>0.2276860218576997</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1501320870792174</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1691356638492455</v>
+      </c>
+      <c r="C44">
+        <v>26.02407252936956</v>
+      </c>
+      <c r="D44">
+        <v>144.5900725293696</v>
+      </c>
+      <c r="E44">
+        <v>-162.034</v>
+      </c>
+      <c r="F44">
+        <v>150.066</v>
+      </c>
+      <c r="G44">
+        <v>31.5</v>
+      </c>
+      <c r="H44">
+        <v>45.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.16</v>
+      </c>
+      <c r="K44">
+        <v>0.908</v>
+      </c>
+      <c r="L44">
+        <v>5.252</v>
+      </c>
+      <c r="M44">
+        <v>35.8357608</v>
+      </c>
+      <c r="N44">
+        <v>-30.5837608</v>
+      </c>
+      <c r="O44">
+        <v>-9.480965848000002</v>
+      </c>
+      <c r="P44">
+        <v>-21.102794952</v>
+      </c>
+      <c r="Q44">
+        <v>-20.194794952</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1265455084268769</v>
+      </c>
+      <c r="T44">
+        <v>0.8572983418845488</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.04543282920897274</v>
+      </c>
+      <c r="W44">
+        <v>0.2279506403848973</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1465575135773314</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1711356638492455</v>
+      </c>
+      <c r="C45">
+        <v>20.2658706219822</v>
+      </c>
+      <c r="D45">
+        <v>142.4048706219822</v>
+      </c>
+      <c r="E45">
+        <v>-158.461</v>
+      </c>
+      <c r="F45">
+        <v>153.639</v>
+      </c>
+      <c r="G45">
+        <v>31.5</v>
+      </c>
+      <c r="H45">
+        <v>45.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.16</v>
+      </c>
+      <c r="K45">
+        <v>0.908</v>
+      </c>
+      <c r="L45">
+        <v>5.252</v>
+      </c>
+      <c r="M45">
+        <v>36.68899320000001</v>
+      </c>
+      <c r="N45">
+        <v>-31.43699320000001</v>
+      </c>
+      <c r="O45">
+        <v>-9.745467892000004</v>
+      </c>
+      <c r="P45">
+        <v>-21.691525308</v>
+      </c>
+      <c r="Q45">
+        <v>-20.783525308</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1280849033115589</v>
+      </c>
+      <c r="T45">
+        <v>0.8723386636719971</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.04437625178550825</v>
+      </c>
+      <c r="W45">
+        <v>0.2282029510736207</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1431491993080911</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1731356638492455</v>
+      </c>
+      <c r="C46">
+        <v>14.57273563263502</v>
+      </c>
+      <c r="D46">
+        <v>140.284735632635</v>
+      </c>
+      <c r="E46">
+        <v>-154.888</v>
+      </c>
+      <c r="F46">
+        <v>157.212</v>
+      </c>
+      <c r="G46">
+        <v>31.5</v>
+      </c>
+      <c r="H46">
+        <v>45.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.16</v>
+      </c>
+      <c r="K46">
+        <v>0.908</v>
+      </c>
+      <c r="L46">
+        <v>5.252</v>
+      </c>
+      <c r="M46">
+        <v>37.54222560000001</v>
+      </c>
+      <c r="N46">
+        <v>-32.29022560000001</v>
+      </c>
+      <c r="O46">
+        <v>-10.009969936</v>
+      </c>
+      <c r="P46">
+        <v>-22.280255664</v>
+      </c>
+      <c r="Q46">
+        <v>-21.372255664</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1296792765849796</v>
+      </c>
+      <c r="T46">
+        <v>0.8879161398089971</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.04336770060856487</v>
+      </c>
+      <c r="W46">
+        <v>0.2284437930946747</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1398958084147255</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1751356638492454</v>
+      </c>
+      <c r="C47">
+        <v>8.94180402953296</v>
+      </c>
+      <c r="D47">
+        <v>138.226804029533</v>
+      </c>
+      <c r="E47">
+        <v>-151.315</v>
+      </c>
+      <c r="F47">
+        <v>160.785</v>
+      </c>
+      <c r="G47">
+        <v>31.5</v>
+      </c>
+      <c r="H47">
+        <v>45.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.16</v>
+      </c>
+      <c r="K47">
+        <v>0.908</v>
+      </c>
+      <c r="L47">
+        <v>5.252</v>
+      </c>
+      <c r="M47">
+        <v>38.395458</v>
+      </c>
+      <c r="N47">
+        <v>-33.143458</v>
+      </c>
+      <c r="O47">
+        <v>-10.27447198</v>
+      </c>
+      <c r="P47">
+        <v>-22.86898601999999</v>
+      </c>
+      <c r="Q47">
+        <v>-21.96098601999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1313316270683429</v>
+      </c>
+      <c r="T47">
+        <v>0.904060069623706</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.04240397392837456</v>
+      </c>
+      <c r="W47">
+        <v>0.2286739310259042</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1367870126721761</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1771356638492455</v>
+      </c>
+      <c r="C48">
+        <v>3.370377879929634</v>
+      </c>
+      <c r="D48">
+        <v>136.2283778799296</v>
+      </c>
+      <c r="E48">
+        <v>-147.742</v>
+      </c>
+      <c r="F48">
+        <v>164.358</v>
+      </c>
+      <c r="G48">
+        <v>31.5</v>
+      </c>
+      <c r="H48">
+        <v>45.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.16</v>
+      </c>
+      <c r="K48">
+        <v>0.908</v>
+      </c>
+      <c r="L48">
+        <v>5.252</v>
+      </c>
+      <c r="M48">
+        <v>39.2486904</v>
+      </c>
+      <c r="N48">
+        <v>-33.9966904</v>
+      </c>
+      <c r="O48">
+        <v>-10.538974024</v>
+      </c>
+      <c r="P48">
+        <v>-23.457716376</v>
+      </c>
+      <c r="Q48">
+        <v>-22.549716376</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1330451757177566</v>
+      </c>
+      <c r="T48">
+        <v>0.9208019227648858</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.0414821484081925</v>
+      </c>
+      <c r="W48">
+        <v>0.2288940629601236</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1338133819619113</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1791356638492455</v>
+      </c>
+      <c r="C49">
+        <v>-2.144086950083533</v>
+      </c>
+      <c r="D49">
+        <v>134.2869130499165</v>
+      </c>
+      <c r="E49">
+        <v>-144.169</v>
+      </c>
+      <c r="F49">
+        <v>167.931</v>
+      </c>
+      <c r="G49">
+        <v>31.5</v>
+      </c>
+      <c r="H49">
+        <v>45.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.16</v>
+      </c>
+      <c r="K49">
+        <v>0.908</v>
+      </c>
+      <c r="L49">
+        <v>5.252</v>
+      </c>
+      <c r="M49">
+        <v>40.1019228</v>
+      </c>
+      <c r="N49">
+        <v>-34.8499228</v>
+      </c>
+      <c r="O49">
+        <v>-10.803476068</v>
+      </c>
+      <c r="P49">
+        <v>-24.046446732</v>
+      </c>
+      <c r="Q49">
+        <v>-23.138446732</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1348233865803558</v>
+      </c>
+      <c r="T49">
+        <v>0.9381755439491289</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04059954950589053</v>
+      </c>
+      <c r="W49">
+        <v>0.2291048275779934</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1309662887286792</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1811356638492455</v>
+      </c>
+      <c r="C50">
+        <v>-7.603991600939651</v>
+      </c>
+      <c r="D50">
+        <v>132.4000083990603</v>
+      </c>
+      <c r="E50">
+        <v>-140.596</v>
+      </c>
+      <c r="F50">
+        <v>171.504</v>
+      </c>
+      <c r="G50">
+        <v>31.5</v>
+      </c>
+      <c r="H50">
+        <v>45.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.16</v>
+      </c>
+      <c r="K50">
+        <v>0.908</v>
+      </c>
+      <c r="L50">
+        <v>5.252</v>
+      </c>
+      <c r="M50">
+        <v>40.9551552</v>
+      </c>
+      <c r="N50">
+        <v>-35.7031552</v>
+      </c>
+      <c r="O50">
+        <v>-11.067978112</v>
+      </c>
+      <c r="P50">
+        <v>-24.635177088</v>
+      </c>
+      <c r="Q50">
+        <v>-23.727177088</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1366699901684396</v>
+      </c>
+      <c r="T50">
+        <v>0.956217381332766</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03975372555785114</v>
+      </c>
+      <c r="W50">
+        <v>0.2293068103367852</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1282378243801651</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1831356638492455</v>
+      </c>
+      <c r="C51">
+        <v>-13.01160412660545</v>
+      </c>
+      <c r="D51">
+        <v>130.5653958733946</v>
+      </c>
+      <c r="E51">
+        <v>-137.023</v>
+      </c>
+      <c r="F51">
+        <v>175.077</v>
+      </c>
+      <c r="G51">
+        <v>31.5</v>
+      </c>
+      <c r="H51">
+        <v>45.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.16</v>
+      </c>
+      <c r="K51">
+        <v>0.908</v>
+      </c>
+      <c r="L51">
+        <v>5.252</v>
+      </c>
+      <c r="M51">
+        <v>41.8083876</v>
+      </c>
+      <c r="N51">
+        <v>-36.5563876</v>
+      </c>
+      <c r="O51">
+        <v>-11.332480156</v>
+      </c>
+      <c r="P51">
+        <v>-25.223907444</v>
+      </c>
+      <c r="Q51">
+        <v>-24.315907444</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.138589009583507</v>
+      </c>
+      <c r="T51">
+        <v>0.9749667417510555</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03894242503626234</v>
+      </c>
+      <c r="W51">
+        <v>0.2295005489013406</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.125620725923427</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1851356638492455</v>
+      </c>
+      <c r="C52">
+        <v>-18.36906858918383</v>
+      </c>
+      <c r="D52">
+        <v>128.7809314108162</v>
+      </c>
+      <c r="E52">
+        <v>-133.45</v>
+      </c>
+      <c r="F52">
+        <v>178.65</v>
+      </c>
+      <c r="G52">
+        <v>31.5</v>
+      </c>
+      <c r="H52">
+        <v>45.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.16</v>
+      </c>
+      <c r="K52">
+        <v>0.908</v>
+      </c>
+      <c r="L52">
+        <v>5.252</v>
+      </c>
+      <c r="M52">
+        <v>42.66162000000001</v>
+      </c>
+      <c r="N52">
+        <v>-37.40962</v>
+      </c>
+      <c r="O52">
+        <v>-11.5969822</v>
+      </c>
+      <c r="P52">
+        <v>-25.8126378</v>
+      </c>
+      <c r="Q52">
+        <v>-24.9046378</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1405847897751772</v>
+      </c>
+      <c r="T52">
+        <v>0.9944660765860767</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03816357653553709</v>
+      </c>
+      <c r="W52">
+        <v>0.2296865379233138</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1231083114049584</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1871356638492455</v>
+      </c>
+      <c r="C53">
+        <v>-23.67841341778416</v>
+      </c>
+      <c r="D53">
+        <v>127.0445865822159</v>
+      </c>
+      <c r="E53">
+        <v>-129.877</v>
+      </c>
+      <c r="F53">
+        <v>182.223</v>
+      </c>
+      <c r="G53">
+        <v>31.5</v>
+      </c>
+      <c r="H53">
+        <v>45.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.16</v>
+      </c>
+      <c r="K53">
+        <v>0.908</v>
+      </c>
+      <c r="L53">
+        <v>5.252</v>
+      </c>
+      <c r="M53">
+        <v>43.5148524</v>
+      </c>
+      <c r="N53">
+        <v>-38.2628524</v>
+      </c>
+      <c r="O53">
+        <v>-11.861484244</v>
+      </c>
+      <c r="P53">
+        <v>-26.401368156</v>
+      </c>
+      <c r="Q53">
+        <v>-25.493368156</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1426620303828339</v>
+      </c>
+      <c r="T53">
+        <v>1.014761302638854</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03741527111327166</v>
+      </c>
+      <c r="W53">
+        <v>0.2298652332581507</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1206944229460377</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1891356638492455</v>
+      </c>
+      <c r="C54">
+        <v>-28.94155910017685</v>
+      </c>
+      <c r="D54">
+        <v>125.3544408998232</v>
+      </c>
+      <c r="E54">
+        <v>-126.304</v>
+      </c>
+      <c r="F54">
+        <v>185.796</v>
+      </c>
+      <c r="G54">
+        <v>31.5</v>
+      </c>
+      <c r="H54">
+        <v>45.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.16</v>
+      </c>
+      <c r="K54">
+        <v>0.908</v>
+      </c>
+      <c r="L54">
+        <v>5.252</v>
+      </c>
+      <c r="M54">
+        <v>44.36808480000001</v>
+      </c>
+      <c r="N54">
+        <v>-39.1160848</v>
+      </c>
+      <c r="O54">
+        <v>-12.125986288</v>
+      </c>
+      <c r="P54">
+        <v>-26.990098512</v>
+      </c>
+      <c r="Q54">
+        <v>-26.082098512</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1448258226824763</v>
+      </c>
+      <c r="T54">
+        <v>1.035902163110497</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03669574666878567</v>
+      </c>
+      <c r="W54">
+        <v>0.230037055695494</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1183733763509216</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1911356638492455</v>
+      </c>
+      <c r="C55">
+        <v>-34.16032526854926</v>
+      </c>
+      <c r="D55">
+        <v>123.7086747314508</v>
+      </c>
+      <c r="E55">
+        <v>-122.731</v>
+      </c>
+      <c r="F55">
+        <v>189.369</v>
+      </c>
+      <c r="G55">
+        <v>31.5</v>
+      </c>
+      <c r="H55">
+        <v>45.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.16</v>
+      </c>
+      <c r="K55">
+        <v>0.908</v>
+      </c>
+      <c r="L55">
+        <v>5.252</v>
+      </c>
+      <c r="M55">
+        <v>45.22131720000001</v>
+      </c>
+      <c r="N55">
+        <v>-39.96931720000001</v>
+      </c>
+      <c r="O55">
+        <v>-12.390488332</v>
+      </c>
+      <c r="P55">
+        <v>-27.578828868</v>
+      </c>
+      <c r="Q55">
+        <v>-26.670828868</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1470816912501885</v>
+      </c>
+      <c r="T55">
+        <v>1.057942634666039</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03600337409012933</v>
+      </c>
+      <c r="W55">
+        <v>0.2302023942672771</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1161399164197721</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1931356638492455</v>
+      </c>
+      <c r="C56">
+        <v>-39.3364372343265</v>
+      </c>
+      <c r="D56">
+        <v>122.1055627656735</v>
+      </c>
+      <c r="E56">
+        <v>-119.158</v>
+      </c>
+      <c r="F56">
+        <v>192.942</v>
+      </c>
+      <c r="G56">
+        <v>31.5</v>
+      </c>
+      <c r="H56">
+        <v>45.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.16</v>
+      </c>
+      <c r="K56">
+        <v>0.908</v>
+      </c>
+      <c r="L56">
+        <v>5.252</v>
+      </c>
+      <c r="M56">
+        <v>46.0745496</v>
+      </c>
+      <c r="N56">
+        <v>-40.8225496</v>
+      </c>
+      <c r="O56">
+        <v>-12.654990376</v>
+      </c>
+      <c r="P56">
+        <v>-28.167559224</v>
+      </c>
+      <c r="Q56">
+        <v>-27.259559224</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1494356410599752</v>
+      </c>
+      <c r="T56">
+        <v>1.080941387593562</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03533664494031213</v>
+      </c>
+      <c r="W56">
+        <v>0.2303616091882535</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1139891772268133</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1951356638492455</v>
+      </c>
+      <c r="C57">
+        <v>-44.47153202139211</v>
+      </c>
+      <c r="D57">
+        <v>120.5434679786079</v>
+      </c>
+      <c r="E57">
+        <v>-115.585</v>
+      </c>
+      <c r="F57">
+        <v>196.515</v>
+      </c>
+      <c r="G57">
+        <v>31.5</v>
+      </c>
+      <c r="H57">
+        <v>45.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.16</v>
+      </c>
+      <c r="K57">
+        <v>0.908</v>
+      </c>
+      <c r="L57">
+        <v>5.252</v>
+      </c>
+      <c r="M57">
+        <v>46.92778200000001</v>
+      </c>
+      <c r="N57">
+        <v>-41.67578200000001</v>
+      </c>
+      <c r="O57">
+        <v>-12.91949242</v>
+      </c>
+      <c r="P57">
+        <v>-28.75628958</v>
+      </c>
+      <c r="Q57">
+        <v>-27.84828958</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.151894210861308</v>
+      </c>
+      <c r="T57">
+        <v>1.104962307317863</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.0346941604868519</v>
+      </c>
+      <c r="W57">
+        <v>0.2305150344757398</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1119166467317804</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1971356638492455</v>
+      </c>
+      <c r="C58">
+        <v>-49.56716394206137</v>
+      </c>
+      <c r="D58">
+        <v>119.0208360579387</v>
+      </c>
+      <c r="E58">
+        <v>-112.012</v>
+      </c>
+      <c r="F58">
+        <v>200.088</v>
+      </c>
+      <c r="G58">
+        <v>31.5</v>
+      </c>
+      <c r="H58">
+        <v>45.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.16</v>
+      </c>
+      <c r="K58">
+        <v>0.908</v>
+      </c>
+      <c r="L58">
+        <v>5.252</v>
+      </c>
+      <c r="M58">
+        <v>47.78101440000001</v>
+      </c>
+      <c r="N58">
+        <v>-42.52901440000001</v>
+      </c>
+      <c r="O58">
+        <v>-13.183994464</v>
+      </c>
+      <c r="P58">
+        <v>-29.345019936</v>
+      </c>
+      <c r="Q58">
+        <v>-28.437019936</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1544645338354286</v>
+      </c>
+      <c r="T58">
+        <v>1.130075087029633</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.03407462190672954</v>
+      </c>
+      <c r="W58">
+        <v>0.230662980288673</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1099181351829985</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1991356638492455</v>
+      </c>
+      <c r="C59">
+        <v>-54.62480975573195</v>
+      </c>
+      <c r="D59">
+        <v>117.5361902442681</v>
+      </c>
+      <c r="E59">
+        <v>-108.439</v>
+      </c>
+      <c r="F59">
+        <v>203.661</v>
+      </c>
+      <c r="G59">
+        <v>31.5</v>
+      </c>
+      <c r="H59">
+        <v>45.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.16</v>
+      </c>
+      <c r="K59">
+        <v>0.908</v>
+      </c>
+      <c r="L59">
+        <v>5.252</v>
+      </c>
+      <c r="M59">
+        <v>48.63424680000001</v>
+      </c>
+      <c r="N59">
+        <v>-43.3822468</v>
+      </c>
+      <c r="O59">
+        <v>-13.448496508</v>
+      </c>
+      <c r="P59">
+        <v>-29.933750292</v>
+      </c>
+      <c r="Q59">
+        <v>-29.025750292</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1571544067153223</v>
+      </c>
+      <c r="T59">
+        <v>1.156355903007066</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.03347682152240096</v>
+      </c>
+      <c r="W59">
+        <v>0.2308057350204507</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1079897468464548</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2011356638492455</v>
+      </c>
+      <c r="C60">
+        <v>-59.64587344620253</v>
+      </c>
+      <c r="D60">
+        <v>116.0881265537975</v>
+      </c>
+      <c r="E60">
+        <v>-104.866</v>
+      </c>
+      <c r="F60">
+        <v>207.234</v>
+      </c>
+      <c r="G60">
+        <v>31.5</v>
+      </c>
+      <c r="H60">
+        <v>45.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.16</v>
+      </c>
+      <c r="K60">
+        <v>0.908</v>
+      </c>
+      <c r="L60">
+        <v>5.252</v>
+      </c>
+      <c r="M60">
+        <v>49.4874792</v>
+      </c>
+      <c r="N60">
+        <v>-44.23547919999999</v>
+      </c>
+      <c r="O60">
+        <v>-13.712998552</v>
+      </c>
+      <c r="P60">
+        <v>-30.52248064799999</v>
+      </c>
+      <c r="Q60">
+        <v>-29.61448064799999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1599723687799728</v>
+      </c>
+      <c r="T60">
+        <v>1.183888186411996</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03289963494442854</v>
+      </c>
+      <c r="W60">
+        <v>0.2309435671752705</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.106127854659447</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2031356638492455</v>
+      </c>
+      <c r="C61">
+        <v>-64.63169065014546</v>
+      </c>
+      <c r="D61">
+        <v>114.6753093498545</v>
+      </c>
+      <c r="E61">
+        <v>-101.293</v>
+      </c>
+      <c r="F61">
+        <v>210.807</v>
+      </c>
+      <c r="G61">
+        <v>31.5</v>
+      </c>
+      <c r="H61">
+        <v>45.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.16</v>
+      </c>
+      <c r="K61">
+        <v>0.908</v>
+      </c>
+      <c r="L61">
+        <v>5.252</v>
+      </c>
+      <c r="M61">
+        <v>50.3407116</v>
+      </c>
+      <c r="N61">
+        <v>-45.0887116</v>
+      </c>
+      <c r="O61">
+        <v>-13.977500596</v>
+      </c>
+      <c r="P61">
+        <v>-31.111211004</v>
+      </c>
+      <c r="Q61">
+        <v>-30.203211004</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1629277924087527</v>
+      </c>
+      <c r="T61">
+        <v>1.212763508031801</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03234201401316703</v>
+      </c>
+      <c r="W61">
+        <v>0.2310767270536557</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1043290774618292</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2051356638492455</v>
+      </c>
+      <c r="C62">
+        <v>-69.58353276609466</v>
+      </c>
+      <c r="D62">
+        <v>113.2964672339053</v>
+      </c>
+      <c r="E62">
+        <v>-97.72000000000003</v>
+      </c>
+      <c r="F62">
+        <v>214.38</v>
+      </c>
+      <c r="G62">
+        <v>31.5</v>
+      </c>
+      <c r="H62">
+        <v>45.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.16</v>
+      </c>
+      <c r="K62">
+        <v>0.908</v>
+      </c>
+      <c r="L62">
+        <v>5.252</v>
+      </c>
+      <c r="M62">
+        <v>51.193944</v>
+      </c>
+      <c r="N62">
+        <v>-45.941944</v>
+      </c>
+      <c r="O62">
+        <v>-14.24200264</v>
+      </c>
+      <c r="P62">
+        <v>-31.69994136</v>
+      </c>
+      <c r="Q62">
+        <v>-30.79194136</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1660309872189715</v>
+      </c>
+      <c r="T62">
+        <v>1.243082595732596</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03180298044628092</v>
+      </c>
+      <c r="W62">
+        <v>0.2312054482694281</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.102590259504132</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2071356638492455</v>
+      </c>
+      <c r="C63">
+        <v>-74.50261077052002</v>
+      </c>
+      <c r="D63">
+        <v>111.95038922948</v>
+      </c>
+      <c r="E63">
+        <v>-94.14700000000002</v>
+      </c>
+      <c r="F63">
+        <v>217.953</v>
+      </c>
+      <c r="G63">
+        <v>31.5</v>
+      </c>
+      <c r="H63">
+        <v>45.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.16</v>
+      </c>
+      <c r="K63">
+        <v>0.908</v>
+      </c>
+      <c r="L63">
+        <v>5.252</v>
+      </c>
+      <c r="M63">
+        <v>52.04717640000001</v>
+      </c>
+      <c r="N63">
+        <v>-46.7951764</v>
+      </c>
+      <c r="O63">
+        <v>-14.506504684</v>
+      </c>
+      <c r="P63">
+        <v>-32.288671716</v>
+      </c>
+      <c r="Q63">
+        <v>-31.38067171599999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1692933202245861</v>
+      </c>
+      <c r="T63">
+        <v>1.274956508443688</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03128162011109598</v>
+      </c>
+      <c r="W63">
+        <v>0.2313299491174703</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1009084519712774</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2091356638492455</v>
+      </c>
+      <c r="C64">
+        <v>-79.39007876506238</v>
+      </c>
+      <c r="D64">
+        <v>110.6359212349376</v>
+      </c>
+      <c r="E64">
+        <v>-90.57400000000001</v>
+      </c>
+      <c r="F64">
+        <v>221.526</v>
+      </c>
+      <c r="G64">
+        <v>31.5</v>
+      </c>
+      <c r="H64">
+        <v>45.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.16</v>
+      </c>
+      <c r="K64">
+        <v>0.908</v>
+      </c>
+      <c r="L64">
+        <v>5.252</v>
+      </c>
+      <c r="M64">
+        <v>52.90040880000001</v>
+      </c>
+      <c r="N64">
+        <v>-47.64840880000001</v>
+      </c>
+      <c r="O64">
+        <v>-14.77100672800001</v>
+      </c>
+      <c r="P64">
+        <v>-32.877402072</v>
+      </c>
+      <c r="Q64">
+        <v>-31.969402072</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1727273549673384</v>
+      </c>
+      <c r="T64">
+        <v>1.308507995507995</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03077707785123959</v>
+      </c>
+      <c r="W64">
+        <v>0.231450433809124</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.09928089629432124</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2111356638492455</v>
+      </c>
+      <c r="C65">
+        <v>-84.24703727676919</v>
+      </c>
+      <c r="D65">
+        <v>109.3519627232308</v>
+      </c>
+      <c r="E65">
+        <v>-87.001</v>
+      </c>
+      <c r="F65">
+        <v>225.099</v>
+      </c>
+      <c r="G65">
+        <v>31.5</v>
+      </c>
+      <c r="H65">
+        <v>45.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.16</v>
+      </c>
+      <c r="K65">
+        <v>0.908</v>
+      </c>
+      <c r="L65">
+        <v>5.252</v>
+      </c>
+      <c r="M65">
+        <v>53.7536412</v>
+      </c>
+      <c r="N65">
+        <v>-48.5016412</v>
+      </c>
+      <c r="O65">
+        <v>-15.035508772</v>
+      </c>
+      <c r="P65">
+        <v>-33.46613242799999</v>
+      </c>
+      <c r="Q65">
+        <v>-32.55813242799999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1763470132096989</v>
+      </c>
+      <c r="T65">
+        <v>1.343873076467671</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03028855280598182</v>
+      </c>
+      <c r="W65">
+        <v>0.2315670935899315</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.09770500905155433</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2131356638492455</v>
+      </c>
+      <c r="C66">
+        <v>-89.07453633116569</v>
+      </c>
+      <c r="D66">
+        <v>108.0974636688343</v>
+      </c>
+      <c r="E66">
+        <v>-83.428</v>
+      </c>
+      <c r="F66">
+        <v>228.672</v>
+      </c>
+      <c r="G66">
+        <v>31.5</v>
+      </c>
+      <c r="H66">
+        <v>45.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.16</v>
+      </c>
+      <c r="K66">
+        <v>0.908</v>
+      </c>
+      <c r="L66">
+        <v>5.252</v>
+      </c>
+      <c r="M66">
+        <v>54.60687360000001</v>
+      </c>
+      <c r="N66">
+        <v>-49.3548736</v>
+      </c>
+      <c r="O66">
+        <v>-15.300010816</v>
+      </c>
+      <c r="P66">
+        <v>-34.054862784</v>
+      </c>
+      <c r="Q66">
+        <v>-33.146862784</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.180167763576635</v>
+      </c>
+      <c r="T66">
+        <v>1.381202884147329</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02981529416838835</v>
+      </c>
+      <c r="W66">
+        <v>0.2316801077525889</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.09617836828512372</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2151356638492455</v>
+      </c>
+      <c r="C67">
+        <v>-93.87357831619767</v>
+      </c>
+      <c r="D67">
+        <v>106.8714216838023</v>
+      </c>
+      <c r="E67">
+        <v>-79.85500000000002</v>
+      </c>
+      <c r="F67">
+        <v>232.245</v>
+      </c>
+      <c r="G67">
+        <v>31.5</v>
+      </c>
+      <c r="H67">
+        <v>45.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.16</v>
+      </c>
+      <c r="K67">
+        <v>0.908</v>
+      </c>
+      <c r="L67">
+        <v>5.252</v>
+      </c>
+      <c r="M67">
+        <v>55.460106</v>
+      </c>
+      <c r="N67">
+        <v>-50.208106</v>
+      </c>
+      <c r="O67">
+        <v>-15.56451286</v>
+      </c>
+      <c r="P67">
+        <v>-34.64359314</v>
+      </c>
+      <c r="Q67">
+        <v>-33.73559314</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1842068425359674</v>
+      </c>
+      <c r="T67">
+        <v>1.420665823694396</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02935659733502853</v>
+      </c>
+      <c r="W67">
+        <v>0.2317896445563952</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.09469870108073719</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2171356638492455</v>
+      </c>
+      <c r="C68">
+        <v>-98.64512065346281</v>
+      </c>
+      <c r="D68">
+        <v>105.6728793465372</v>
+      </c>
+      <c r="E68">
+        <v>-76.28200000000001</v>
+      </c>
+      <c r="F68">
+        <v>235.818</v>
+      </c>
+      <c r="G68">
+        <v>31.5</v>
+      </c>
+      <c r="H68">
+        <v>45.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.16</v>
+      </c>
+      <c r="K68">
+        <v>0.908</v>
+      </c>
+      <c r="L68">
+        <v>5.252</v>
+      </c>
+      <c r="M68">
+        <v>56.31333840000001</v>
+      </c>
+      <c r="N68">
+        <v>-51.0613384</v>
+      </c>
+      <c r="O68">
+        <v>-15.829014904</v>
+      </c>
+      <c r="P68">
+        <v>-35.232323496</v>
+      </c>
+      <c r="Q68">
+        <v>-34.324323496</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1884835143752606</v>
+      </c>
+      <c r="T68">
+        <v>1.462450112626583</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02891180040570992</v>
+      </c>
+      <c r="W68">
+        <v>0.2318958620631165</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.09326387227648369</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2191356638492455</v>
+      </c>
+      <c r="C69">
+        <v>-103.390078291691</v>
+      </c>
+      <c r="D69">
+        <v>104.500921708309</v>
+      </c>
+      <c r="E69">
+        <v>-72.709</v>
+      </c>
+      <c r="F69">
+        <v>239.391</v>
+      </c>
+      <c r="G69">
+        <v>31.5</v>
+      </c>
+      <c r="H69">
+        <v>45.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.16</v>
+      </c>
+      <c r="K69">
+        <v>0.908</v>
+      </c>
+      <c r="L69">
+        <v>5.252</v>
+      </c>
+      <c r="M69">
+        <v>57.16657080000001</v>
+      </c>
+      <c r="N69">
+        <v>-51.91457080000001</v>
+      </c>
+      <c r="O69">
+        <v>-16.093516948</v>
+      </c>
+      <c r="P69">
+        <v>-35.82105385200001</v>
+      </c>
+      <c r="Q69">
+        <v>-34.913053852</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1930193784472382</v>
+      </c>
+      <c r="T69">
+        <v>1.506766782706177</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02848028099666947</v>
+      </c>
+      <c r="W69">
+        <v>0.2319989088979953</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.09187187418280474</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2211356638492455</v>
+      </c>
+      <c r="C70">
+        <v>-108.1093260361225</v>
+      </c>
+      <c r="D70">
+        <v>103.3546739638775</v>
+      </c>
+      <c r="E70">
+        <v>-69.136</v>
+      </c>
+      <c r="F70">
+        <v>242.964</v>
+      </c>
+      <c r="G70">
+        <v>31.5</v>
+      </c>
+      <c r="H70">
+        <v>45.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.16</v>
+      </c>
+      <c r="K70">
+        <v>0.908</v>
+      </c>
+      <c r="L70">
+        <v>5.252</v>
+      </c>
+      <c r="M70">
+        <v>58.01980320000001</v>
+      </c>
+      <c r="N70">
+        <v>-52.76780320000001</v>
+      </c>
+      <c r="O70">
+        <v>-16.35801899200001</v>
+      </c>
+      <c r="P70">
+        <v>-36.409784208</v>
+      </c>
+      <c r="Q70">
+        <v>-35.501784208</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1978387340237144</v>
+      </c>
+      <c r="T70">
+        <v>1.553853244665745</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02806145333495375</v>
+      </c>
+      <c r="W70">
+        <v>0.2320989249436131</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.0905208172095282</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2231356638492455</v>
+      </c>
+      <c r="C71">
+        <v>-112.8037007262466</v>
+      </c>
+      <c r="D71">
+        <v>102.2332992737535</v>
+      </c>
+      <c r="E71">
+        <v>-65.56299999999999</v>
+      </c>
+      <c r="F71">
+        <v>246.537</v>
+      </c>
+      <c r="G71">
+        <v>31.5</v>
+      </c>
+      <c r="H71">
+        <v>45.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.16</v>
+      </c>
+      <c r="K71">
+        <v>0.908</v>
+      </c>
+      <c r="L71">
+        <v>5.252</v>
+      </c>
+      <c r="M71">
+        <v>58.87303560000001</v>
+      </c>
+      <c r="N71">
+        <v>-53.62103560000001</v>
+      </c>
+      <c r="O71">
+        <v>-16.62252103600001</v>
+      </c>
+      <c r="P71">
+        <v>-36.998514564</v>
+      </c>
+      <c r="Q71">
+        <v>-36.090514564</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2029690157664149</v>
+      </c>
+      <c r="T71">
+        <v>1.603977542880769</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02765476560546166</v>
+      </c>
+      <c r="W71">
+        <v>0.2321960419734158</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.08920892130794089</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2251356638492455</v>
+      </c>
+      <c r="C72">
+        <v>-117.4740032732938</v>
+      </c>
+      <c r="D72">
+        <v>101.1359967267063</v>
+      </c>
+      <c r="E72">
+        <v>-61.98999999999998</v>
+      </c>
+      <c r="F72">
+        <v>250.11</v>
+      </c>
+      <c r="G72">
+        <v>31.5</v>
+      </c>
+      <c r="H72">
+        <v>45.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.16</v>
+      </c>
+      <c r="K72">
+        <v>0.908</v>
+      </c>
+      <c r="L72">
+        <v>5.252</v>
+      </c>
+      <c r="M72">
+        <v>59.72626800000001</v>
+      </c>
+      <c r="N72">
+        <v>-54.47426800000001</v>
+      </c>
+      <c r="O72">
+        <v>-16.88702308000001</v>
+      </c>
+      <c r="P72">
+        <v>-37.58724492</v>
+      </c>
+      <c r="Q72">
+        <v>-36.67924492</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.208441316291962</v>
+      </c>
+      <c r="T72">
+        <v>1.657443460976795</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02725969752538364</v>
+      </c>
+      <c r="W72">
+        <v>0.2322903842309384</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.0879345081463988</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2271356638492455</v>
+      </c>
+      <c r="C73">
+        <v>-122.1210005679077</v>
+      </c>
+      <c r="D73">
+        <v>100.0619994320923</v>
+      </c>
+      <c r="E73">
+        <v>-58.41700000000003</v>
+      </c>
+      <c r="F73">
+        <v>253.683</v>
+      </c>
+      <c r="G73">
+        <v>31.5</v>
+      </c>
+      <c r="H73">
+        <v>45.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.16</v>
+      </c>
+      <c r="K73">
+        <v>0.908</v>
+      </c>
+      <c r="L73">
+        <v>5.252</v>
+      </c>
+      <c r="M73">
+        <v>60.5795004</v>
+      </c>
+      <c r="N73">
+        <v>-55.3275004</v>
+      </c>
+      <c r="O73">
+        <v>-17.151525124</v>
+      </c>
+      <c r="P73">
+        <v>-38.175975276</v>
+      </c>
+      <c r="Q73">
+        <v>-37.26797527599999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2142910168537538</v>
+      </c>
+      <c r="T73">
+        <v>1.714596683769098</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02687575812361767</v>
+      </c>
+      <c r="W73">
+        <v>0.2323820689600801</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.08669599394715377</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2291356638492455</v>
+      </c>
+      <c r="C74">
+        <v>-126.7454272675444</v>
+      </c>
+      <c r="D74">
+        <v>99.01057273245556</v>
+      </c>
+      <c r="E74">
+        <v>-54.84400000000005</v>
+      </c>
+      <c r="F74">
+        <v>257.256</v>
+      </c>
+      <c r="G74">
+        <v>31.5</v>
+      </c>
+      <c r="H74">
+        <v>45.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.16</v>
+      </c>
+      <c r="K74">
+        <v>0.908</v>
+      </c>
+      <c r="L74">
+        <v>5.252</v>
+      </c>
+      <c r="M74">
+        <v>61.4327328</v>
+      </c>
+      <c r="N74">
+        <v>-56.18073279999999</v>
+      </c>
+      <c r="O74">
+        <v>-17.416027168</v>
+      </c>
+      <c r="P74">
+        <v>-38.76470563199999</v>
+      </c>
+      <c r="Q74">
+        <v>-37.85670563199999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2205585531699593</v>
+      </c>
+      <c r="T74">
+        <v>1.775832279617994</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0265024837052341</v>
+      </c>
+      <c r="W74">
+        <v>0.2324712068911901</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.08549188292011001</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2311356638492455</v>
+      </c>
+      <c r="C75">
+        <v>-131.3479874723545</v>
+      </c>
+      <c r="D75">
+        <v>97.98101252764548</v>
+      </c>
+      <c r="E75">
+        <v>-51.27100000000002</v>
+      </c>
+      <c r="F75">
+        <v>260.829</v>
+      </c>
+      <c r="G75">
+        <v>31.5</v>
+      </c>
+      <c r="H75">
+        <v>45.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.16</v>
+      </c>
+      <c r="K75">
+        <v>0.908</v>
+      </c>
+      <c r="L75">
+        <v>5.252</v>
+      </c>
+      <c r="M75">
+        <v>62.28596520000001</v>
+      </c>
+      <c r="N75">
+        <v>-57.0339652</v>
+      </c>
+      <c r="O75">
+        <v>-17.680529212</v>
+      </c>
+      <c r="P75">
+        <v>-39.353435988</v>
+      </c>
+      <c r="Q75">
+        <v>-38.445435988</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2272903514355133</v>
+      </c>
+      <c r="T75">
+        <v>1.841603845529771</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02613943598324459</v>
+      </c>
+      <c r="W75">
+        <v>0.2325579026872012</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.08432076123627286</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2331356638492454</v>
+      </c>
+      <c r="C76">
+        <v>-135.9293562975811</v>
+      </c>
+      <c r="D76">
+        <v>96.97264370241891</v>
+      </c>
+      <c r="E76">
+        <v>-47.69800000000004</v>
+      </c>
+      <c r="F76">
+        <v>264.402</v>
+      </c>
+      <c r="G76">
+        <v>31.5</v>
+      </c>
+      <c r="H76">
+        <v>45.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.16</v>
+      </c>
+      <c r="K76">
+        <v>0.908</v>
+      </c>
+      <c r="L76">
+        <v>5.252</v>
+      </c>
+      <c r="M76">
+        <v>63.1391976</v>
+      </c>
+      <c r="N76">
+        <v>-57.8871976</v>
+      </c>
+      <c r="O76">
+        <v>-17.945031256</v>
+      </c>
+      <c r="P76">
+        <v>-39.942166344</v>
+      </c>
+      <c r="Q76">
+        <v>-39.034166344</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2345399803368792</v>
+      </c>
+      <c r="T76">
+        <v>1.912434762665532</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02578620036184939</v>
+      </c>
+      <c r="W76">
+        <v>0.2326422553535904</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.08318129148983677</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2351356638492454</v>
+      </c>
+      <c r="C77">
+        <v>-140.4901813498536</v>
+      </c>
+      <c r="D77">
+        <v>95.98481865014642</v>
+      </c>
+      <c r="E77">
+        <v>-44.125</v>
+      </c>
+      <c r="F77">
+        <v>267.975</v>
+      </c>
+      <c r="G77">
+        <v>31.5</v>
+      </c>
+      <c r="H77">
+        <v>45.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.16</v>
+      </c>
+      <c r="K77">
+        <v>0.908</v>
+      </c>
+      <c r="L77">
+        <v>5.252</v>
+      </c>
+      <c r="M77">
+        <v>63.99243000000001</v>
+      </c>
+      <c r="N77">
+        <v>-58.74043</v>
+      </c>
+      <c r="O77">
+        <v>-18.2095333</v>
+      </c>
+      <c r="P77">
+        <v>-40.5308967</v>
+      </c>
+      <c r="Q77">
+        <v>-39.6228967</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2423695795503544</v>
+      </c>
+      <c r="T77">
+        <v>1.988932153172153</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02544238435702473</v>
+      </c>
+      <c r="W77">
+        <v>0.2327243586155425</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.08207220760330558</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2371356638492455</v>
+      </c>
+      <c r="C78">
+        <v>-145.0310841141603</v>
+      </c>
+      <c r="D78">
+        <v>95.01691588583969</v>
+      </c>
+      <c r="E78">
+        <v>-40.55200000000002</v>
+      </c>
+      <c r="F78">
+        <v>271.548</v>
+      </c>
+      <c r="G78">
+        <v>31.5</v>
+      </c>
+      <c r="H78">
+        <v>45.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.16</v>
+      </c>
+      <c r="K78">
+        <v>0.908</v>
+      </c>
+      <c r="L78">
+        <v>5.252</v>
+      </c>
+      <c r="M78">
+        <v>64.84566240000001</v>
+      </c>
+      <c r="N78">
+        <v>-59.59366240000001</v>
+      </c>
+      <c r="O78">
+        <v>-18.474035344</v>
+      </c>
+      <c r="P78">
+        <v>-41.119627056</v>
+      </c>
+      <c r="Q78">
+        <v>-40.211627056</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2508516453649525</v>
+      </c>
+      <c r="T78">
+        <v>2.071804326220994</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02510761614180072</v>
+      </c>
+      <c r="W78">
+        <v>0.232804301265338</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.08099231013484109</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2391356638492455</v>
+      </c>
+      <c r="C79">
+        <v>-149.5526612577422</v>
+      </c>
+      <c r="D79">
+        <v>94.06833874225788</v>
+      </c>
+      <c r="E79">
+        <v>-36.97899999999998</v>
+      </c>
+      <c r="F79">
+        <v>275.121</v>
+      </c>
+      <c r="G79">
+        <v>31.5</v>
+      </c>
+      <c r="H79">
+        <v>45.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.16</v>
+      </c>
+      <c r="K79">
+        <v>0.908</v>
+      </c>
+      <c r="L79">
+        <v>5.252</v>
+      </c>
+      <c r="M79">
+        <v>65.69889480000002</v>
+      </c>
+      <c r="N79">
+        <v>-60.44689480000002</v>
+      </c>
+      <c r="O79">
+        <v>-18.73853738800001</v>
+      </c>
+      <c r="P79">
+        <v>-41.70835741200001</v>
+      </c>
+      <c r="Q79">
+        <v>-40.80035741200001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2600712821199505</v>
+      </c>
+      <c r="T79">
+        <v>2.161882775187123</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02478154320489421</v>
+      </c>
+      <c r="W79">
+        <v>0.2328821674826713</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.07994046195127169</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2411356638492455</v>
+      </c>
+      <c r="C80">
+        <v>-154.0554858566556</v>
+      </c>
+      <c r="D80">
+        <v>93.13851414334439</v>
+      </c>
+      <c r="E80">
+        <v>-33.40600000000001</v>
+      </c>
+      <c r="F80">
+        <v>278.694</v>
+      </c>
+      <c r="G80">
+        <v>31.5</v>
+      </c>
+      <c r="H80">
+        <v>45.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.16</v>
+      </c>
+      <c r="K80">
+        <v>0.908</v>
+      </c>
+      <c r="L80">
+        <v>5.252</v>
+      </c>
+      <c r="M80">
+        <v>66.5521272</v>
+      </c>
+      <c r="N80">
+        <v>-61.3001272</v>
+      </c>
+      <c r="O80">
+        <v>-19.003039432</v>
+      </c>
+      <c r="P80">
+        <v>-42.297087768</v>
+      </c>
+      <c r="Q80">
+        <v>-41.389087768</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2701290676708573</v>
+      </c>
+      <c r="T80">
+        <v>2.260150174059266</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02446383111252378</v>
+      </c>
+      <c r="W80">
+        <v>0.2329580371303293</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.07891558423394773</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2431356638492455</v>
+      </c>
+      <c r="C81">
+        <v>-158.540108550304</v>
+      </c>
+      <c r="D81">
+        <v>92.226891449696</v>
+      </c>
+      <c r="E81">
+        <v>-29.83300000000003</v>
+      </c>
+      <c r="F81">
+        <v>282.267</v>
+      </c>
+      <c r="G81">
+        <v>31.5</v>
+      </c>
+      <c r="H81">
+        <v>45.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.16</v>
+      </c>
+      <c r="K81">
+        <v>0.908</v>
+      </c>
+      <c r="L81">
+        <v>5.252</v>
+      </c>
+      <c r="M81">
+        <v>67.4053596</v>
+      </c>
+      <c r="N81">
+        <v>-62.15335959999999</v>
+      </c>
+      <c r="O81">
+        <v>-19.267541476</v>
+      </c>
+      <c r="P81">
+        <v>-42.885818124</v>
+      </c>
+      <c r="Q81">
+        <v>-41.977818124</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2811447375599457</v>
+      </c>
+      <c r="T81">
+        <v>2.367776372823992</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02415416236426399</v>
+      </c>
+      <c r="W81">
+        <v>0.2330319860274138</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.07791665278794835</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2451356638492455</v>
+      </c>
+      <c r="C82">
+        <v>-163.0070586288235</v>
+      </c>
+      <c r="D82">
+        <v>91.33294137117655</v>
+      </c>
+      <c r="E82">
+        <v>-26.25999999999999</v>
+      </c>
+      <c r="F82">
+        <v>285.84</v>
+      </c>
+      <c r="G82">
+        <v>31.5</v>
+      </c>
+      <c r="H82">
+        <v>45.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.16</v>
+      </c>
+      <c r="K82">
+        <v>0.908</v>
+      </c>
+      <c r="L82">
+        <v>5.252</v>
+      </c>
+      <c r="M82">
+        <v>68.25859200000001</v>
+      </c>
+      <c r="N82">
+        <v>-63.006592</v>
+      </c>
+      <c r="O82">
+        <v>-19.53204352000001</v>
+      </c>
+      <c r="P82">
+        <v>-43.47454848</v>
+      </c>
+      <c r="Q82">
+        <v>-42.56654847999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.293261974437943</v>
+      </c>
+      <c r="T82">
+        <v>2.486165191465192</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02385223533471069</v>
+      </c>
+      <c r="W82">
+        <v>0.2331040862020711</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.076942694628099</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2471356638492455</v>
+      </c>
+      <c r="C83">
+        <v>-167.4568450578361</v>
+      </c>
+      <c r="D83">
+        <v>90.45615494216395</v>
+      </c>
+      <c r="E83">
+        <v>-22.68700000000001</v>
+      </c>
+      <c r="F83">
+        <v>289.413</v>
+      </c>
+      <c r="G83">
+        <v>31.5</v>
+      </c>
+      <c r="H83">
+        <v>45.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.16</v>
+      </c>
+      <c r="K83">
+        <v>0.908</v>
+      </c>
+      <c r="L83">
+        <v>5.252</v>
+      </c>
+      <c r="M83">
+        <v>69.1118244</v>
+      </c>
+      <c r="N83">
+        <v>-63.8598244</v>
+      </c>
+      <c r="O83">
+        <v>-19.796545564</v>
+      </c>
+      <c r="P83">
+        <v>-44.06327883599999</v>
+      </c>
+      <c r="Q83">
+        <v>-43.15527883599999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3066547099346769</v>
+      </c>
+      <c r="T83">
+        <v>2.617015991015992</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02355776329354142</v>
+      </c>
+      <c r="W83">
+        <v>0.2331744061255023</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.07599278481787552</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2491356638492455</v>
+      </c>
+      <c r="C84">
+        <v>-171.8899574447397</v>
+      </c>
+      <c r="D84">
+        <v>89.59604255526033</v>
+      </c>
+      <c r="E84">
+        <v>-19.11399999999998</v>
+      </c>
+      <c r="F84">
+        <v>292.986</v>
+      </c>
+      <c r="G84">
+        <v>31.5</v>
+      </c>
+      <c r="H84">
+        <v>45.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.16</v>
+      </c>
+      <c r="K84">
+        <v>0.908</v>
+      </c>
+      <c r="L84">
+        <v>5.252</v>
+      </c>
+      <c r="M84">
+        <v>69.96505680000001</v>
+      </c>
+      <c r="N84">
+        <v>-64.71305680000002</v>
+      </c>
+      <c r="O84">
+        <v>-20.06104760800001</v>
+      </c>
+      <c r="P84">
+        <v>-44.65200919200001</v>
+      </c>
+      <c r="Q84">
+        <v>-43.74400919200001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3215355271532701</v>
+      </c>
+      <c r="T84">
+        <v>2.762405768294658</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02327047349727871</v>
+      </c>
+      <c r="W84">
+        <v>0.2332430109288499</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.07506604353960866</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2511356638492455</v>
+      </c>
+      <c r="C85">
+        <v>-176.306866950388</v>
+      </c>
+      <c r="D85">
+        <v>88.75213304961206</v>
+      </c>
+      <c r="E85">
+        <v>-15.541</v>
+      </c>
+      <c r="F85">
+        <v>296.559</v>
+      </c>
+      <c r="G85">
+        <v>31.5</v>
+      </c>
+      <c r="H85">
+        <v>45.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.16</v>
+      </c>
+      <c r="K85">
+        <v>0.908</v>
+      </c>
+      <c r="L85">
+        <v>5.252</v>
+      </c>
+      <c r="M85">
+        <v>70.81828920000001</v>
+      </c>
+      <c r="N85">
+        <v>-65.56628920000001</v>
+      </c>
+      <c r="O85">
+        <v>-20.32554965200001</v>
+      </c>
+      <c r="P85">
+        <v>-45.24073954800001</v>
+      </c>
+      <c r="Q85">
+        <v>-44.33273954800001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3381670287505212</v>
+      </c>
+      <c r="T85">
+        <v>2.924900225253168</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0229901063467091</v>
+      </c>
+      <c r="W85">
+        <v>0.2333099626044059</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.07416163337648085</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2531356638492455</v>
+      </c>
+      <c r="C86">
+        <v>-180.7080271497287</v>
+      </c>
+      <c r="D86">
+        <v>87.92397285027128</v>
+      </c>
+      <c r="E86">
+        <v>-11.96800000000002</v>
+      </c>
+      <c r="F86">
+        <v>300.132</v>
+      </c>
+      <c r="G86">
+        <v>31.5</v>
+      </c>
+      <c r="H86">
+        <v>45.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.16</v>
+      </c>
+      <c r="K86">
+        <v>0.908</v>
+      </c>
+      <c r="L86">
+        <v>5.252</v>
+      </c>
+      <c r="M86">
+        <v>71.67152160000001</v>
+      </c>
+      <c r="N86">
+        <v>-66.41952160000001</v>
+      </c>
+      <c r="O86">
+        <v>-20.59005169600001</v>
+      </c>
+      <c r="P86">
+        <v>-45.82946990400001</v>
+      </c>
+      <c r="Q86">
+        <v>-44.92146990400001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3568774680474286</v>
+      </c>
+      <c r="T86">
+        <v>3.107706489331489</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02271641460448637</v>
+      </c>
+      <c r="W86">
+        <v>0.2333753201924487</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.07327875678866558</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2551356638492455</v>
+      </c>
+      <c r="C87">
+        <v>-185.0938748447028</v>
+      </c>
+      <c r="D87">
+        <v>87.11112515529722</v>
+      </c>
+      <c r="E87">
+        <v>-8.395000000000039</v>
+      </c>
+      <c r="F87">
+        <v>303.705</v>
+      </c>
+      <c r="G87">
+        <v>31.5</v>
+      </c>
+      <c r="H87">
+        <v>45.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.16</v>
+      </c>
+      <c r="K87">
+        <v>0.908</v>
+      </c>
+      <c r="L87">
+        <v>5.252</v>
+      </c>
+      <c r="M87">
+        <v>72.524754</v>
+      </c>
+      <c r="N87">
+        <v>-67.27275400000001</v>
+      </c>
+      <c r="O87">
+        <v>-20.85455374000001</v>
+      </c>
+      <c r="P87">
+        <v>-46.41820026</v>
+      </c>
+      <c r="Q87">
+        <v>-45.51020026</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3780826325839239</v>
+      </c>
+      <c r="T87">
+        <v>3.314886921953589</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.022449162667963</v>
+      </c>
+      <c r="W87">
+        <v>0.2334391399548904</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.07241665376762252</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2571356638492455</v>
+      </c>
+      <c r="C88">
+        <v>-189.4648308324653</v>
+      </c>
+      <c r="D88">
+        <v>86.31316916753477</v>
+      </c>
+      <c r="E88">
+        <v>-4.822000000000003</v>
+      </c>
+      <c r="F88">
+        <v>307.278</v>
+      </c>
+      <c r="G88">
+        <v>31.5</v>
+      </c>
+      <c r="H88">
+        <v>45.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.16</v>
+      </c>
+      <c r="K88">
+        <v>0.908</v>
+      </c>
+      <c r="L88">
+        <v>5.252</v>
+      </c>
+      <c r="M88">
+        <v>73.37798640000001</v>
+      </c>
+      <c r="N88">
+        <v>-68.12598640000002</v>
+      </c>
+      <c r="O88">
+        <v>-21.11905578400001</v>
+      </c>
+      <c r="P88">
+        <v>-47.00693061600001</v>
+      </c>
+      <c r="Q88">
+        <v>-46.098930616</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4023171063399185</v>
+      </c>
+      <c r="T88">
+        <v>3.551664559235988</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02218812589275412</v>
+      </c>
+      <c r="W88">
+        <v>0.2335014755368103</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.07157459965404545</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2591356638492455</v>
+      </c>
+      <c r="C89">
+        <v>-193.8213006317673</v>
+      </c>
+      <c r="D89">
+        <v>85.52969936823266</v>
+      </c>
+      <c r="E89">
+        <v>-1.249000000000024</v>
+      </c>
+      <c r="F89">
+        <v>310.851</v>
+      </c>
+      <c r="G89">
+        <v>31.5</v>
+      </c>
+      <c r="H89">
+        <v>45.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.16</v>
+      </c>
+      <c r="K89">
+        <v>0.908</v>
+      </c>
+      <c r="L89">
+        <v>5.252</v>
+      </c>
+      <c r="M89">
+        <v>74.23121880000001</v>
+      </c>
+      <c r="N89">
+        <v>-68.97921880000001</v>
+      </c>
+      <c r="O89">
+        <v>-21.38355782800001</v>
+      </c>
+      <c r="P89">
+        <v>-47.595660972</v>
+      </c>
+      <c r="Q89">
+        <v>-46.687660972</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4302799606737583</v>
+      </c>
+      <c r="T89">
+        <v>3.824869525331064</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02193308996295236</v>
+      </c>
+      <c r="W89">
+        <v>0.233562378116847</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.07075190310629786</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2611356638492455</v>
+      </c>
+      <c r="C90">
+        <v>-198.1636751701341</v>
+      </c>
+      <c r="D90">
+        <v>84.76032482986595</v>
+      </c>
+      <c r="E90">
+        <v>2.324000000000012</v>
+      </c>
+      <c r="F90">
+        <v>314.424</v>
+      </c>
+      <c r="G90">
+        <v>31.5</v>
+      </c>
+      <c r="H90">
+        <v>45.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.16</v>
+      </c>
+      <c r="K90">
+        <v>0.908</v>
+      </c>
+      <c r="L90">
+        <v>5.252</v>
+      </c>
+      <c r="M90">
+        <v>75.08445120000002</v>
+      </c>
+      <c r="N90">
+        <v>-69.83245120000002</v>
+      </c>
+      <c r="O90">
+        <v>-21.64805987200001</v>
+      </c>
+      <c r="P90">
+        <v>-48.18439132800001</v>
+      </c>
+      <c r="Q90">
+        <v>-47.27639132800001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.462903290729905</v>
+      </c>
+      <c r="T90">
+        <v>4.143608652441987</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02168385030428244</v>
+      </c>
+      <c r="W90">
+        <v>0.2336218965473374</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.06994790420736263</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2631356638492455</v>
+      </c>
+      <c r="C91">
+        <v>-202.4923314342832</v>
+      </c>
+      <c r="D91">
+        <v>84.00466856571686</v>
+      </c>
+      <c r="E91">
+        <v>5.896999999999991</v>
+      </c>
+      <c r="F91">
+        <v>317.997</v>
+      </c>
+      <c r="G91">
+        <v>31.5</v>
+      </c>
+      <c r="H91">
+        <v>45.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.16</v>
+      </c>
+      <c r="K91">
+        <v>0.908</v>
+      </c>
+      <c r="L91">
+        <v>5.252</v>
+      </c>
+      <c r="M91">
+        <v>75.93768360000001</v>
+      </c>
+      <c r="N91">
+        <v>-70.68568360000002</v>
+      </c>
+      <c r="O91">
+        <v>-21.91256191600001</v>
+      </c>
+      <c r="P91">
+        <v>-48.77312168400001</v>
+      </c>
+      <c r="Q91">
+        <v>-47.86512168400001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5014581353417146</v>
+      </c>
+      <c r="T91">
+        <v>4.520300348118531</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02144021153681859</v>
+      </c>
+      <c r="W91">
+        <v>0.2336800774850077</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.06916197269941471</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2651356638492455</v>
+      </c>
+      <c r="C92">
+        <v>-206.8076330860605</v>
+      </c>
+      <c r="D92">
+        <v>83.26236691393943</v>
+      </c>
+      <c r="E92">
+        <v>9.46999999999997</v>
+      </c>
+      <c r="F92">
+        <v>321.57</v>
+      </c>
+      <c r="G92">
+        <v>31.5</v>
+      </c>
+      <c r="H92">
+        <v>45.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.16</v>
+      </c>
+      <c r="K92">
+        <v>0.908</v>
+      </c>
+      <c r="L92">
+        <v>5.252</v>
+      </c>
+      <c r="M92">
+        <v>76.790916</v>
+      </c>
+      <c r="N92">
+        <v>-71.538916</v>
+      </c>
+      <c r="O92">
+        <v>-22.17706396000001</v>
+      </c>
+      <c r="P92">
+        <v>-49.36185204</v>
+      </c>
+      <c r="Q92">
+        <v>-48.45385203999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.547723948875886</v>
+      </c>
+      <c r="T92">
+        <v>4.972330382930384</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02120198696418728</v>
+      </c>
+      <c r="W92">
+        <v>0.2337369655129521</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.06839350633608787</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2671356638492455</v>
+      </c>
+      <c r="C93">
+        <v>-211.1099310460053</v>
+      </c>
+      <c r="D93">
+        <v>82.53306895399469</v>
+      </c>
+      <c r="E93">
+        <v>13.04300000000001</v>
+      </c>
+      <c r="F93">
+        <v>325.143</v>
+      </c>
+      <c r="G93">
+        <v>31.5</v>
+      </c>
+      <c r="H93">
+        <v>45.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.16</v>
+      </c>
+      <c r="K93">
+        <v>0.908</v>
+      </c>
+      <c r="L93">
+        <v>5.252</v>
+      </c>
+      <c r="M93">
+        <v>77.64414840000001</v>
+      </c>
+      <c r="N93">
+        <v>-72.39214840000001</v>
+      </c>
+      <c r="O93">
+        <v>-22.44156600400001</v>
+      </c>
+      <c r="P93">
+        <v>-49.950582396</v>
+      </c>
+      <c r="Q93">
+        <v>-49.042582396</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6042710543065402</v>
+      </c>
+      <c r="T93">
+        <v>5.524811536589317</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02096899809644896</v>
+      </c>
+      <c r="W93">
+        <v>0.233792603254568</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.06764192934338364</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2691356638492455</v>
+      </c>
+      <c r="C94">
+        <v>-215.399564046512</v>
+      </c>
+      <c r="D94">
+        <v>81.81643595348801</v>
+      </c>
+      <c r="E94">
+        <v>16.61599999999999</v>
+      </c>
+      <c r="F94">
+        <v>328.716</v>
+      </c>
+      <c r="G94">
+        <v>31.5</v>
+      </c>
+      <c r="H94">
+        <v>45.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.16</v>
+      </c>
+      <c r="K94">
+        <v>0.908</v>
+      </c>
+      <c r="L94">
+        <v>5.252</v>
+      </c>
+      <c r="M94">
+        <v>78.4973808</v>
+      </c>
+      <c r="N94">
+        <v>-73.24538080000001</v>
+      </c>
+      <c r="O94">
+        <v>-22.70606804800001</v>
+      </c>
+      <c r="P94">
+        <v>-50.539312752</v>
+      </c>
+      <c r="Q94">
+        <v>-49.631312752</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6749549360948579</v>
+      </c>
+      <c r="T94">
+        <v>6.215412978662983</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02074107420409625</v>
+      </c>
+      <c r="W94">
+        <v>0.2338470314800618</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.06690669098095559</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2711356638492455</v>
+      </c>
+      <c r="C95">
+        <v>-219.6768591564232</v>
+      </c>
+      <c r="D95">
+        <v>81.11214084357687</v>
+      </c>
+      <c r="E95">
+        <v>20.18900000000002</v>
+      </c>
+      <c r="F95">
+        <v>332.289</v>
+      </c>
+      <c r="G95">
+        <v>31.5</v>
+      </c>
+      <c r="H95">
+        <v>45.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.16</v>
+      </c>
+      <c r="K95">
+        <v>0.908</v>
+      </c>
+      <c r="L95">
+        <v>5.252</v>
+      </c>
+      <c r="M95">
+        <v>79.35061320000001</v>
+      </c>
+      <c r="N95">
+        <v>-74.09861320000002</v>
+      </c>
+      <c r="O95">
+        <v>-22.97057009200001</v>
+      </c>
+      <c r="P95">
+        <v>-51.12804310800001</v>
+      </c>
+      <c r="Q95">
+        <v>-50.22004310800001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7658342126798376</v>
+      </c>
+      <c r="T95">
+        <v>7.103329118471982</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0205180519008264</v>
+      </c>
+      <c r="W95">
+        <v>0.2339002892060827</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.06618726419621412</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2731356638492455</v>
+      </c>
+      <c r="C96">
+        <v>-223.9421322787572</v>
+      </c>
+      <c r="D96">
+        <v>80.41986772124277</v>
+      </c>
+      <c r="E96">
+        <v>23.762</v>
+      </c>
+      <c r="F96">
+        <v>335.862</v>
+      </c>
+      <c r="G96">
+        <v>31.5</v>
+      </c>
+      <c r="H96">
+        <v>45.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.16</v>
+      </c>
+      <c r="K96">
+        <v>0.908</v>
+      </c>
+      <c r="L96">
+        <v>5.252</v>
+      </c>
+      <c r="M96">
+        <v>80.20384560000001</v>
+      </c>
+      <c r="N96">
+        <v>-74.95184560000001</v>
+      </c>
+      <c r="O96">
+        <v>-23.23507213600001</v>
+      </c>
+      <c r="P96">
+        <v>-51.71677346400001</v>
+      </c>
+      <c r="Q96">
+        <v>-50.80877346400001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8870065814598107</v>
+      </c>
+      <c r="T96">
+        <v>8.287217304883979</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02029977475294526</v>
+      </c>
+      <c r="W96">
+        <v>0.2339524137889967</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.06548314436433944</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2751356638492455</v>
+      </c>
+      <c r="C97">
+        <v>-228.1956886231653</v>
+      </c>
+      <c r="D97">
+        <v>79.73931137683473</v>
+      </c>
+      <c r="E97">
+        <v>27.33500000000004</v>
+      </c>
+      <c r="F97">
+        <v>339.4350000000001</v>
+      </c>
+      <c r="G97">
+        <v>31.5</v>
+      </c>
+      <c r="H97">
+        <v>45.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.16</v>
+      </c>
+      <c r="K97">
+        <v>0.908</v>
+      </c>
+      <c r="L97">
+        <v>5.252</v>
+      </c>
+      <c r="M97">
+        <v>81.05707800000002</v>
+      </c>
+      <c r="N97">
+        <v>-75.80507800000002</v>
+      </c>
+      <c r="O97">
+        <v>-23.49957418000001</v>
+      </c>
+      <c r="P97">
+        <v>-52.30550382000001</v>
+      </c>
+      <c r="Q97">
+        <v>-51.39750382000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.056647897751773</v>
+      </c>
+      <c r="T97">
+        <v>9.944660765860782</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02008609291344057</v>
+      </c>
+      <c r="W97">
+        <v>0.2340034410122704</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.0647938481078727</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2771356638492455</v>
+      </c>
+      <c r="C98">
+        <v>-232.4378231545988</v>
+      </c>
+      <c r="D98">
+        <v>79.07017684540119</v>
+      </c>
+      <c r="E98">
+        <v>30.90799999999996</v>
+      </c>
+      <c r="F98">
+        <v>343.008</v>
+      </c>
+      <c r="G98">
+        <v>31.5</v>
+      </c>
+      <c r="H98">
+        <v>45.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.16</v>
+      </c>
+      <c r="K98">
+        <v>0.908</v>
+      </c>
+      <c r="L98">
+        <v>5.252</v>
+      </c>
+      <c r="M98">
+        <v>81.9103104</v>
+      </c>
+      <c r="N98">
+        <v>-76.6583104</v>
+      </c>
+      <c r="O98">
+        <v>-23.76407622400001</v>
+      </c>
+      <c r="P98">
+        <v>-52.894234176</v>
+      </c>
+      <c r="Q98">
+        <v>-51.986234176</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.311109872189714</v>
+      </c>
+      <c r="T98">
+        <v>12.43082595732595</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01987686277892557</v>
+      </c>
+      <c r="W98">
+        <v>0.2340534051683926</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.06411891219008248</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2791356638492455</v>
+      </c>
+      <c r="C99">
+        <v>-236.6688210195765</v>
+      </c>
+      <c r="D99">
+        <v>78.41217898042349</v>
+      </c>
+      <c r="E99">
+        <v>34.48099999999999</v>
+      </c>
+      <c r="F99">
+        <v>346.581</v>
+      </c>
+      <c r="G99">
+        <v>31.5</v>
+      </c>
+      <c r="H99">
+        <v>45.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.16</v>
+      </c>
+      <c r="K99">
+        <v>0.908</v>
+      </c>
+      <c r="L99">
+        <v>5.252</v>
+      </c>
+      <c r="M99">
+        <v>82.76354280000001</v>
+      </c>
+      <c r="N99">
+        <v>-77.51154280000002</v>
+      </c>
+      <c r="O99">
+        <v>-24.02857826800001</v>
+      </c>
+      <c r="P99">
+        <v>-53.48296453200001</v>
+      </c>
+      <c r="Q99">
+        <v>-52.57496453200001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.735213162919619</v>
+      </c>
+      <c r="T99">
+        <v>16.57443460976793</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01967194666780263</v>
+      </c>
+      <c r="W99">
+        <v>0.2341023391357288</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.06345789247678257</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2811356638492455</v>
+      </c>
+      <c r="C100">
+        <v>-240.8889579513424</v>
+      </c>
+      <c r="D100">
+        <v>77.76504204865761</v>
+      </c>
+      <c r="E100">
+        <v>38.05399999999997</v>
+      </c>
+      <c r="F100">
+        <v>350.154</v>
+      </c>
+      <c r="G100">
+        <v>31.5</v>
+      </c>
+      <c r="H100">
+        <v>45.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.16</v>
+      </c>
+      <c r="K100">
+        <v>0.908</v>
+      </c>
+      <c r="L100">
+        <v>5.252</v>
+      </c>
+      <c r="M100">
+        <v>83.61677520000001</v>
+      </c>
+      <c r="N100">
+        <v>-78.36477520000001</v>
+      </c>
+      <c r="O100">
+        <v>-24.29308031200001</v>
+      </c>
+      <c r="P100">
+        <v>-54.071694888</v>
+      </c>
+      <c r="Q100">
+        <v>-53.163694888</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.583419744379428</v>
+      </c>
+      <c r="T100">
+        <v>24.86165191465189</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01947121251813117</v>
+      </c>
+      <c r="W100">
+        <v>0.2341502744506703</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.06281036296171338</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2831356638492455</v>
+      </c>
+      <c r="C101">
+        <v>-245.0985006551259</v>
+      </c>
+      <c r="D101">
+        <v>77.12849934487419</v>
+      </c>
+      <c r="E101">
+        <v>41.62700000000001</v>
+      </c>
+      <c r="F101">
+        <v>353.727</v>
+      </c>
+      <c r="G101">
+        <v>31.5</v>
+      </c>
+      <c r="H101">
+        <v>45.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.16</v>
+      </c>
+      <c r="K101">
+        <v>0.908</v>
+      </c>
+      <c r="L101">
+        <v>5.252</v>
+      </c>
+      <c r="M101">
+        <v>84.47000760000002</v>
+      </c>
+      <c r="N101">
+        <v>-79.21800760000002</v>
+      </c>
+      <c r="O101">
+        <v>-24.55758235600001</v>
+      </c>
+      <c r="P101">
+        <v>-54.66042524400001</v>
+      </c>
+      <c r="Q101">
+        <v>-53.75242524400001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.128039488758856</v>
+      </c>
+      <c r="T101">
+        <v>49.72330382930379</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01927453360380661</v>
+      </c>
+      <c r="W101">
+        <v>0.234197241375411</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.06217591485098906</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/morocco/morocco_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_real_estate_development.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07999969892735882</v>
+        <v>0.07977429989079128</v>
       </c>
       <c r="C2">
-        <v>2016.902515994468</v>
+        <v>2009.7959487884</v>
       </c>
       <c r="D2">
-        <v>1980.802515994468</v>
+        <v>1993.9439487884</v>
       </c>
       <c r="E2">
-        <v>-474.2</v>
+        <v>-453.952</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.248</v>
       </c>
       <c r="G2">
         <v>36.1</v>
@@ -1573,28 +1573,28 @@
         <v>40.733</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.0184744</v>
       </c>
       <c r="N2">
-        <v>40.733</v>
+        <v>39.71452559999999</v>
       </c>
       <c r="O2">
-        <v>13.03456</v>
+        <v>12.708648192</v>
       </c>
       <c r="P2">
-        <v>27.69844</v>
+        <v>27.005877408</v>
       </c>
       <c r="Q2">
-        <v>27.76544</v>
+        <v>27.072877408</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07999969892735882</v>
+        <v>0.08023460595029422</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241992</v>
+        <v>0.4487983507122039</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>39.99413240038237</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07977429989079128</v>
+        <v>0.07954890085422374</v>
       </c>
       <c r="C3">
-        <v>2009.7959487884</v>
+        <v>2002.864917153322</v>
       </c>
       <c r="D3">
-        <v>1993.9439487884</v>
+        <v>2007.260917153322</v>
       </c>
       <c r="E3">
-        <v>-453.952</v>
+        <v>-433.704</v>
       </c>
       <c r="F3">
-        <v>20.248</v>
+        <v>40.496</v>
       </c>
       <c r="G3">
         <v>36.1</v>
@@ -1655,28 +1655,28 @@
         <v>40.733</v>
       </c>
       <c r="M3">
-        <v>1.0184744</v>
+        <v>2.0369488</v>
       </c>
       <c r="N3">
-        <v>39.71452559999999</v>
+        <v>38.6960512</v>
       </c>
       <c r="O3">
-        <v>12.708648192</v>
+        <v>12.382736384</v>
       </c>
       <c r="P3">
-        <v>27.005877408</v>
+        <v>26.313314816</v>
       </c>
       <c r="Q3">
-        <v>27.072877408</v>
+        <v>26.380314816</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08023460595029422</v>
+        <v>0.08047430699410585</v>
       </c>
       <c r="T3">
-        <v>0.4487983507122039</v>
+        <v>0.4519224588632289</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>39.99413240038237</v>
+        <v>19.99706620019118</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07954890085422374</v>
+        <v>0.07932350181765618</v>
       </c>
       <c r="C4">
-        <v>2002.864917153322</v>
+        <v>1996.112961788724</v>
       </c>
       <c r="D4">
-        <v>2007.260917153322</v>
+        <v>2020.756961788724</v>
       </c>
       <c r="E4">
-        <v>-433.704</v>
+        <v>-413.456</v>
       </c>
       <c r="F4">
-        <v>40.496</v>
+        <v>60.744</v>
       </c>
       <c r="G4">
         <v>36.1</v>
@@ -1737,28 +1737,28 @@
         <v>40.733</v>
       </c>
       <c r="M4">
-        <v>2.0369488</v>
+        <v>3.0554232</v>
       </c>
       <c r="N4">
-        <v>38.6960512</v>
+        <v>37.6775768</v>
       </c>
       <c r="O4">
-        <v>12.382736384</v>
+        <v>12.056824576</v>
       </c>
       <c r="P4">
-        <v>26.313314816</v>
+        <v>25.620752224</v>
       </c>
       <c r="Q4">
-        <v>26.380314816</v>
+        <v>25.687752224</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08047430699410585</v>
+        <v>0.0807189503274806</v>
       </c>
       <c r="T4">
-        <v>0.4519224588632289</v>
+        <v>0.4551109816153061</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>19.99706620019118</v>
+        <v>13.33137746679412</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07932350181765618</v>
+        <v>0.07918514278108864</v>
       </c>
       <c r="C5">
-        <v>1996.112961788724</v>
+        <v>1984.239644748853</v>
       </c>
       <c r="D5">
-        <v>2020.756961788724</v>
+        <v>2029.131644748853</v>
       </c>
       <c r="E5">
-        <v>-413.456</v>
+        <v>-393.208</v>
       </c>
       <c r="F5">
-        <v>60.744</v>
+        <v>80.992</v>
       </c>
       <c r="G5">
         <v>36.1</v>
@@ -1819,45 +1819,45 @@
         <v>40.733</v>
       </c>
       <c r="M5">
-        <v>3.0554232</v>
+        <v>4.333072</v>
       </c>
       <c r="N5">
-        <v>37.6775768</v>
+        <v>36.399928</v>
       </c>
       <c r="O5">
-        <v>12.056824576</v>
+        <v>11.64797696</v>
       </c>
       <c r="P5">
-        <v>25.620752224</v>
+        <v>24.75195103999999</v>
       </c>
       <c r="Q5">
-        <v>25.687752224</v>
+        <v>24.81895103999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0807189503274806</v>
+        <v>0.08096869039696733</v>
       </c>
       <c r="T5">
-        <v>0.4551109816153061</v>
+        <v>0.4583659319247182</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.32</v>
       </c>
       <c r="W5">
-        <v>0.034204</v>
+        <v>0.03638</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>13.33137746679412</v>
+        <v>9.400489998781463</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07918514278108864</v>
+        <v>0.0790087037445211</v>
       </c>
       <c r="C6">
-        <v>1984.239644748853</v>
+        <v>1974.772494107577</v>
       </c>
       <c r="D6">
-        <v>2029.131644748853</v>
+        <v>2039.912494107577</v>
       </c>
       <c r="E6">
-        <v>-393.208</v>
+        <v>-372.96</v>
       </c>
       <c r="F6">
-        <v>80.992</v>
+        <v>101.24</v>
       </c>
       <c r="G6">
         <v>36.1</v>
@@ -1901,45 +1901,45 @@
         <v>40.733</v>
       </c>
       <c r="M6">
-        <v>4.333072</v>
+        <v>5.497332000000001</v>
       </c>
       <c r="N6">
-        <v>36.399928</v>
+        <v>35.235668</v>
       </c>
       <c r="O6">
-        <v>11.64797696</v>
+        <v>11.27541376</v>
       </c>
       <c r="P6">
-        <v>24.75195103999999</v>
+        <v>23.96025424</v>
       </c>
       <c r="Q6">
-        <v>24.81895103999999</v>
+        <v>24.02725424</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08096869039696733</v>
+        <v>0.08122368815212747</v>
       </c>
       <c r="T6">
-        <v>0.4583659319247182</v>
+        <v>0.4616894075038022</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.32</v>
       </c>
       <c r="W6">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>9.400489998781463</v>
+        <v>7.409594326848004</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0790087037445211</v>
+        <v>0.07881050470795353</v>
       </c>
       <c r="C7">
-        <v>1974.772494107577</v>
+        <v>1966.772373823177</v>
       </c>
       <c r="D7">
-        <v>2039.912494107577</v>
+        <v>2052.160373823177</v>
       </c>
       <c r="E7">
-        <v>-372.96</v>
+        <v>-352.712</v>
       </c>
       <c r="F7">
-        <v>101.24</v>
+        <v>121.488</v>
       </c>
       <c r="G7">
         <v>36.1</v>
@@ -1983,28 +1983,28 @@
         <v>40.733</v>
       </c>
       <c r="M7">
-        <v>5.497332000000001</v>
+        <v>6.596798400000001</v>
       </c>
       <c r="N7">
-        <v>35.235668</v>
+        <v>34.13620159999999</v>
       </c>
       <c r="O7">
-        <v>11.27541376</v>
+        <v>10.923584512</v>
       </c>
       <c r="P7">
-        <v>23.96025424</v>
+        <v>23.21261708799999</v>
       </c>
       <c r="Q7">
-        <v>24.02725424</v>
+        <v>23.27961708799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08122368815212747</v>
+        <v>0.08148411139143993</v>
       </c>
       <c r="T7">
-        <v>0.4616894075038022</v>
+        <v>0.4650835953292496</v>
       </c>
       <c r="U7">
         <v>0.0543</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>7.409594326848004</v>
+        <v>6.174661939040003</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07881050470795353</v>
+        <v>0.07865990567138599</v>
       </c>
       <c r="C8">
-        <v>1966.772373823177</v>
+        <v>1955.929555270456</v>
       </c>
       <c r="D8">
-        <v>2052.160373823177</v>
+        <v>2061.565555270456</v>
       </c>
       <c r="E8">
-        <v>-352.712</v>
+        <v>-332.464</v>
       </c>
       <c r="F8">
-        <v>121.488</v>
+        <v>141.736</v>
       </c>
       <c r="G8">
         <v>36.1</v>
@@ -2065,45 +2065,45 @@
         <v>40.733</v>
       </c>
       <c r="M8">
-        <v>6.5967984</v>
+        <v>7.8380008</v>
       </c>
       <c r="N8">
-        <v>34.1362016</v>
+        <v>32.8949992</v>
       </c>
       <c r="O8">
-        <v>10.923584512</v>
+        <v>10.526399744</v>
       </c>
       <c r="P8">
-        <v>23.212617088</v>
+        <v>22.368599456</v>
       </c>
       <c r="Q8">
-        <v>23.279617088</v>
+        <v>22.435599456</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08148411139143993</v>
+        <v>0.08175013513052257</v>
       </c>
       <c r="T8">
-        <v>0.4650835953292496</v>
+        <v>0.4685507764412658</v>
       </c>
       <c r="U8">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V8">
         <v>0.32</v>
       </c>
       <c r="W8">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>6.174661939040004</v>
+        <v>5.196860913818738</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07865990567138598</v>
+        <v>0.07846850663481844</v>
       </c>
       <c r="C9">
-        <v>1955.929555270457</v>
+        <v>1947.759905392499</v>
       </c>
       <c r="D9">
-        <v>2061.565555270457</v>
+        <v>2073.643905392499</v>
       </c>
       <c r="E9">
-        <v>-332.4639999999999</v>
+        <v>-312.216</v>
       </c>
       <c r="F9">
-        <v>141.736</v>
+        <v>161.984</v>
       </c>
       <c r="G9">
         <v>36.1</v>
@@ -2147,28 +2147,28 @@
         <v>40.733</v>
       </c>
       <c r="M9">
-        <v>7.838000800000001</v>
+        <v>8.957715200000001</v>
       </c>
       <c r="N9">
-        <v>32.89499919999999</v>
+        <v>31.77528479999999</v>
       </c>
       <c r="O9">
-        <v>10.526399744</v>
+        <v>10.168091136</v>
       </c>
       <c r="P9">
-        <v>22.36859945599999</v>
+        <v>21.60719366399999</v>
       </c>
       <c r="Q9">
-        <v>22.43559945599999</v>
+        <v>21.67419366399999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08175013513052257</v>
+        <v>0.08202194199436787</v>
       </c>
       <c r="T9">
-        <v>0.4685507764412658</v>
+        <v>0.4720933310557171</v>
       </c>
       <c r="U9">
         <v>0.0553</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>5.196860913818736</v>
+        <v>4.547253299591395</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07846850663481844</v>
+        <v>0.07864430759825089</v>
       </c>
       <c r="C10">
-        <v>1947.759905392499</v>
+        <v>1916.412612302112</v>
       </c>
       <c r="D10">
-        <v>2073.643905392499</v>
+        <v>2062.544612302112</v>
       </c>
       <c r="E10">
-        <v>-312.216</v>
+        <v>-291.968</v>
       </c>
       <c r="F10">
-        <v>161.984</v>
+        <v>182.232</v>
       </c>
       <c r="G10">
         <v>36.1</v>
@@ -2229,45 +2229,45 @@
         <v>40.733</v>
       </c>
       <c r="M10">
-        <v>8.957715200000001</v>
+        <v>11.1708216</v>
       </c>
       <c r="N10">
-        <v>31.77528479999999</v>
+        <v>29.5621784</v>
       </c>
       <c r="O10">
-        <v>10.168091136</v>
+        <v>9.459897088</v>
       </c>
       <c r="P10">
-        <v>21.60719366399999</v>
+        <v>20.102281312</v>
       </c>
       <c r="Q10">
-        <v>21.67419366399999</v>
+        <v>20.169281312</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08202194199436787</v>
+        <v>0.08229972263544054</v>
       </c>
       <c r="T10">
-        <v>0.4720933310557171</v>
+        <v>0.4757137440133432</v>
       </c>
       <c r="U10">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.037604</v>
+        <v>0.041684</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.547253299591395</v>
+        <v>3.646374587165549</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07864430759825089</v>
+        <v>0.07868410856168334</v>
       </c>
       <c r="C11">
-        <v>1916.412612302112</v>
+        <v>1893.66823133627</v>
       </c>
       <c r="D11">
-        <v>2062.544612302112</v>
+        <v>2060.04823133627</v>
       </c>
       <c r="E11">
-        <v>-291.968</v>
+        <v>-271.72</v>
       </c>
       <c r="F11">
-        <v>182.232</v>
+        <v>202.48</v>
       </c>
       <c r="G11">
         <v>36.1</v>
@@ -2311,45 +2311,45 @@
         <v>40.733</v>
       </c>
       <c r="M11">
-        <v>11.1708216</v>
+        <v>12.978968</v>
       </c>
       <c r="N11">
-        <v>29.5621784</v>
+        <v>27.754032</v>
       </c>
       <c r="O11">
-        <v>9.459897088</v>
+        <v>8.881290239999998</v>
       </c>
       <c r="P11">
-        <v>20.102281312</v>
+        <v>18.87274176</v>
       </c>
       <c r="Q11">
-        <v>20.169281312</v>
+        <v>18.93974176</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08229972263544054</v>
+        <v>0.08258367617964815</v>
       </c>
       <c r="T11">
-        <v>0.4757137440133432</v>
+        <v>0.4794146105922499</v>
       </c>
       <c r="U11">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V11">
         <v>0.32</v>
       </c>
       <c r="W11">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.646374587165549</v>
+        <v>3.138385116597868</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07868410856168334</v>
+        <v>0.07913598952511579</v>
       </c>
       <c r="C12">
-        <v>1893.66823133627</v>
+        <v>1845.495559150008</v>
       </c>
       <c r="D12">
-        <v>2060.04823133627</v>
+        <v>2032.123559150008</v>
       </c>
       <c r="E12">
-        <v>-271.72</v>
+        <v>-251.472</v>
       </c>
       <c r="F12">
-        <v>202.48</v>
+        <v>222.728</v>
       </c>
       <c r="G12">
         <v>36.1</v>
@@ -2393,45 +2393,45 @@
         <v>40.733</v>
       </c>
       <c r="M12">
-        <v>12.978968</v>
+        <v>16.0141432</v>
       </c>
       <c r="N12">
-        <v>27.754032</v>
+        <v>24.71885679999999</v>
       </c>
       <c r="O12">
-        <v>8.881290239999998</v>
+        <v>7.910034175999998</v>
       </c>
       <c r="P12">
-        <v>18.87274176</v>
+        <v>16.80882262399999</v>
       </c>
       <c r="Q12">
-        <v>18.93974176</v>
+        <v>16.87582262399999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08258367617964815</v>
+        <v>0.08287401070237729</v>
       </c>
       <c r="T12">
-        <v>0.4794146105922499</v>
+        <v>0.4831986427122555</v>
       </c>
       <c r="U12">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>3.138385116597867</v>
+        <v>2.54356411649922</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07913598952511579</v>
+        <v>0.07937571048854825</v>
       </c>
       <c r="C13">
-        <v>1845.495559150008</v>
+        <v>1810.738778536731</v>
       </c>
       <c r="D13">
-        <v>2032.123559150008</v>
+        <v>2017.614778536732</v>
       </c>
       <c r="E13">
-        <v>-251.472</v>
+        <v>-231.224</v>
       </c>
       <c r="F13">
-        <v>222.728</v>
+        <v>242.976</v>
       </c>
       <c r="G13">
         <v>36.1</v>
@@ -2475,45 +2475,45 @@
         <v>40.733</v>
       </c>
       <c r="M13">
-        <v>16.0141432</v>
+        <v>18.4175808</v>
       </c>
       <c r="N13">
-        <v>24.71885679999999</v>
+        <v>22.31541919999999</v>
       </c>
       <c r="O13">
-        <v>7.910034175999998</v>
+        <v>7.140934143999998</v>
       </c>
       <c r="P13">
-        <v>16.80882262399999</v>
+        <v>15.17448505599999</v>
       </c>
       <c r="Q13">
-        <v>16.87582262399999</v>
+        <v>15.24148505599999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08287401070237729</v>
+        <v>0.08317094373698664</v>
       </c>
       <c r="T13">
-        <v>0.4831986427122555</v>
+        <v>0.4870686755622614</v>
       </c>
       <c r="U13">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y13">
-        <v>2.54356411649922</v>
+        <v>2.211636829088866</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07937571048854825</v>
+        <v>0.07932371145198069</v>
       </c>
       <c r="C14">
-        <v>1810.738778536731</v>
+        <v>1793.620325359095</v>
       </c>
       <c r="D14">
-        <v>2017.614778536732</v>
+        <v>2020.744325359095</v>
       </c>
       <c r="E14">
-        <v>-231.224</v>
+        <v>-210.976</v>
       </c>
       <c r="F14">
-        <v>242.976</v>
+        <v>263.224</v>
       </c>
       <c r="G14">
         <v>36.1</v>
@@ -2557,28 +2557,28 @@
         <v>40.733</v>
       </c>
       <c r="M14">
-        <v>18.4175808</v>
+        <v>19.9523792</v>
       </c>
       <c r="N14">
-        <v>22.31541919999999</v>
+        <v>20.7806208</v>
       </c>
       <c r="O14">
-        <v>7.140934143999998</v>
+        <v>6.649798656</v>
       </c>
       <c r="P14">
-        <v>15.17448505599999</v>
+        <v>14.130822144</v>
       </c>
       <c r="Q14">
-        <v>15.24148505599999</v>
+        <v>14.197822144</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08317094373698664</v>
+        <v>0.08347470281836861</v>
       </c>
       <c r="T14">
-        <v>0.4870686755622614</v>
+        <v>0.4910276746846811</v>
       </c>
       <c r="U14">
         <v>0.07580000000000001</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.211636829088866</v>
+        <v>2.041510919158954</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07932371145198069</v>
+        <v>0.08062355241541314</v>
       </c>
       <c r="C15">
-        <v>1793.620325359095</v>
+        <v>1697.94503352534</v>
       </c>
       <c r="D15">
-        <v>2020.744325359095</v>
+        <v>1945.31703352534</v>
       </c>
       <c r="E15">
-        <v>-210.976</v>
+        <v>-190.728</v>
       </c>
       <c r="F15">
-        <v>263.224</v>
+        <v>283.472</v>
       </c>
       <c r="G15">
         <v>36.1</v>
@@ -2639,45 +2639,45 @@
         <v>40.733</v>
       </c>
       <c r="M15">
-        <v>19.9523792</v>
+        <v>25.51248</v>
       </c>
       <c r="N15">
-        <v>20.7806208</v>
+        <v>15.22051999999999</v>
       </c>
       <c r="O15">
-        <v>6.649798656</v>
+        <v>4.870566399999998</v>
       </c>
       <c r="P15">
-        <v>14.130822144</v>
+        <v>10.3499536</v>
       </c>
       <c r="Q15">
-        <v>14.197822144</v>
+        <v>10.4169536</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08347470281836861</v>
+        <v>0.08378552606443389</v>
       </c>
       <c r="T15">
-        <v>0.4910276746846811</v>
+        <v>0.4950787435541338</v>
       </c>
       <c r="U15">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V15">
         <v>0.32</v>
       </c>
       <c r="W15">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.041510919158954</v>
+        <v>1.596591158523201</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08062355241541314</v>
+        <v>0.08721252238363118</v>
       </c>
       <c r="C16">
-        <v>1697.94503352534</v>
+        <v>1368.185929762489</v>
       </c>
       <c r="D16">
-        <v>1945.31703352534</v>
+        <v>1635.805929762489</v>
       </c>
       <c r="E16">
-        <v>-190.728</v>
+        <v>-170.48</v>
       </c>
       <c r="F16">
-        <v>283.472</v>
+        <v>303.72</v>
       </c>
       <c r="G16">
         <v>36.1</v>
@@ -2721,45 +2721,45 @@
         <v>40.733</v>
       </c>
       <c r="M16">
-        <v>25.51248</v>
+        <v>44.586096</v>
       </c>
       <c r="N16">
-        <v>15.22051999999999</v>
+        <v>-3.853096000000008</v>
       </c>
       <c r="O16">
-        <v>4.870566399999998</v>
+        <v>-1.232990720000003</v>
       </c>
       <c r="P16">
-        <v>10.3499536</v>
+        <v>-2.620105280000005</v>
       </c>
       <c r="Q16">
-        <v>10.4169536</v>
+        <v>-2.553105280000005</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08378552606443389</v>
+        <v>0.08427056227623145</v>
       </c>
       <c r="T16">
-        <v>0.4950787435541338</v>
+        <v>0.5014003913814578</v>
       </c>
       <c r="U16">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.32</v>
+        <v>0.2923458470102428</v>
       </c>
       <c r="W16">
-        <v>0.06119999999999999</v>
+        <v>0.1038836296588964</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y16">
-        <v>1.596591158523201</v>
+        <v>0.9135807719070087</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08721252238363117</v>
+        <v>0.08822252238363118</v>
       </c>
       <c r="C17">
-        <v>1368.185929762489</v>
+        <v>1308.9924853092</v>
       </c>
       <c r="D17">
-        <v>1635.805929762489</v>
+        <v>1596.8604853092</v>
       </c>
       <c r="E17">
-        <v>-170.48</v>
+        <v>-150.232</v>
       </c>
       <c r="F17">
-        <v>303.72</v>
+        <v>323.968</v>
       </c>
       <c r="G17">
         <v>36.1</v>
@@ -2803,37 +2803,37 @@
         <v>40.733</v>
       </c>
       <c r="M17">
-        <v>44.586096</v>
+        <v>47.55850240000001</v>
       </c>
       <c r="N17">
-        <v>-3.853096000000001</v>
+        <v>-6.825502400000012</v>
       </c>
       <c r="O17">
-        <v>-1.23299072</v>
+        <v>-2.184160768000004</v>
       </c>
       <c r="P17">
-        <v>-2.620105280000001</v>
+        <v>-4.641341632000008</v>
       </c>
       <c r="Q17">
-        <v>-2.55310528</v>
+        <v>-4.574341632000008</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08427056227623145</v>
+        <v>0.08472854516047229</v>
       </c>
       <c r="T17">
-        <v>0.5014003913814578</v>
+        <v>0.5073694436598085</v>
       </c>
       <c r="U17">
         <v>0.1468</v>
       </c>
       <c r="V17">
-        <v>0.2923458470102429</v>
+        <v>0.2740742315721026</v>
       </c>
       <c r="W17">
-        <v>0.1038836296588963</v>
+        <v>0.1065659028052154</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.9135807719070088</v>
+        <v>0.8564819736628206</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08822252238363118</v>
+        <v>0.08923252238363118</v>
       </c>
       <c r="C18">
-        <v>1308.9924853092</v>
+        <v>1251.610351677345</v>
       </c>
       <c r="D18">
-        <v>1596.8604853092</v>
+        <v>1559.726351677345</v>
       </c>
       <c r="E18">
-        <v>-150.232</v>
+        <v>-129.984</v>
       </c>
       <c r="F18">
-        <v>323.968</v>
+        <v>344.216</v>
       </c>
       <c r="G18">
         <v>36.1</v>
@@ -2885,37 +2885,37 @@
         <v>40.733</v>
       </c>
       <c r="M18">
-        <v>47.55850240000001</v>
+        <v>50.53090880000001</v>
       </c>
       <c r="N18">
-        <v>-6.825502400000012</v>
+        <v>-9.797908800000009</v>
       </c>
       <c r="O18">
-        <v>-2.184160768000004</v>
+        <v>-3.135330816000003</v>
       </c>
       <c r="P18">
-        <v>-4.641341632000008</v>
+        <v>-6.662577984000006</v>
       </c>
       <c r="Q18">
-        <v>-4.574341632000008</v>
+        <v>-6.595577984000006</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08472854516047229</v>
+        <v>0.08519756377686352</v>
       </c>
       <c r="T18">
-        <v>0.5073694436598085</v>
+        <v>0.5134823285231797</v>
       </c>
       <c r="U18">
         <v>0.1468</v>
       </c>
       <c r="V18">
-        <v>0.2740742315721026</v>
+        <v>0.2579522179502142</v>
       </c>
       <c r="W18">
-        <v>0.1065659028052154</v>
+        <v>0.1089326144049085</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.8564819736628206</v>
+        <v>0.8061006810944195</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08923252238363118</v>
+        <v>0.1003658338059337</v>
       </c>
       <c r="C19">
-        <v>1251.610351677345</v>
+        <v>913.1243995449732</v>
       </c>
       <c r="D19">
-        <v>1559.726351677345</v>
+        <v>1241.488399544973</v>
       </c>
       <c r="E19">
-        <v>-129.984</v>
+        <v>-109.7359999999999</v>
       </c>
       <c r="F19">
-        <v>344.216</v>
+        <v>364.4640000000001</v>
       </c>
       <c r="G19">
         <v>36.1</v>
@@ -2967,45 +2967,45 @@
         <v>40.733</v>
       </c>
       <c r="M19">
-        <v>50.53090880000001</v>
+        <v>73.18437120000002</v>
       </c>
       <c r="N19">
-        <v>-9.797908800000009</v>
+        <v>-32.45137120000002</v>
       </c>
       <c r="O19">
-        <v>-3.135330816000003</v>
+        <v>-10.38443878400001</v>
       </c>
       <c r="P19">
-        <v>-6.662577984000006</v>
+        <v>-22.06693241600001</v>
       </c>
       <c r="Q19">
-        <v>-6.595577984000006</v>
+        <v>-21.99993241600001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08519756377686352</v>
+        <v>0.08616986506963327</v>
       </c>
       <c r="T19">
-        <v>0.5134823285231797</v>
+        <v>0.5261546738150147</v>
       </c>
       <c r="U19">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.2579522179502142</v>
+        <v>0.1781057866081658</v>
       </c>
       <c r="W19">
-        <v>0.1089326144049085</v>
+        <v>0.1650363580490803</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y19">
-        <v>0.8061006810944195</v>
+        <v>0.5565805831505182</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1003658338059337</v>
+        <v>0.1019158338059337</v>
       </c>
       <c r="C20">
-        <v>913.1243995449736</v>
+        <v>858.5847052265822</v>
       </c>
       <c r="D20">
-        <v>1241.488399544974</v>
+        <v>1207.196705226582</v>
       </c>
       <c r="E20">
-        <v>-109.736</v>
+        <v>-89.488</v>
       </c>
       <c r="F20">
-        <v>364.464</v>
+        <v>384.712</v>
       </c>
       <c r="G20">
         <v>36.1</v>
@@ -3049,37 +3049,37 @@
         <v>40.733</v>
       </c>
       <c r="M20">
-        <v>73.1843712</v>
+        <v>77.25016960000001</v>
       </c>
       <c r="N20">
-        <v>-32.4513712</v>
+        <v>-36.51716960000001</v>
       </c>
       <c r="O20">
-        <v>-10.384438784</v>
+        <v>-11.685494272</v>
       </c>
       <c r="P20">
-        <v>-22.066932416</v>
+        <v>-24.83167532800001</v>
       </c>
       <c r="Q20">
-        <v>-21.999932416</v>
+        <v>-24.76467532800001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08616986506963327</v>
+        <v>0.08666825846555468</v>
       </c>
       <c r="T20">
-        <v>0.5261546738150147</v>
+        <v>0.5326504105287804</v>
       </c>
       <c r="U20">
         <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.1781057866081659</v>
+        <v>0.168731797839315</v>
       </c>
       <c r="W20">
-        <v>0.1650363580490803</v>
+        <v>0.1669186549938655</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.5565805831505183</v>
+        <v>0.5272868682478594</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1019158338059337</v>
+        <v>0.1034658338059337</v>
       </c>
       <c r="C21">
-        <v>858.5847052265822</v>
+        <v>805.8884638745485</v>
       </c>
       <c r="D21">
-        <v>1207.196705226582</v>
+        <v>1174.748463874549</v>
       </c>
       <c r="E21">
-        <v>-89.488</v>
+        <v>-69.23999999999995</v>
       </c>
       <c r="F21">
-        <v>384.712</v>
+        <v>404.96</v>
       </c>
       <c r="G21">
         <v>36.1</v>
@@ -3131,37 +3131,37 @@
         <v>40.733</v>
       </c>
       <c r="M21">
-        <v>77.25016960000001</v>
+        <v>81.31596800000001</v>
       </c>
       <c r="N21">
-        <v>-36.51716960000001</v>
+        <v>-40.58296800000002</v>
       </c>
       <c r="O21">
-        <v>-11.685494272</v>
+        <v>-12.98654976</v>
       </c>
       <c r="P21">
-        <v>-24.83167532800001</v>
+        <v>-27.59641824000001</v>
       </c>
       <c r="Q21">
-        <v>-24.76467532800001</v>
+        <v>-27.52941824000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08666825846555468</v>
+        <v>0.0871791116963741</v>
       </c>
       <c r="T21">
-        <v>0.5326504105287804</v>
+        <v>0.53930854066039</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.168731797839315</v>
+        <v>0.1602952079473492</v>
       </c>
       <c r="W21">
-        <v>0.1669186549938655</v>
+        <v>0.1686127222441723</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.5272868682478594</v>
+        <v>0.5009225248354664</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1034658338059337</v>
+        <v>0.1125285748362946</v>
       </c>
       <c r="C22">
-        <v>805.8884638745485</v>
+        <v>626.092007609325</v>
       </c>
       <c r="D22">
-        <v>1174.748463874549</v>
+        <v>1015.200007609325</v>
       </c>
       <c r="E22">
-        <v>-69.23999999999995</v>
+        <v>-48.99199999999996</v>
       </c>
       <c r="F22">
-        <v>404.96</v>
+        <v>425.208</v>
       </c>
       <c r="G22">
         <v>36.1</v>
@@ -3213,45 +3213,45 @@
         <v>40.733</v>
       </c>
       <c r="M22">
-        <v>81.31596800000001</v>
+        <v>100.2640464</v>
       </c>
       <c r="N22">
-        <v>-40.58296800000002</v>
+        <v>-59.53104640000002</v>
       </c>
       <c r="O22">
-        <v>-12.98654976</v>
+        <v>-19.04993484800001</v>
       </c>
       <c r="P22">
-        <v>-27.59641824000001</v>
+        <v>-40.48111155200001</v>
       </c>
       <c r="Q22">
-        <v>-27.52941824000001</v>
+        <v>-40.41411155200001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0871791116963741</v>
+        <v>0.08790889922463305</v>
       </c>
       <c r="T22">
-        <v>0.53930854066039</v>
+        <v>0.5488201186214021</v>
       </c>
       <c r="U22">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.1602952079473492</v>
+        <v>0.1300023335184286</v>
       </c>
       <c r="W22">
-        <v>0.1686127222441723</v>
+        <v>0.2051454497563545</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y22">
-        <v>0.5009225248354664</v>
+        <v>0.4062572922450893</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1125285748362946</v>
+        <v>0.1144285748362946</v>
       </c>
       <c r="C23">
-        <v>626.0920076093254</v>
+        <v>577.737930526145</v>
       </c>
       <c r="D23">
-        <v>1015.200007609325</v>
+        <v>987.093930526145</v>
       </c>
       <c r="E23">
-        <v>-48.99200000000002</v>
+        <v>-28.74399999999997</v>
       </c>
       <c r="F23">
-        <v>425.208</v>
+        <v>445.456</v>
       </c>
       <c r="G23">
         <v>36.1</v>
@@ -3295,37 +3295,37 @@
         <v>40.733</v>
       </c>
       <c r="M23">
-        <v>100.2640464</v>
+        <v>105.0385248</v>
       </c>
       <c r="N23">
-        <v>-59.5310464</v>
+        <v>-64.3055248</v>
       </c>
       <c r="O23">
-        <v>-19.049934848</v>
+        <v>-20.577767936</v>
       </c>
       <c r="P23">
-        <v>-40.481111552</v>
+        <v>-43.727756864</v>
       </c>
       <c r="Q23">
-        <v>-40.414111552</v>
+        <v>-43.660756864</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08790889922463305</v>
+        <v>0.08844875690700013</v>
       </c>
       <c r="T23">
-        <v>0.5488201186214021</v>
+        <v>0.5558562739883431</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.1300023335184286</v>
+        <v>0.1240931365403182</v>
       </c>
       <c r="W23">
-        <v>0.2051454497563545</v>
+        <v>0.206538838403793</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.4062572922450893</v>
+        <v>0.3877910516884944</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1144285748362946</v>
+        <v>0.1163285748362946</v>
       </c>
       <c r="C24">
-        <v>577.737930526145</v>
+        <v>530.8981771502554</v>
       </c>
       <c r="D24">
-        <v>987.093930526145</v>
+        <v>960.5021771502554</v>
       </c>
       <c r="E24">
-        <v>-28.74399999999997</v>
+        <v>-8.495999999999981</v>
       </c>
       <c r="F24">
-        <v>445.456</v>
+        <v>465.704</v>
       </c>
       <c r="G24">
         <v>36.1</v>
@@ -3377,37 +3377,37 @@
         <v>40.733</v>
       </c>
       <c r="M24">
-        <v>105.0385248</v>
+        <v>109.8130032</v>
       </c>
       <c r="N24">
-        <v>-64.3055248</v>
+        <v>-69.08000320000002</v>
       </c>
       <c r="O24">
-        <v>-20.577767936</v>
+        <v>-22.10560102400001</v>
       </c>
       <c r="P24">
-        <v>-43.727756864</v>
+        <v>-46.97440217600001</v>
       </c>
       <c r="Q24">
-        <v>-43.660756864</v>
+        <v>-46.90740217600001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08844875690700013</v>
+        <v>0.08900263686683131</v>
       </c>
       <c r="T24">
-        <v>0.5558562739883431</v>
+        <v>0.5630751866375424</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.1240931365403182</v>
+        <v>0.1186977827776957</v>
       </c>
       <c r="W24">
-        <v>0.206538838403793</v>
+        <v>0.2078110628210194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3877910516884944</v>
+        <v>0.3709305711802988</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1163285748362946</v>
+        <v>0.1182285748362946</v>
       </c>
       <c r="C25">
-        <v>530.8981771502554</v>
+        <v>485.4535728996501</v>
       </c>
       <c r="D25">
-        <v>960.5021771502554</v>
+        <v>935.3055728996501</v>
       </c>
       <c r="E25">
-        <v>-8.495999999999981</v>
+        <v>11.75200000000007</v>
       </c>
       <c r="F25">
-        <v>465.704</v>
+        <v>485.9520000000001</v>
       </c>
       <c r="G25">
         <v>36.1</v>
@@ -3459,37 +3459,37 @@
         <v>40.733</v>
       </c>
       <c r="M25">
-        <v>109.8130032</v>
+        <v>114.5874816</v>
       </c>
       <c r="N25">
-        <v>-69.08000320000002</v>
+        <v>-73.85448160000001</v>
       </c>
       <c r="O25">
-        <v>-22.10560102400001</v>
+        <v>-23.633434112</v>
       </c>
       <c r="P25">
-        <v>-46.97440217600001</v>
+        <v>-50.22104748800001</v>
       </c>
       <c r="Q25">
-        <v>-46.90740217600001</v>
+        <v>-50.15404748800001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08900263686683131</v>
+        <v>0.0895710926150791</v>
       </c>
       <c r="T25">
-        <v>0.5630751866375424</v>
+        <v>0.570484070672247</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.1186977827776957</v>
+        <v>0.113752041828625</v>
       </c>
       <c r="W25">
-        <v>0.2078110628210194</v>
+        <v>0.2089772685368102</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3709305711802988</v>
+        <v>0.3554751307144531</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1182285748362946</v>
+        <v>0.1201285748362946</v>
       </c>
       <c r="C26">
-        <v>485.4535728996501</v>
+        <v>441.2971286381627</v>
       </c>
       <c r="D26">
-        <v>935.3055728996501</v>
+        <v>911.3971286381627</v>
       </c>
       <c r="E26">
-        <v>11.75200000000001</v>
+        <v>32</v>
       </c>
       <c r="F26">
-        <v>485.952</v>
+        <v>506.2</v>
       </c>
       <c r="G26">
         <v>36.1</v>
@@ -3541,37 +3541,37 @@
         <v>40.733</v>
       </c>
       <c r="M26">
-        <v>114.5874816</v>
+        <v>119.36196</v>
       </c>
       <c r="N26">
-        <v>-73.85448160000001</v>
+        <v>-78.62896000000001</v>
       </c>
       <c r="O26">
-        <v>-23.633434112</v>
+        <v>-25.1612672</v>
       </c>
       <c r="P26">
-        <v>-50.22104748800001</v>
+        <v>-53.46769280000001</v>
       </c>
       <c r="Q26">
-        <v>-50.15404748800001</v>
+        <v>-53.40069280000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08957109261507909</v>
+        <v>0.09015470718328014</v>
       </c>
       <c r="T26">
-        <v>0.5704840706722469</v>
+        <v>0.5780905249478769</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.113752041828625</v>
+        <v>0.10920196015548</v>
       </c>
       <c r="W26">
-        <v>0.2089772685368102</v>
+        <v>0.2100501777953378</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3554751307144531</v>
+        <v>0.341256125485875</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1201285748362946</v>
+        <v>0.1220285748362946</v>
       </c>
       <c r="C27">
-        <v>441.2971286381627</v>
+        <v>398.3325220620682</v>
       </c>
       <c r="D27">
-        <v>911.3971286381627</v>
+        <v>888.6805220620681</v>
       </c>
       <c r="E27">
-        <v>32</v>
+        <v>52.24799999999999</v>
       </c>
       <c r="F27">
-        <v>506.2</v>
+        <v>526.448</v>
       </c>
       <c r="G27">
         <v>36.1</v>
@@ -3623,37 +3623,37 @@
         <v>40.733</v>
       </c>
       <c r="M27">
-        <v>119.36196</v>
+        <v>124.1364384</v>
       </c>
       <c r="N27">
-        <v>-78.62896000000001</v>
+        <v>-83.4034384</v>
       </c>
       <c r="O27">
-        <v>-25.1612672</v>
+        <v>-26.689100288</v>
       </c>
       <c r="P27">
-        <v>-53.46769280000001</v>
+        <v>-56.714338112</v>
       </c>
       <c r="Q27">
-        <v>-53.40069280000001</v>
+        <v>-56.647338112</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09015470718328014</v>
+        <v>0.09075409511818934</v>
       </c>
       <c r="T27">
-        <v>0.5780905249478769</v>
+        <v>0.5859025590687942</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.10920196015548</v>
+        <v>0.1050018847648846</v>
       </c>
       <c r="W27">
-        <v>0.2100501777953378</v>
+        <v>0.2110405555724402</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.341256125485875</v>
+        <v>0.3281308898902645</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1220285748362946</v>
+        <v>0.1239285748362946</v>
       </c>
       <c r="C28">
-        <v>398.3325220620682</v>
+        <v>356.4728006726034</v>
       </c>
       <c r="D28">
-        <v>888.6805220620681</v>
+        <v>867.0688006726034</v>
       </c>
       <c r="E28">
-        <v>52.24799999999999</v>
+        <v>72.49600000000004</v>
       </c>
       <c r="F28">
-        <v>526.448</v>
+        <v>546.696</v>
       </c>
       <c r="G28">
         <v>36.1</v>
@@ -3705,37 +3705,37 @@
         <v>40.733</v>
       </c>
       <c r="M28">
-        <v>124.1364384</v>
+        <v>128.9109168</v>
       </c>
       <c r="N28">
-        <v>-83.4034384</v>
+        <v>-88.17791680000002</v>
       </c>
       <c r="O28">
-        <v>-26.689100288</v>
+        <v>-28.21693337600001</v>
       </c>
       <c r="P28">
-        <v>-56.714338112</v>
+        <v>-59.96098342400001</v>
       </c>
       <c r="Q28">
-        <v>-56.647338112</v>
+        <v>-59.89398342400001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09075409511818934</v>
+        <v>0.09136990464035633</v>
       </c>
       <c r="T28">
-        <v>0.5859025590687942</v>
+        <v>0.5939286215217914</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1050018847648846</v>
+        <v>0.1011129260698889</v>
       </c>
       <c r="W28">
-        <v>0.2110405555724402</v>
+        <v>0.2119575720327202</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3281308898902645</v>
+        <v>0.3159778939684028</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1239285748362946</v>
+        <v>0.1258285748362946</v>
       </c>
       <c r="C29">
-        <v>356.4728006726034</v>
+        <v>315.6392695089172</v>
       </c>
       <c r="D29">
-        <v>867.0688006726034</v>
+        <v>846.4832695089173</v>
       </c>
       <c r="E29">
-        <v>72.49600000000004</v>
+        <v>92.74400000000009</v>
       </c>
       <c r="F29">
-        <v>546.696</v>
+        <v>566.9440000000001</v>
       </c>
       <c r="G29">
         <v>36.1</v>
@@ -3787,37 +3787,37 @@
         <v>40.733</v>
       </c>
       <c r="M29">
-        <v>128.9109168</v>
+        <v>133.6853952</v>
       </c>
       <c r="N29">
-        <v>-88.17791680000002</v>
+        <v>-92.95239520000001</v>
       </c>
       <c r="O29">
-        <v>-28.21693337600001</v>
+        <v>-29.744766464</v>
       </c>
       <c r="P29">
-        <v>-59.96098342400001</v>
+        <v>-63.207628736</v>
       </c>
       <c r="Q29">
-        <v>-59.89398342400001</v>
+        <v>-63.140628736</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09136990464035633</v>
+        <v>0.09200281998258349</v>
       </c>
       <c r="T29">
-        <v>0.5939286215217914</v>
+        <v>0.6021776301540385</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1011129260698889</v>
+        <v>0.09750175013882142</v>
       </c>
       <c r="W29">
-        <v>0.2119575720327202</v>
+        <v>0.2128090873172659</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3159778939684028</v>
+        <v>0.3046929691838171</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1258285748362946</v>
+        <v>0.1277285748362946</v>
       </c>
       <c r="C30">
-        <v>315.6392695089172</v>
+        <v>275.7605336480699</v>
       </c>
       <c r="D30">
-        <v>846.4832695089173</v>
+        <v>826.8525336480699</v>
       </c>
       <c r="E30">
-        <v>92.74400000000009</v>
+        <v>112.992</v>
       </c>
       <c r="F30">
-        <v>566.9440000000001</v>
+        <v>587.192</v>
       </c>
       <c r="G30">
         <v>36.1</v>
@@ -3869,37 +3869,37 @@
         <v>40.733</v>
       </c>
       <c r="M30">
-        <v>133.6853952</v>
+        <v>138.4598736</v>
       </c>
       <c r="N30">
-        <v>-92.95239520000001</v>
+        <v>-97.7268736</v>
       </c>
       <c r="O30">
-        <v>-29.744766464</v>
+        <v>-31.272599552</v>
       </c>
       <c r="P30">
-        <v>-63.207628736</v>
+        <v>-66.454274048</v>
       </c>
       <c r="Q30">
-        <v>-63.140628736</v>
+        <v>-66.38727404800001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09200281998258349</v>
+        <v>0.09265356392600016</v>
       </c>
       <c r="T30">
-        <v>0.6021776301540385</v>
+        <v>0.6106590052266306</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.09750175013882142</v>
+        <v>0.09413962082368967</v>
       </c>
       <c r="W30">
-        <v>0.2128090873172659</v>
+        <v>0.213601877409774</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3046929691838171</v>
+        <v>0.2941863150740303</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1277285748362946</v>
+        <v>0.1296285748362946</v>
       </c>
       <c r="C31">
-        <v>275.76053364807</v>
+        <v>236.7716709172015</v>
       </c>
       <c r="D31">
-        <v>826.8525336480699</v>
+        <v>808.1116709172014</v>
       </c>
       <c r="E31">
-        <v>112.9919999999999</v>
+        <v>133.24</v>
       </c>
       <c r="F31">
-        <v>587.1919999999999</v>
+        <v>607.4399999999999</v>
       </c>
       <c r="G31">
         <v>36.1</v>
@@ -3951,37 +3951,37 @@
         <v>40.733</v>
       </c>
       <c r="M31">
-        <v>138.4598736</v>
+        <v>143.234352</v>
       </c>
       <c r="N31">
-        <v>-97.72687359999998</v>
+        <v>-102.501352</v>
       </c>
       <c r="O31">
-        <v>-31.27259955199999</v>
+        <v>-32.80043264</v>
       </c>
       <c r="P31">
-        <v>-66.45427404799999</v>
+        <v>-69.70091936</v>
       </c>
       <c r="Q31">
-        <v>-66.38727404799999</v>
+        <v>-69.63391936000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09265356392600016</v>
+        <v>0.09332290055351444</v>
       </c>
       <c r="T31">
-        <v>0.6106590052266306</v>
+        <v>0.6193827053012967</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.09413962082368968</v>
+        <v>0.09100163346290001</v>
       </c>
       <c r="W31">
-        <v>0.213601877409774</v>
+        <v>0.2143418148294482</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2941863150740303</v>
+        <v>0.2843801045715626</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1296285748362946</v>
+        <v>0.1315285748362946</v>
       </c>
       <c r="C32">
-        <v>236.7716709172015</v>
+        <v>198.6135146166368</v>
       </c>
       <c r="D32">
-        <v>808.1116709172014</v>
+        <v>790.2015146166368</v>
       </c>
       <c r="E32">
-        <v>133.24</v>
+        <v>153.488</v>
       </c>
       <c r="F32">
-        <v>607.4399999999999</v>
+        <v>627.688</v>
       </c>
       <c r="G32">
         <v>36.1</v>
@@ -4033,37 +4033,37 @@
         <v>40.733</v>
       </c>
       <c r="M32">
-        <v>143.234352</v>
+        <v>148.0088304</v>
       </c>
       <c r="N32">
-        <v>-102.501352</v>
+        <v>-107.2758304</v>
       </c>
       <c r="O32">
-        <v>-32.80043264</v>
+        <v>-34.328265728</v>
       </c>
       <c r="P32">
-        <v>-69.70091936</v>
+        <v>-72.947564672</v>
       </c>
       <c r="Q32">
-        <v>-69.63391936000001</v>
+        <v>-72.88056467200001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09332290055351444</v>
+        <v>0.09401163824269582</v>
       </c>
       <c r="T32">
-        <v>0.6193827053012967</v>
+        <v>0.6283592662476922</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.09100163346290001</v>
+        <v>0.08806609689958066</v>
       </c>
       <c r="W32">
-        <v>0.2143418148294482</v>
+        <v>0.2150340143510789</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2843801045715626</v>
+        <v>0.2752065528111896</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1315285748362946</v>
+        <v>0.1334285748362946</v>
       </c>
       <c r="C33">
-        <v>198.6135146166368</v>
+        <v>161.2320295568096</v>
       </c>
       <c r="D33">
-        <v>790.2015146166368</v>
+        <v>773.0680295568096</v>
       </c>
       <c r="E33">
-        <v>153.488</v>
+        <v>173.736</v>
       </c>
       <c r="F33">
-        <v>627.688</v>
+        <v>647.936</v>
       </c>
       <c r="G33">
         <v>36.1</v>
@@ -4115,37 +4115,37 @@
         <v>40.733</v>
       </c>
       <c r="M33">
-        <v>148.0088304</v>
+        <v>152.7833088</v>
       </c>
       <c r="N33">
-        <v>-107.2758304</v>
+        <v>-112.0503088</v>
       </c>
       <c r="O33">
-        <v>-34.328265728</v>
+        <v>-35.85609881600001</v>
       </c>
       <c r="P33">
-        <v>-72.947564672</v>
+        <v>-76.194209984</v>
       </c>
       <c r="Q33">
-        <v>-72.88056467200001</v>
+        <v>-76.127209984</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09401163824269582</v>
+        <v>0.09472063292273547</v>
       </c>
       <c r="T33">
-        <v>0.6283592662476922</v>
+        <v>0.6375998436925113</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08806609689958066</v>
+        <v>0.08531403137146874</v>
       </c>
       <c r="W33">
-        <v>0.2150340143510789</v>
+        <v>0.2156829514026077</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2752065528111896</v>
+        <v>0.2666063480358399</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1334285748362946</v>
+        <v>0.1353285748362946</v>
       </c>
       <c r="C34">
-        <v>161.2320295568096</v>
+        <v>124.5777675466778</v>
       </c>
       <c r="D34">
-        <v>773.0680295568096</v>
+        <v>756.6617675466778</v>
       </c>
       <c r="E34">
-        <v>173.736</v>
+        <v>193.984</v>
       </c>
       <c r="F34">
-        <v>647.936</v>
+        <v>668.184</v>
       </c>
       <c r="G34">
         <v>36.1</v>
@@ -4197,37 +4197,37 @@
         <v>40.733</v>
       </c>
       <c r="M34">
-        <v>152.7833088</v>
+        <v>157.5577872</v>
       </c>
       <c r="N34">
-        <v>-112.0503088</v>
+        <v>-116.8247872</v>
       </c>
       <c r="O34">
-        <v>-35.85609881600001</v>
+        <v>-37.383931904</v>
       </c>
       <c r="P34">
-        <v>-76.194209984</v>
+        <v>-79.440855296</v>
       </c>
       <c r="Q34">
-        <v>-76.127209984</v>
+        <v>-79.373855296</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09472063292273547</v>
+        <v>0.09545079162307479</v>
       </c>
       <c r="T34">
-        <v>0.6375998436925113</v>
+        <v>0.6471162592700115</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08531403137146874</v>
+        <v>0.08272875769354546</v>
       </c>
       <c r="W34">
-        <v>0.2156829514026077</v>
+        <v>0.216292558935862</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2666063480358399</v>
+        <v>0.2585273677923297</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1353285748362946</v>
+        <v>0.1372285748362946</v>
       </c>
       <c r="C35">
-        <v>124.5777675466778</v>
+        <v>88.60539077592694</v>
       </c>
       <c r="D35">
-        <v>756.6617675466778</v>
+        <v>740.9373907759269</v>
       </c>
       <c r="E35">
-        <v>193.984</v>
+        <v>214.232</v>
       </c>
       <c r="F35">
-        <v>668.184</v>
+        <v>688.432</v>
       </c>
       <c r="G35">
         <v>36.1</v>
@@ -4279,37 +4279,37 @@
         <v>40.733</v>
       </c>
       <c r="M35">
-        <v>157.5577872</v>
+        <v>162.3322656</v>
       </c>
       <c r="N35">
-        <v>-116.8247872</v>
+        <v>-121.5992656</v>
       </c>
       <c r="O35">
-        <v>-37.383931904</v>
+        <v>-38.911764992</v>
       </c>
       <c r="P35">
-        <v>-79.440855296</v>
+        <v>-82.68750060799999</v>
       </c>
       <c r="Q35">
-        <v>-79.373855296</v>
+        <v>-82.620500608</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09545079162307479</v>
+        <v>0.09620307634463654</v>
       </c>
       <c r="T35">
-        <v>0.6471162592700115</v>
+        <v>0.6569210510771329</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.08272875769354546</v>
+        <v>0.08029555893785295</v>
       </c>
       <c r="W35">
-        <v>0.216292558935862</v>
+        <v>0.2168663072024543</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2585273677923297</v>
+        <v>0.2509236216807905</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1372285748362946</v>
+        <v>0.1391285748362946</v>
       </c>
       <c r="C36">
-        <v>88.60539077592694</v>
+        <v>53.27325341559958</v>
       </c>
       <c r="D36">
-        <v>740.9373907759269</v>
+        <v>725.8532534155996</v>
       </c>
       <c r="E36">
-        <v>214.232</v>
+        <v>234.4800000000001</v>
       </c>
       <c r="F36">
-        <v>688.432</v>
+        <v>708.6800000000001</v>
       </c>
       <c r="G36">
         <v>36.1</v>
@@ -4361,37 +4361,37 @@
         <v>40.733</v>
       </c>
       <c r="M36">
-        <v>162.3322656</v>
+        <v>167.106744</v>
       </c>
       <c r="N36">
-        <v>-121.5992656</v>
+        <v>-126.373744</v>
       </c>
       <c r="O36">
-        <v>-38.911764992</v>
+        <v>-40.43959808</v>
       </c>
       <c r="P36">
-        <v>-82.68750060799999</v>
+        <v>-85.93414592000002</v>
       </c>
       <c r="Q36">
-        <v>-82.620500608</v>
+        <v>-85.86714592000003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09620307634463654</v>
+        <v>0.09697850828840017</v>
       </c>
       <c r="T36">
-        <v>0.6569210510771329</v>
+        <v>0.6670275287860118</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.08029555893785295</v>
+        <v>0.07800140011105715</v>
       </c>
       <c r="W36">
-        <v>0.2168663072024543</v>
+        <v>0.2174072698538127</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2509236216807905</v>
+        <v>0.2437543753470536</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1391285748362946</v>
+        <v>0.1410285748362946</v>
       </c>
       <c r="C37">
-        <v>53.27325341559958</v>
+        <v>18.54303330613686</v>
       </c>
       <c r="D37">
-        <v>725.8532534155996</v>
+        <v>711.371033306137</v>
       </c>
       <c r="E37">
-        <v>234.4800000000001</v>
+        <v>254.7280000000001</v>
       </c>
       <c r="F37">
-        <v>708.6800000000001</v>
+        <v>728.9280000000001</v>
       </c>
       <c r="G37">
         <v>36.1</v>
@@ -4443,37 +4443,37 @@
         <v>40.733</v>
       </c>
       <c r="M37">
-        <v>167.106744</v>
+        <v>171.8812224</v>
       </c>
       <c r="N37">
-        <v>-126.373744</v>
+        <v>-131.1482224</v>
       </c>
       <c r="O37">
-        <v>-40.43959808</v>
+        <v>-41.96743116800001</v>
       </c>
       <c r="P37">
-        <v>-85.93414592000002</v>
+        <v>-89.18079123200002</v>
       </c>
       <c r="Q37">
-        <v>-85.86714592000003</v>
+        <v>-89.11379123200003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09697850828840017</v>
+        <v>0.09777817248040643</v>
       </c>
       <c r="T37">
-        <v>0.6670275287860118</v>
+        <v>0.6774498339232934</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07800140011105715</v>
+        <v>0.07583469455241666</v>
       </c>
       <c r="W37">
-        <v>0.2174072698538127</v>
+        <v>0.2179181790245402</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2437543753470536</v>
+        <v>0.2369834204763021</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1410285748362946</v>
+        <v>0.1429285748362946</v>
       </c>
       <c r="C38">
-        <v>18.5430333061372</v>
+        <v>-15.62059312573126</v>
       </c>
       <c r="D38">
-        <v>711.3710333061372</v>
+        <v>697.4554068742686</v>
       </c>
       <c r="E38">
-        <v>254.728</v>
+        <v>274.9759999999999</v>
       </c>
       <c r="F38">
-        <v>728.928</v>
+        <v>749.1759999999999</v>
       </c>
       <c r="G38">
         <v>36.1</v>
@@ -4525,37 +4525,37 @@
         <v>40.733</v>
       </c>
       <c r="M38">
-        <v>171.8812224</v>
+        <v>176.6557008</v>
       </c>
       <c r="N38">
-        <v>-131.1482224</v>
+        <v>-135.9227008</v>
       </c>
       <c r="O38">
-        <v>-41.967431168</v>
+        <v>-43.49526425599999</v>
       </c>
       <c r="P38">
-        <v>-89.180791232</v>
+        <v>-92.42743654399999</v>
       </c>
       <c r="Q38">
-        <v>-89.11379123200001</v>
+        <v>-92.360436544</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09777817248040643</v>
+        <v>0.09860322283723827</v>
       </c>
       <c r="T38">
-        <v>0.6774498339232934</v>
+        <v>0.6882030058903297</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07583469455241666</v>
+        <v>0.07378510821316218</v>
       </c>
       <c r="W38">
-        <v>0.2179181790245402</v>
+        <v>0.2184014714833364</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2369834204763022</v>
+        <v>0.2305784631661318</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1429285748362946</v>
+        <v>0.1448285748362945</v>
       </c>
       <c r="C39">
-        <v>-15.62059312573126</v>
+        <v>-49.25023852708898</v>
       </c>
       <c r="D39">
-        <v>697.4554068742686</v>
+        <v>684.073761472911</v>
       </c>
       <c r="E39">
-        <v>274.9759999999999</v>
+        <v>295.224</v>
       </c>
       <c r="F39">
-        <v>749.1759999999999</v>
+        <v>769.424</v>
       </c>
       <c r="G39">
         <v>36.1</v>
@@ -4607,37 +4607,37 @@
         <v>40.733</v>
       </c>
       <c r="M39">
-        <v>176.6557008</v>
+        <v>181.4301792</v>
       </c>
       <c r="N39">
-        <v>-135.9227008</v>
+        <v>-140.6971792</v>
       </c>
       <c r="O39">
-        <v>-43.49526425599999</v>
+        <v>-45.023097344</v>
       </c>
       <c r="P39">
-        <v>-92.42743654399999</v>
+        <v>-95.67408185599999</v>
       </c>
       <c r="Q39">
-        <v>-92.360436544</v>
+        <v>-95.60708185599999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09860322283723827</v>
+        <v>0.09945488772170985</v>
       </c>
       <c r="T39">
-        <v>0.6882030058903297</v>
+        <v>0.6993030543724318</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.07378510821316218</v>
+        <v>0.07184339483913159</v>
       </c>
       <c r="W39">
-        <v>0.2184014714833364</v>
+        <v>0.2188593274969328</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2305784631661318</v>
+        <v>0.2245106088722862</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1448285748362945</v>
+        <v>0.1467285748362946</v>
       </c>
       <c r="C40">
-        <v>-49.25023852708898</v>
+        <v>-82.37605978738839</v>
       </c>
       <c r="D40">
-        <v>684.073761472911</v>
+        <v>671.1959402126116</v>
       </c>
       <c r="E40">
-        <v>295.224</v>
+        <v>315.472</v>
       </c>
       <c r="F40">
-        <v>769.424</v>
+        <v>789.672</v>
       </c>
       <c r="G40">
         <v>36.1</v>
@@ -4689,37 +4689,37 @@
         <v>40.733</v>
       </c>
       <c r="M40">
-        <v>181.4301792</v>
+        <v>186.2046576</v>
       </c>
       <c r="N40">
-        <v>-140.6971792</v>
+        <v>-145.4716576</v>
       </c>
       <c r="O40">
-        <v>-45.023097344</v>
+        <v>-46.55093043200001</v>
       </c>
       <c r="P40">
-        <v>-95.67408185599999</v>
+        <v>-98.92072716800001</v>
       </c>
       <c r="Q40">
-        <v>-95.60708185599999</v>
+        <v>-98.85372716800002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09945488772170985</v>
+        <v>0.1003344760450166</v>
       </c>
       <c r="T40">
-        <v>0.6993030543724318</v>
+        <v>0.7107670388703404</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07184339483913159</v>
+        <v>0.07000125650992307</v>
       </c>
       <c r="W40">
-        <v>0.2188593274969328</v>
+        <v>0.2192937037149602</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2245106088722862</v>
+        <v>0.2187539265935097</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1467285748362946</v>
+        <v>0.1486285748362946</v>
       </c>
       <c r="C41">
-        <v>-82.37605978738839</v>
+        <v>-115.0259849179686</v>
       </c>
       <c r="D41">
-        <v>671.1959402126116</v>
+        <v>658.7940150820315</v>
       </c>
       <c r="E41">
-        <v>315.472</v>
+        <v>335.7200000000001</v>
       </c>
       <c r="F41">
-        <v>789.672</v>
+        <v>809.9200000000001</v>
       </c>
       <c r="G41">
         <v>36.1</v>
@@ -4771,37 +4771,37 @@
         <v>40.733</v>
       </c>
       <c r="M41">
-        <v>186.2046576</v>
+        <v>190.979136</v>
       </c>
       <c r="N41">
-        <v>-145.4716576</v>
+        <v>-150.246136</v>
       </c>
       <c r="O41">
-        <v>-46.55093043200001</v>
+        <v>-48.07876352</v>
       </c>
       <c r="P41">
-        <v>-98.92072716800001</v>
+        <v>-102.16737248</v>
       </c>
       <c r="Q41">
-        <v>-98.85372716800002</v>
+        <v>-102.10037248</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1003344760450166</v>
+        <v>0.1012433839791002</v>
       </c>
       <c r="T41">
-        <v>0.7107670388703404</v>
+        <v>0.7226131561848462</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07000125650992307</v>
+        <v>0.068251225097175</v>
       </c>
       <c r="W41">
-        <v>0.2192937037149602</v>
+        <v>0.2197063611220862</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2187539265935097</v>
+        <v>0.2132850784286719</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1486285748362946</v>
+        <v>0.1505285748362946</v>
       </c>
       <c r="C42">
-        <v>-115.0259849179686</v>
+        <v>-147.2259152350996</v>
       </c>
       <c r="D42">
-        <v>658.7940150820315</v>
+        <v>646.8420847649004</v>
       </c>
       <c r="E42">
-        <v>335.7200000000001</v>
+        <v>355.968</v>
       </c>
       <c r="F42">
-        <v>809.9200000000001</v>
+        <v>830.168</v>
       </c>
       <c r="G42">
         <v>36.1</v>
@@ -4853,37 +4853,37 @@
         <v>40.733</v>
       </c>
       <c r="M42">
-        <v>190.979136</v>
+        <v>195.7536144</v>
       </c>
       <c r="N42">
-        <v>-150.246136</v>
+        <v>-155.0206144</v>
       </c>
       <c r="O42">
-        <v>-48.07876352</v>
+        <v>-49.606596608</v>
       </c>
       <c r="P42">
-        <v>-102.16737248</v>
+        <v>-105.414017792</v>
       </c>
       <c r="Q42">
-        <v>-102.10037248</v>
+        <v>-105.347017792</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1012433839791002</v>
+        <v>0.1021831023516273</v>
       </c>
       <c r="T42">
-        <v>0.7226131561848462</v>
+        <v>0.7348608367981486</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.068251225097175</v>
+        <v>0.06658656107041465</v>
       </c>
       <c r="W42">
-        <v>0.2197063611220862</v>
+        <v>0.2200988888995963</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2132850784286719</v>
+        <v>0.2080830033450458</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1505285748362946</v>
+        <v>0.1524285748362946</v>
       </c>
       <c r="C43">
-        <v>-147.2259152350996</v>
+        <v>-178.999905926996</v>
       </c>
       <c r="D43">
-        <v>646.8420847649004</v>
+        <v>635.316094073004</v>
       </c>
       <c r="E43">
-        <v>355.968</v>
+        <v>376.2160000000001</v>
       </c>
       <c r="F43">
-        <v>830.168</v>
+        <v>850.4160000000001</v>
       </c>
       <c r="G43">
         <v>36.1</v>
@@ -4935,37 +4935,37 @@
         <v>40.733</v>
       </c>
       <c r="M43">
-        <v>195.7536144</v>
+        <v>200.5280928</v>
       </c>
       <c r="N43">
-        <v>-155.0206144</v>
+        <v>-159.7950928</v>
       </c>
       <c r="O43">
-        <v>-49.606596608</v>
+        <v>-51.13442969600001</v>
       </c>
       <c r="P43">
-        <v>-105.414017792</v>
+        <v>-108.660663104</v>
       </c>
       <c r="Q43">
-        <v>-105.347017792</v>
+        <v>-108.593663104</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1021831023516273</v>
+        <v>0.1031552248059657</v>
       </c>
       <c r="T43">
-        <v>0.7348608367981486</v>
+        <v>0.7475308512257028</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06658656107041465</v>
+        <v>0.06500116675921429</v>
       </c>
       <c r="W43">
-        <v>0.2200988888995963</v>
+        <v>0.2204727248781773</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2080830033450458</v>
+        <v>0.2031286461225447</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1524285748362946</v>
+        <v>0.1543285748362946</v>
       </c>
       <c r="C44">
-        <v>-178.9999059269959</v>
+        <v>-210.370327653804</v>
       </c>
       <c r="D44">
-        <v>635.316094073004</v>
+        <v>624.193672346196</v>
       </c>
       <c r="E44">
-        <v>376.216</v>
+        <v>396.464</v>
       </c>
       <c r="F44">
-        <v>850.4159999999999</v>
+        <v>870.664</v>
       </c>
       <c r="G44">
         <v>36.1</v>
@@ -5017,37 +5017,37 @@
         <v>40.733</v>
       </c>
       <c r="M44">
-        <v>200.5280928</v>
+        <v>205.3025712</v>
       </c>
       <c r="N44">
-        <v>-159.7950928</v>
+        <v>-164.5695712</v>
       </c>
       <c r="O44">
-        <v>-51.134429696</v>
+        <v>-52.66226278400001</v>
       </c>
       <c r="P44">
-        <v>-108.660663104</v>
+        <v>-111.907308416</v>
       </c>
       <c r="Q44">
-        <v>-108.593663104</v>
+        <v>-111.840308416</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1031552248059657</v>
+        <v>0.1041614568201055</v>
       </c>
       <c r="T44">
-        <v>0.7475308512257028</v>
+        <v>0.7606454275629959</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06500116675921429</v>
+        <v>0.06348951171830233</v>
       </c>
       <c r="W44">
-        <v>0.2204727248781773</v>
+        <v>0.2208291731368243</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2031286461225447</v>
+        <v>0.1984047241196948</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1543285748362946</v>
+        <v>0.1562285748362946</v>
       </c>
       <c r="C45">
-        <v>-210.370327653804</v>
+        <v>-241.3580114649545</v>
       </c>
       <c r="D45">
-        <v>624.193672346196</v>
+        <v>613.4539885350455</v>
       </c>
       <c r="E45">
-        <v>396.464</v>
+        <v>416.712</v>
       </c>
       <c r="F45">
-        <v>870.664</v>
+        <v>890.912</v>
       </c>
       <c r="G45">
         <v>36.1</v>
@@ -5099,37 +5099,37 @@
         <v>40.733</v>
       </c>
       <c r="M45">
-        <v>205.3025712</v>
+        <v>210.0770496</v>
       </c>
       <c r="N45">
-        <v>-164.5695712</v>
+        <v>-169.3440496</v>
       </c>
       <c r="O45">
-        <v>-52.66226278400001</v>
+        <v>-54.190095872</v>
       </c>
       <c r="P45">
-        <v>-111.907308416</v>
+        <v>-115.153953728</v>
       </c>
       <c r="Q45">
-        <v>-111.840308416</v>
+        <v>-115.086953728</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1041614568201055</v>
+        <v>0.1052036256918931</v>
       </c>
       <c r="T45">
-        <v>0.7606454275629959</v>
+        <v>0.7742283816266209</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06348951171830233</v>
+        <v>0.0620465682701591</v>
       </c>
       <c r="W45">
-        <v>0.2208291731368243</v>
+        <v>0.2211694192018965</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1984047241196948</v>
+        <v>0.1938955258442472</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1562285748362946</v>
+        <v>0.1581285748362946</v>
       </c>
       <c r="C46">
-        <v>-241.3580114649545</v>
+        <v>-271.9823790091457</v>
       </c>
       <c r="D46">
-        <v>613.4539885350455</v>
+        <v>603.0776209908543</v>
       </c>
       <c r="E46">
-        <v>416.712</v>
+        <v>436.96</v>
       </c>
       <c r="F46">
-        <v>890.912</v>
+        <v>911.16</v>
       </c>
       <c r="G46">
         <v>36.1</v>
@@ -5181,37 +5181,37 @@
         <v>40.733</v>
       </c>
       <c r="M46">
-        <v>210.0770496</v>
+        <v>214.851528</v>
       </c>
       <c r="N46">
-        <v>-169.3440496</v>
+        <v>-174.118528</v>
       </c>
       <c r="O46">
-        <v>-54.190095872</v>
+        <v>-55.71792896</v>
       </c>
       <c r="P46">
-        <v>-115.153953728</v>
+        <v>-118.40059904</v>
       </c>
       <c r="Q46">
-        <v>-115.086953728</v>
+        <v>-118.33359904</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1052036256918931</v>
+        <v>0.1062836916135638</v>
       </c>
       <c r="T46">
-        <v>0.7742283816266209</v>
+        <v>0.7883052612925594</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0620465682701591</v>
+        <v>0.06066775564193334</v>
       </c>
       <c r="W46">
-        <v>0.2211694192018965</v>
+        <v>0.2214945432196321</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1938955258442472</v>
+        <v>0.1895867363810417</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1581285748362946</v>
+        <v>0.1600285748362946</v>
       </c>
       <c r="C47">
-        <v>-271.9823790091457</v>
+        <v>-302.2615597493833</v>
       </c>
       <c r="D47">
-        <v>603.0776209908543</v>
+        <v>593.0464402506167</v>
       </c>
       <c r="E47">
-        <v>436.96</v>
+        <v>457.208</v>
       </c>
       <c r="F47">
-        <v>911.16</v>
+        <v>931.408</v>
       </c>
       <c r="G47">
         <v>36.1</v>
@@ -5263,37 +5263,37 @@
         <v>40.733</v>
       </c>
       <c r="M47">
-        <v>214.851528</v>
+        <v>219.6260064</v>
       </c>
       <c r="N47">
-        <v>-174.118528</v>
+        <v>-178.8930064</v>
       </c>
       <c r="O47">
-        <v>-55.71792896</v>
+        <v>-57.24576204800001</v>
       </c>
       <c r="P47">
-        <v>-118.40059904</v>
+        <v>-121.647244352</v>
       </c>
       <c r="Q47">
-        <v>-118.33359904</v>
+        <v>-121.580244352</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1062836916135638</v>
+        <v>0.107403759976778</v>
       </c>
       <c r="T47">
-        <v>0.7883052612925594</v>
+        <v>0.8029035068720513</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06066775564193334</v>
+        <v>0.05934889138884783</v>
       </c>
       <c r="W47">
-        <v>0.2214945432196321</v>
+        <v>0.2218055314105097</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1895867363810417</v>
+        <v>0.1854652855901495</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1600285748362946</v>
+        <v>0.1619285748362946</v>
       </c>
       <c r="C48">
-        <v>-302.2615597493833</v>
+        <v>-332.2124966713649</v>
       </c>
       <c r="D48">
-        <v>593.0464402506167</v>
+        <v>583.3435033286352</v>
       </c>
       <c r="E48">
-        <v>457.208</v>
+        <v>477.4560000000001</v>
       </c>
       <c r="F48">
-        <v>931.408</v>
+        <v>951.6560000000001</v>
       </c>
       <c r="G48">
         <v>36.1</v>
@@ -5345,37 +5345,37 @@
         <v>40.733</v>
       </c>
       <c r="M48">
-        <v>219.6260064</v>
+        <v>224.4004848</v>
       </c>
       <c r="N48">
-        <v>-178.8930064</v>
+        <v>-183.6674848</v>
       </c>
       <c r="O48">
-        <v>-57.24576204800001</v>
+        <v>-58.773595136</v>
       </c>
       <c r="P48">
-        <v>-121.647244352</v>
+        <v>-124.893889664</v>
       </c>
       <c r="Q48">
-        <v>-121.580244352</v>
+        <v>-124.826889664</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.107403759976778</v>
+        <v>0.1085660950706795</v>
       </c>
       <c r="T48">
-        <v>0.8029035068720513</v>
+        <v>0.8180526296432221</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05934889138884783</v>
+        <v>0.05808614901887234</v>
       </c>
       <c r="W48">
-        <v>0.2218055314105097</v>
+        <v>0.2221032860613499</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1854652855901495</v>
+        <v>0.1815192156839761</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1619285748362946</v>
+        <v>0.1638285748362946</v>
       </c>
       <c r="C49">
-        <v>-332.2124966713649</v>
+        <v>-361.8510417818322</v>
       </c>
       <c r="D49">
-        <v>583.3435033286352</v>
+        <v>573.9529582181679</v>
       </c>
       <c r="E49">
-        <v>477.4560000000001</v>
+        <v>497.7040000000001</v>
       </c>
       <c r="F49">
-        <v>951.6560000000001</v>
+        <v>971.9040000000001</v>
       </c>
       <c r="G49">
         <v>36.1</v>
@@ -5427,37 +5427,37 @@
         <v>40.733</v>
       </c>
       <c r="M49">
-        <v>224.4004848</v>
+        <v>229.1749632</v>
       </c>
       <c r="N49">
-        <v>-183.6674848</v>
+        <v>-188.4419632</v>
       </c>
       <c r="O49">
-        <v>-58.773595136</v>
+        <v>-60.30142822400001</v>
       </c>
       <c r="P49">
-        <v>-124.893889664</v>
+        <v>-128.140534976</v>
       </c>
       <c r="Q49">
-        <v>-124.826889664</v>
+        <v>-128.073534976</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1085660950706795</v>
+        <v>0.1097731353605002</v>
       </c>
       <c r="T49">
-        <v>0.8180526296432221</v>
+        <v>0.8337844109825148</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05808614901887234</v>
+        <v>0.0568760209143125</v>
       </c>
       <c r="W49">
-        <v>0.2221032860613499</v>
+        <v>0.2223886342684051</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1815192156839761</v>
+        <v>0.1777375653572266</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1638285748362945</v>
+        <v>0.1657285748362946</v>
       </c>
       <c r="C50">
-        <v>-361.8510417818321</v>
+        <v>-391.1920425291777</v>
       </c>
       <c r="D50">
-        <v>573.9529582181679</v>
+        <v>564.8599574708222</v>
       </c>
       <c r="E50">
-        <v>497.704</v>
+        <v>517.952</v>
       </c>
       <c r="F50">
-        <v>971.904</v>
+        <v>992.1519999999999</v>
       </c>
       <c r="G50">
         <v>36.1</v>
@@ -5509,37 +5509,37 @@
         <v>40.733</v>
       </c>
       <c r="M50">
-        <v>229.1749632</v>
+        <v>233.9494416</v>
       </c>
       <c r="N50">
-        <v>-188.4419632</v>
+        <v>-193.2164416</v>
       </c>
       <c r="O50">
-        <v>-60.30142822400001</v>
+        <v>-61.829261312</v>
       </c>
       <c r="P50">
-        <v>-128.140534976</v>
+        <v>-131.387180288</v>
       </c>
       <c r="Q50">
-        <v>-128.073534976</v>
+        <v>-131.320180288</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1097731353605002</v>
+        <v>0.1110275105636473</v>
       </c>
       <c r="T50">
-        <v>0.8337844109825148</v>
+        <v>0.8501331249233485</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0568760209143125</v>
+        <v>0.05571528579361226</v>
       </c>
       <c r="W50">
-        <v>0.2223886342684051</v>
+        <v>0.2226623356098662</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1777375653572266</v>
+        <v>0.1741102681050383</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1657285748362946</v>
+        <v>0.1676285748362946</v>
       </c>
       <c r="C51">
-        <v>-391.1920425291777</v>
+        <v>-420.2494201373187</v>
       </c>
       <c r="D51">
-        <v>564.8599574708222</v>
+        <v>556.0505798626813</v>
       </c>
       <c r="E51">
-        <v>517.952</v>
+        <v>538.2</v>
       </c>
       <c r="F51">
-        <v>992.1519999999999</v>
+        <v>1012.4</v>
       </c>
       <c r="G51">
         <v>36.1</v>
@@ -5591,37 +5591,37 @@
         <v>40.733</v>
       </c>
       <c r="M51">
-        <v>233.9494416</v>
+        <v>238.72392</v>
       </c>
       <c r="N51">
-        <v>-193.2164416</v>
+        <v>-197.99092</v>
       </c>
       <c r="O51">
-        <v>-61.829261312</v>
+        <v>-63.3570944</v>
       </c>
       <c r="P51">
-        <v>-131.387180288</v>
+        <v>-134.6338256</v>
       </c>
       <c r="Q51">
-        <v>-131.320180288</v>
+        <v>-134.5668256</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1110275105636473</v>
+        <v>0.1123320607749202</v>
       </c>
       <c r="T51">
-        <v>0.8501331249233485</v>
+        <v>0.8671357874218154</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05571528579361226</v>
+        <v>0.05460098007774</v>
       </c>
       <c r="W51">
-        <v>0.2226623356098662</v>
+        <v>0.2229250888976689</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1741102681050383</v>
+        <v>0.1706280627429375</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1676285748362946</v>
+        <v>0.1695285748362946</v>
       </c>
       <c r="C52">
-        <v>-420.2494201373187</v>
+        <v>-449.0362407221102</v>
       </c>
       <c r="D52">
-        <v>556.0505798626813</v>
+        <v>547.5117592778897</v>
       </c>
       <c r="E52">
-        <v>538.2</v>
+        <v>558.4479999999999</v>
       </c>
       <c r="F52">
-        <v>1012.4</v>
+        <v>1032.648</v>
       </c>
       <c r="G52">
         <v>36.1</v>
@@ -5673,37 +5673,37 @@
         <v>40.733</v>
       </c>
       <c r="M52">
-        <v>238.72392</v>
+        <v>243.4983984</v>
       </c>
       <c r="N52">
-        <v>-197.99092</v>
+        <v>-202.7653984</v>
       </c>
       <c r="O52">
-        <v>-63.3570944</v>
+        <v>-64.88492748799999</v>
       </c>
       <c r="P52">
-        <v>-134.6338256</v>
+        <v>-137.880470912</v>
       </c>
       <c r="Q52">
-        <v>-134.5668256</v>
+        <v>-137.813470912</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1123320607749202</v>
+        <v>0.1136898579335921</v>
       </c>
       <c r="T52">
-        <v>0.8671357874218154</v>
+        <v>0.8848324361447095</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05460098007774</v>
+        <v>0.05353037262523531</v>
       </c>
       <c r="W52">
-        <v>0.2229250888976689</v>
+        <v>0.2231775381349695</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1706280627429375</v>
+        <v>0.1672824144538604</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1695285748362946</v>
+        <v>0.1714285748362946</v>
       </c>
       <c r="C53">
-        <v>-449.0362407221102</v>
+        <v>-477.5647799543954</v>
       </c>
       <c r="D53">
-        <v>547.5117592778897</v>
+        <v>539.2312200456046</v>
       </c>
       <c r="E53">
-        <v>558.4479999999999</v>
+        <v>578.6959999999999</v>
       </c>
       <c r="F53">
-        <v>1032.648</v>
+        <v>1052.896</v>
       </c>
       <c r="G53">
         <v>36.1</v>
@@ -5755,37 +5755,37 @@
         <v>40.733</v>
       </c>
       <c r="M53">
-        <v>243.4983984</v>
+        <v>248.2728768</v>
       </c>
       <c r="N53">
-        <v>-202.7653984</v>
+        <v>-207.5398768</v>
       </c>
       <c r="O53">
-        <v>-64.88492748799999</v>
+        <v>-66.412760576</v>
       </c>
       <c r="P53">
-        <v>-137.880470912</v>
+        <v>-141.127116224</v>
       </c>
       <c r="Q53">
-        <v>-137.813470912</v>
+        <v>-141.060116224</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1136898579335921</v>
+        <v>0.1151042299738752</v>
       </c>
       <c r="T53">
-        <v>0.8848324361447095</v>
+        <v>0.9032664452310578</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05353037262523531</v>
+        <v>0.05250094238244232</v>
       </c>
       <c r="W53">
-        <v>0.2231775381349695</v>
+        <v>0.2234202777862201</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1672824144538604</v>
+        <v>0.1640654449451323</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1714285748362946</v>
+        <v>0.1733285748362946</v>
       </c>
       <c r="C54">
-        <v>-477.5647799543954</v>
+        <v>-505.8465819427091</v>
       </c>
       <c r="D54">
-        <v>539.2312200456046</v>
+        <v>531.1974180572909</v>
       </c>
       <c r="E54">
-        <v>578.6959999999999</v>
+        <v>598.944</v>
       </c>
       <c r="F54">
-        <v>1052.896</v>
+        <v>1073.144</v>
       </c>
       <c r="G54">
         <v>36.1</v>
@@ -5837,37 +5837,37 @@
         <v>40.733</v>
       </c>
       <c r="M54">
-        <v>248.2728768</v>
+        <v>253.0473552</v>
       </c>
       <c r="N54">
-        <v>-207.5398768</v>
+        <v>-212.3143552</v>
       </c>
       <c r="O54">
-        <v>-66.412760576</v>
+        <v>-67.940593664</v>
       </c>
       <c r="P54">
-        <v>-141.127116224</v>
+        <v>-144.373761536</v>
       </c>
       <c r="Q54">
-        <v>-141.060116224</v>
+        <v>-144.306761536</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1151042299738752</v>
+        <v>0.1165787880584258</v>
       </c>
       <c r="T54">
-        <v>0.9032664452310578</v>
+        <v>0.9224848802359739</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05250094238244232</v>
+        <v>0.05151035856390567</v>
       </c>
       <c r="W54">
-        <v>0.2234202777862201</v>
+        <v>0.2236538574506311</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1640654449451323</v>
+        <v>0.1609698705122052</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1733285748362946</v>
+        <v>0.1752285748362946</v>
       </c>
       <c r="C55">
-        <v>-505.8465819427091</v>
+        <v>-533.8925129296292</v>
       </c>
       <c r="D55">
-        <v>531.1974180572909</v>
+        <v>523.3994870703708</v>
       </c>
       <c r="E55">
-        <v>598.944</v>
+        <v>619.192</v>
       </c>
       <c r="F55">
-        <v>1073.144</v>
+        <v>1093.392</v>
       </c>
       <c r="G55">
         <v>36.1</v>
@@ -5919,37 +5919,37 @@
         <v>40.733</v>
       </c>
       <c r="M55">
-        <v>253.0473552</v>
+        <v>257.8218336</v>
       </c>
       <c r="N55">
-        <v>-212.3143552</v>
+        <v>-217.0888336</v>
       </c>
       <c r="O55">
-        <v>-67.940593664</v>
+        <v>-69.46842675200001</v>
       </c>
       <c r="P55">
-        <v>-144.373761536</v>
+        <v>-147.620406848</v>
       </c>
       <c r="Q55">
-        <v>-144.306761536</v>
+        <v>-147.553406848</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1165787880584258</v>
+        <v>0.1181174573640437</v>
       </c>
       <c r="T55">
-        <v>0.9224848802359739</v>
+        <v>0.9425388993715386</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05151035856390567</v>
+        <v>0.05055646303494444</v>
       </c>
       <c r="W55">
-        <v>0.2236538574506311</v>
+        <v>0.2238787860163601</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1609698705122052</v>
+        <v>0.1579889469842014</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1752285748362946</v>
+        <v>0.1771285748362946</v>
       </c>
       <c r="C56">
-        <v>-533.8925129296292</v>
+        <v>-561.7128103270034</v>
       </c>
       <c r="D56">
-        <v>523.3994870703708</v>
+        <v>515.8271896729967</v>
       </c>
       <c r="E56">
-        <v>619.192</v>
+        <v>639.4400000000001</v>
       </c>
       <c r="F56">
-        <v>1093.392</v>
+        <v>1113.64</v>
       </c>
       <c r="G56">
         <v>36.1</v>
@@ -6001,37 +6001,37 @@
         <v>40.733</v>
       </c>
       <c r="M56">
-        <v>257.8218336</v>
+        <v>262.596312</v>
       </c>
       <c r="N56">
-        <v>-217.0888336</v>
+        <v>-221.863312</v>
       </c>
       <c r="O56">
-        <v>-69.46842675200001</v>
+        <v>-70.99625984000001</v>
       </c>
       <c r="P56">
-        <v>-147.620406848</v>
+        <v>-150.86705216</v>
       </c>
       <c r="Q56">
-        <v>-147.553406848</v>
+        <v>-150.80005216</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1181174573640437</v>
+        <v>0.1197245119721336</v>
       </c>
       <c r="T56">
-        <v>0.9425388993715386</v>
+        <v>0.9634842082464617</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05055646303494444</v>
+        <v>0.04963725461612728</v>
       </c>
       <c r="W56">
-        <v>0.2238787860163601</v>
+        <v>0.2240955353615172</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1579889469842014</v>
+        <v>0.1551164206753978</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1771285748362946</v>
+        <v>0.1790285748362946</v>
       </c>
       <c r="C57">
-        <v>-561.7128103270034</v>
+        <v>-589.317127555368</v>
       </c>
       <c r="D57">
-        <v>515.8271896729967</v>
+        <v>508.4708724446322</v>
       </c>
       <c r="E57">
-        <v>639.4400000000001</v>
+        <v>659.6880000000001</v>
       </c>
       <c r="F57">
-        <v>1113.64</v>
+        <v>1133.888</v>
       </c>
       <c r="G57">
         <v>36.1</v>
@@ -6083,37 +6083,37 @@
         <v>40.733</v>
       </c>
       <c r="M57">
-        <v>262.596312</v>
+        <v>267.3707904</v>
       </c>
       <c r="N57">
-        <v>-221.863312</v>
+        <v>-226.6377904</v>
       </c>
       <c r="O57">
-        <v>-70.99625984000001</v>
+        <v>-72.52409292800002</v>
       </c>
       <c r="P57">
-        <v>-150.86705216</v>
+        <v>-154.113697472</v>
       </c>
       <c r="Q57">
-        <v>-150.80005216</v>
+        <v>-154.046697472</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1197245119721336</v>
+        <v>0.1214046145169548</v>
       </c>
       <c r="T57">
-        <v>0.9634842082464617</v>
+        <v>0.9853815766156995</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04963725461612728</v>
+        <v>0.04875087506941071</v>
       </c>
       <c r="W57">
-        <v>0.2240955353615172</v>
+        <v>0.224304543658633</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1551164206753978</v>
+        <v>0.1523464845919085</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1790285748362946</v>
+        <v>0.1809285748362946</v>
       </c>
       <c r="C58">
-        <v>-589.317127555368</v>
+        <v>-616.7145751005318</v>
       </c>
       <c r="D58">
-        <v>508.4708724446322</v>
+        <v>501.3214248994685</v>
       </c>
       <c r="E58">
-        <v>659.6880000000001</v>
+        <v>679.9360000000001</v>
       </c>
       <c r="F58">
-        <v>1133.888</v>
+        <v>1154.136</v>
       </c>
       <c r="G58">
         <v>36.1</v>
@@ -6165,37 +6165,37 @@
         <v>40.733</v>
       </c>
       <c r="M58">
-        <v>267.3707904</v>
+        <v>272.1452688000001</v>
       </c>
       <c r="N58">
-        <v>-226.6377904</v>
+        <v>-231.4122688</v>
       </c>
       <c r="O58">
-        <v>-72.52409292800002</v>
+        <v>-74.05192601600002</v>
       </c>
       <c r="P58">
-        <v>-154.113697472</v>
+        <v>-157.360342784</v>
       </c>
       <c r="Q58">
-        <v>-154.046697472</v>
+        <v>-157.293342784</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1214046145169548</v>
+        <v>0.1231628613661863</v>
       </c>
       <c r="T58">
-        <v>0.9853815766156995</v>
+        <v>1.008297427234669</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04875087506941071</v>
+        <v>0.04789559655942105</v>
       </c>
       <c r="W58">
-        <v>0.224304543658633</v>
+        <v>0.2245062183312885</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1523464845919085</v>
+        <v>0.1496737392481908</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1809285748362946</v>
+        <v>0.1828285748362946</v>
       </c>
       <c r="C59">
-        <v>-616.7145751005318</v>
+        <v>-643.9137581544818</v>
       </c>
       <c r="D59">
-        <v>501.3214248994685</v>
+        <v>494.3702418455182</v>
       </c>
       <c r="E59">
-        <v>679.9360000000001</v>
+        <v>700.184</v>
       </c>
       <c r="F59">
-        <v>1154.136</v>
+        <v>1174.384</v>
       </c>
       <c r="G59">
         <v>36.1</v>
@@ -6247,37 +6247,37 @@
         <v>40.733</v>
       </c>
       <c r="M59">
-        <v>272.1452688000001</v>
+        <v>276.9197472</v>
       </c>
       <c r="N59">
-        <v>-231.4122688</v>
+        <v>-236.1867472</v>
       </c>
       <c r="O59">
-        <v>-74.05192601600002</v>
+        <v>-75.579759104</v>
       </c>
       <c r="P59">
-        <v>-157.360342784</v>
+        <v>-160.606988096</v>
       </c>
       <c r="Q59">
-        <v>-157.293342784</v>
+        <v>-160.539988096</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1231628613661863</v>
+        <v>0.1250048342558574</v>
       </c>
       <c r="T59">
-        <v>1.008297427234669</v>
+        <v>1.032304508835495</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04789559655942105</v>
+        <v>0.04706981041184483</v>
       </c>
       <c r="W59">
-        <v>0.2245062183312885</v>
+        <v>0.224700938704887</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1496737392481908</v>
+        <v>0.1470931575370151</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1828285748362946</v>
+        <v>0.1847285748362946</v>
       </c>
       <c r="C60">
-        <v>-643.9137581544813</v>
+        <v>-670.9228111676092</v>
       </c>
       <c r="D60">
-        <v>494.3702418455184</v>
+        <v>487.6091888323906</v>
       </c>
       <c r="E60">
-        <v>700.1839999999997</v>
+        <v>720.4319999999998</v>
       </c>
       <c r="F60">
-        <v>1174.384</v>
+        <v>1194.632</v>
       </c>
       <c r="G60">
         <v>36.1</v>
@@ -6329,37 +6329,37 @@
         <v>40.733</v>
       </c>
       <c r="M60">
-        <v>276.9197472</v>
+        <v>281.6942256</v>
       </c>
       <c r="N60">
-        <v>-236.1867472</v>
+        <v>-240.9612256</v>
       </c>
       <c r="O60">
-        <v>-75.57975910399999</v>
+        <v>-77.107592192</v>
       </c>
       <c r="P60">
-        <v>-160.606988096</v>
+        <v>-163.853633408</v>
       </c>
       <c r="Q60">
-        <v>-160.5399880959999</v>
+        <v>-163.786633408</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1250048342558574</v>
+        <v>0.12693665948161</v>
       </c>
       <c r="T60">
-        <v>1.032304508835494</v>
+        <v>1.05748266758758</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04706981041184484</v>
+        <v>0.04627201701503391</v>
       </c>
       <c r="W60">
-        <v>0.224700938704887</v>
+        <v>0.224889058387855</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1470931575370151</v>
+        <v>0.144600053171981</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1847285748362946</v>
+        <v>0.1866285748362946</v>
       </c>
       <c r="C61">
-        <v>-670.9228111676092</v>
+        <v>-697.7494296039492</v>
       </c>
       <c r="D61">
-        <v>487.6091888323906</v>
+        <v>481.0305703960507</v>
       </c>
       <c r="E61">
-        <v>720.4319999999998</v>
+        <v>740.6799999999998</v>
       </c>
       <c r="F61">
-        <v>1194.632</v>
+        <v>1214.88</v>
       </c>
       <c r="G61">
         <v>36.1</v>
@@ -6411,37 +6411,37 @@
         <v>40.733</v>
       </c>
       <c r="M61">
-        <v>281.6942256</v>
+        <v>286.468704</v>
       </c>
       <c r="N61">
-        <v>-240.9612256</v>
+        <v>-245.735704</v>
       </c>
       <c r="O61">
-        <v>-77.107592192</v>
+        <v>-78.63542528000001</v>
       </c>
       <c r="P61">
-        <v>-163.853633408</v>
+        <v>-167.10027872</v>
       </c>
       <c r="Q61">
-        <v>-163.786633408</v>
+        <v>-167.03327872</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.12693665948161</v>
+        <v>0.1289650759686503</v>
       </c>
       <c r="T61">
-        <v>1.05748266758758</v>
+        <v>1.083919734277269</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04627201701503391</v>
+        <v>0.04550081673145</v>
       </c>
       <c r="W61">
-        <v>0.224889058387855</v>
+        <v>0.2250709074147241</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.144600053171981</v>
+        <v>0.1421900522857813</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1866285748362946</v>
+        <v>0.1885285748362946</v>
       </c>
       <c r="C62">
-        <v>-697.7494296039492</v>
+        <v>-724.4008991600685</v>
       </c>
       <c r="D62">
-        <v>481.0305703960507</v>
+        <v>474.6271008399314</v>
       </c>
       <c r="E62">
-        <v>740.6799999999998</v>
+        <v>760.9279999999999</v>
       </c>
       <c r="F62">
-        <v>1214.88</v>
+        <v>1235.128</v>
       </c>
       <c r="G62">
         <v>36.1</v>
@@ -6493,37 +6493,37 @@
         <v>40.733</v>
       </c>
       <c r="M62">
-        <v>286.468704</v>
+        <v>291.2431824</v>
       </c>
       <c r="N62">
-        <v>-245.735704</v>
+        <v>-250.5101824</v>
       </c>
       <c r="O62">
-        <v>-78.63542528000001</v>
+        <v>-80.163258368</v>
       </c>
       <c r="P62">
-        <v>-167.10027872</v>
+        <v>-170.346924032</v>
       </c>
       <c r="Q62">
-        <v>-167.03327872</v>
+        <v>-170.279924032</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1289650759686503</v>
+        <v>0.1310975138140003</v>
       </c>
       <c r="T62">
-        <v>1.083919734277269</v>
+        <v>1.111712547976686</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04550081673145</v>
+        <v>0.04475490170306558</v>
       </c>
       <c r="W62">
-        <v>0.2250709074147241</v>
+        <v>0.2252467941784171</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1421900522857813</v>
+        <v>0.1398590678220799</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1885285748362946</v>
+        <v>0.1904285748362946</v>
       </c>
       <c r="C63">
-        <v>-724.4008991600685</v>
+        <v>-750.8841226808466</v>
       </c>
       <c r="D63">
-        <v>474.6271008399314</v>
+        <v>468.3918773191533</v>
       </c>
       <c r="E63">
-        <v>760.9279999999999</v>
+        <v>781.1759999999999</v>
       </c>
       <c r="F63">
-        <v>1235.128</v>
+        <v>1255.376</v>
       </c>
       <c r="G63">
         <v>36.1</v>
@@ -6575,37 +6575,37 @@
         <v>40.733</v>
       </c>
       <c r="M63">
-        <v>291.2431824</v>
+        <v>296.0176608</v>
       </c>
       <c r="N63">
-        <v>-250.5101824</v>
+        <v>-255.2846608</v>
       </c>
       <c r="O63">
-        <v>-80.163258368</v>
+        <v>-81.691091456</v>
       </c>
       <c r="P63">
-        <v>-170.346924032</v>
+        <v>-173.593569344</v>
       </c>
       <c r="Q63">
-        <v>-170.279924032</v>
+        <v>-173.526569344</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1310975138140003</v>
+        <v>0.1333421852301582</v>
       </c>
       <c r="T63">
-        <v>1.111712547976686</v>
+        <v>1.140968141344494</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04475490170306558</v>
+        <v>0.04403304844979033</v>
       </c>
       <c r="W63">
-        <v>0.2252467941784171</v>
+        <v>0.2254170071755395</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1398590678220799</v>
+        <v>0.1376032764055948</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1904285748362946</v>
+        <v>0.1923285748362946</v>
       </c>
       <c r="C64">
-        <v>-750.8841226808466</v>
+        <v>-777.2056449811944</v>
       </c>
       <c r="D64">
-        <v>468.3918773191533</v>
+        <v>462.3183550188056</v>
       </c>
       <c r="E64">
-        <v>781.1759999999999</v>
+        <v>801.424</v>
       </c>
       <c r="F64">
-        <v>1255.376</v>
+        <v>1275.624</v>
       </c>
       <c r="G64">
         <v>36.1</v>
@@ -6657,37 +6657,37 @@
         <v>40.733</v>
       </c>
       <c r="M64">
-        <v>296.0176608</v>
+        <v>300.7921392</v>
       </c>
       <c r="N64">
-        <v>-255.2846608</v>
+        <v>-260.0591392</v>
       </c>
       <c r="O64">
-        <v>-81.691091456</v>
+        <v>-83.218924544</v>
       </c>
       <c r="P64">
-        <v>-173.593569344</v>
+        <v>-176.840214656</v>
       </c>
       <c r="Q64">
-        <v>-173.526569344</v>
+        <v>-176.773214656</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1333421852301582</v>
+        <v>0.1357081902363787</v>
       </c>
       <c r="T64">
-        <v>1.140968141344494</v>
+        <v>1.171805118137588</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04403304844979033</v>
+        <v>0.04333411117280953</v>
       </c>
       <c r="W64">
-        <v>0.2254170071755395</v>
+        <v>0.2255818165854515</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1376032764055948</v>
+        <v>0.1354190974150298</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1923285748362946</v>
+        <v>0.1942285748362945</v>
       </c>
       <c r="C65">
-        <v>-777.2056449811944</v>
+        <v>-803.3716757613495</v>
       </c>
       <c r="D65">
-        <v>462.3183550188056</v>
+        <v>456.4003242386506</v>
       </c>
       <c r="E65">
-        <v>801.424</v>
+        <v>821.672</v>
       </c>
       <c r="F65">
-        <v>1275.624</v>
+        <v>1295.872</v>
       </c>
       <c r="G65">
         <v>36.1</v>
@@ -6739,37 +6739,37 @@
         <v>40.733</v>
       </c>
       <c r="M65">
-        <v>300.7921392</v>
+        <v>305.5666176</v>
       </c>
       <c r="N65">
-        <v>-260.0591392</v>
+        <v>-264.8336176</v>
       </c>
       <c r="O65">
-        <v>-83.218924544</v>
+        <v>-84.74675763200001</v>
       </c>
       <c r="P65">
-        <v>-176.840214656</v>
+        <v>-180.086859968</v>
       </c>
       <c r="Q65">
-        <v>-176.773214656</v>
+        <v>-180.019859968</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1357081902363787</v>
+        <v>0.138205639965167</v>
       </c>
       <c r="T65">
-        <v>1.171805118137588</v>
+        <v>1.204355260308077</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04333411117280953</v>
+        <v>0.04265701568573437</v>
       </c>
       <c r="W65">
-        <v>0.2255818165854515</v>
+        <v>0.2257414757013038</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1354190974150298</v>
+        <v>0.1333031740179199</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1942285748362945</v>
+        <v>0.1961285748362946</v>
       </c>
       <c r="C66">
-        <v>-803.3716757613495</v>
+        <v>-829.3881107844165</v>
       </c>
       <c r="D66">
-        <v>456.4003242386506</v>
+        <v>450.6318892155835</v>
       </c>
       <c r="E66">
-        <v>821.672</v>
+        <v>841.9200000000001</v>
       </c>
       <c r="F66">
-        <v>1295.872</v>
+        <v>1316.12</v>
       </c>
       <c r="G66">
         <v>36.1</v>
@@ -6821,37 +6821,37 @@
         <v>40.733</v>
       </c>
       <c r="M66">
-        <v>305.5666176</v>
+        <v>310.3410960000001</v>
       </c>
       <c r="N66">
-        <v>-264.8336176</v>
+        <v>-269.608096</v>
       </c>
       <c r="O66">
-        <v>-84.74675763200001</v>
+        <v>-86.27459072000002</v>
       </c>
       <c r="P66">
-        <v>-180.086859968</v>
+        <v>-183.33350528</v>
       </c>
       <c r="Q66">
-        <v>-180.019859968</v>
+        <v>-183.26650528</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.138205639965167</v>
+        <v>0.1408458011070289</v>
       </c>
       <c r="T66">
-        <v>1.204355260308077</v>
+        <v>1.238765410602593</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04265701568573437</v>
+        <v>0.04200075390595385</v>
       </c>
       <c r="W66">
-        <v>0.2257414757013038</v>
+        <v>0.2258962222289761</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1333031740179199</v>
+        <v>0.1312523559561057</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1961285748362946</v>
+        <v>0.1980285748362946</v>
       </c>
       <c r="C67">
-        <v>-829.3881107844165</v>
+        <v>-855.2605514679763</v>
       </c>
       <c r="D67">
-        <v>450.6318892155835</v>
+        <v>445.0074485320236</v>
       </c>
       <c r="E67">
-        <v>841.9200000000001</v>
+        <v>862.1679999999999</v>
       </c>
       <c r="F67">
-        <v>1316.12</v>
+        <v>1336.368</v>
       </c>
       <c r="G67">
         <v>36.1</v>
@@ -6903,37 +6903,37 @@
         <v>40.733</v>
       </c>
       <c r="M67">
-        <v>310.3410960000001</v>
+        <v>315.1155744</v>
       </c>
       <c r="N67">
-        <v>-269.608096</v>
+        <v>-274.3825744</v>
       </c>
       <c r="O67">
-        <v>-86.27459072000002</v>
+        <v>-87.802423808</v>
       </c>
       <c r="P67">
-        <v>-183.33350528</v>
+        <v>-186.580150592</v>
       </c>
       <c r="Q67">
-        <v>-183.26650528</v>
+        <v>-186.513150592</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1408458011070289</v>
+        <v>0.1436412658454709</v>
       </c>
       <c r="T67">
-        <v>1.238765410602593</v>
+        <v>1.275199687385023</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04200075390595385</v>
+        <v>0.04136437884677273</v>
       </c>
       <c r="W67">
-        <v>0.2258962222289761</v>
+        <v>0.226046279467931</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1312523559561057</v>
+        <v>0.1292636838961648</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1980285748362946</v>
+        <v>0.1999285748362946</v>
       </c>
       <c r="C68">
-        <v>-855.2605514679763</v>
+        <v>-880.9943230266174</v>
       </c>
       <c r="D68">
-        <v>445.0074485320236</v>
+        <v>439.5216769733825</v>
       </c>
       <c r="E68">
-        <v>862.1679999999999</v>
+        <v>882.4159999999999</v>
       </c>
       <c r="F68">
-        <v>1336.368</v>
+        <v>1356.616</v>
       </c>
       <c r="G68">
         <v>36.1</v>
@@ -6985,37 +6985,37 @@
         <v>40.733</v>
       </c>
       <c r="M68">
-        <v>315.1155744</v>
+        <v>319.8900528</v>
       </c>
       <c r="N68">
-        <v>-274.3825744</v>
+        <v>-279.1570528</v>
       </c>
       <c r="O68">
-        <v>-87.802423808</v>
+        <v>-89.33025689600001</v>
       </c>
       <c r="P68">
-        <v>-186.580150592</v>
+        <v>-189.826795904</v>
       </c>
       <c r="Q68">
-        <v>-186.513150592</v>
+        <v>-189.759795904</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1436412658454709</v>
+        <v>0.1466061526892731</v>
       </c>
       <c r="T68">
-        <v>1.275199687385023</v>
+        <v>1.313842102154266</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04136437884677273</v>
+        <v>0.04074700005801492</v>
       </c>
       <c r="W68">
-        <v>0.226046279467931</v>
+        <v>0.2261918573863201</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1292636838961648</v>
+        <v>0.1273343751812966</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1999285748362946</v>
+        <v>0.2018285748362946</v>
       </c>
       <c r="C69">
-        <v>-880.9943230266174</v>
+        <v>-906.5944912889092</v>
       </c>
       <c r="D69">
-        <v>439.5216769733825</v>
+        <v>434.1695087110907</v>
       </c>
       <c r="E69">
-        <v>882.4159999999999</v>
+        <v>902.664</v>
       </c>
       <c r="F69">
-        <v>1356.616</v>
+        <v>1376.864</v>
       </c>
       <c r="G69">
         <v>36.1</v>
@@ -7067,37 +7067,37 @@
         <v>40.733</v>
       </c>
       <c r="M69">
-        <v>319.8900528</v>
+        <v>324.6645312</v>
       </c>
       <c r="N69">
-        <v>-279.1570528</v>
+        <v>-283.9315312</v>
       </c>
       <c r="O69">
-        <v>-89.33025689600001</v>
+        <v>-90.858089984</v>
       </c>
       <c r="P69">
-        <v>-189.826795904</v>
+        <v>-193.073441216</v>
       </c>
       <c r="Q69">
-        <v>-189.759795904</v>
+        <v>-193.006441216</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1466061526892731</v>
+        <v>0.1497563449608129</v>
       </c>
       <c r="T69">
-        <v>1.313842102154266</v>
+        <v>1.354899667846587</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04074700005801492</v>
+        <v>0.04014777946892648</v>
       </c>
       <c r="W69">
-        <v>0.2261918573863201</v>
+        <v>0.2263331536012272</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1273343751812966</v>
+        <v>0.1254618108403952</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2018285748362946</v>
+        <v>0.2037285748362946</v>
       </c>
       <c r="C70">
-        <v>-906.5944912889092</v>
+        <v>-932.0658783004503</v>
       </c>
       <c r="D70">
-        <v>434.1695087110907</v>
+        <v>428.9461216995497</v>
       </c>
       <c r="E70">
-        <v>902.664</v>
+        <v>922.912</v>
       </c>
       <c r="F70">
-        <v>1376.864</v>
+        <v>1397.112</v>
       </c>
       <c r="G70">
         <v>36.1</v>
@@ -7149,37 +7149,37 @@
         <v>40.733</v>
       </c>
       <c r="M70">
-        <v>324.6645312</v>
+        <v>329.4390096</v>
       </c>
       <c r="N70">
-        <v>-283.9315312</v>
+        <v>-288.7060096</v>
       </c>
       <c r="O70">
-        <v>-90.858089984</v>
+        <v>-92.38592307200001</v>
       </c>
       <c r="P70">
-        <v>-193.073441216</v>
+        <v>-196.320086528</v>
       </c>
       <c r="Q70">
-        <v>-193.006441216</v>
+        <v>-196.253086528</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1497563449608129</v>
+        <v>0.1531097754434197</v>
       </c>
       <c r="T70">
-        <v>1.354899667846587</v>
+        <v>1.398606108744864</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04014777946892648</v>
+        <v>0.03956592759256522</v>
       </c>
       <c r="W70">
-        <v>0.2263331536012272</v>
+        <v>0.2264703542736731</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1254618108403952</v>
+        <v>0.1236435237267663</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2037285748362946</v>
+        <v>0.2056285748362946</v>
       </c>
       <c r="C71">
-        <v>-932.0658783004503</v>
+        <v>-957.413076814007</v>
       </c>
       <c r="D71">
-        <v>428.9461216995497</v>
+        <v>423.8469231859931</v>
       </c>
       <c r="E71">
-        <v>922.912</v>
+        <v>943.1600000000001</v>
       </c>
       <c r="F71">
-        <v>1397.112</v>
+        <v>1417.36</v>
       </c>
       <c r="G71">
         <v>36.1</v>
@@ -7231,37 +7231,37 @@
         <v>40.733</v>
       </c>
       <c r="M71">
-        <v>329.4390096</v>
+        <v>334.213488</v>
       </c>
       <c r="N71">
-        <v>-288.7060096</v>
+        <v>-293.480488</v>
       </c>
       <c r="O71">
-        <v>-92.38592307200001</v>
+        <v>-93.91375616000002</v>
       </c>
       <c r="P71">
-        <v>-196.320086528</v>
+        <v>-199.56673184</v>
       </c>
       <c r="Q71">
-        <v>-196.253086528</v>
+        <v>-199.49973184</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1531097754434197</v>
+        <v>0.1566867679582004</v>
       </c>
       <c r="T71">
-        <v>1.398606108744864</v>
+        <v>1.445226312369692</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03956592759256522</v>
+        <v>0.03900070005552857</v>
       </c>
       <c r="W71">
-        <v>0.2264703542736731</v>
+        <v>0.2266036349269064</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1236435237267663</v>
+        <v>0.1218771876735268</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2056285748362946</v>
+        <v>0.2075285748362946</v>
       </c>
       <c r="C72">
-        <v>-957.413076814007</v>
+        <v>-982.6404637582655</v>
       </c>
       <c r="D72">
-        <v>423.8469231859931</v>
+        <v>418.8675362417346</v>
       </c>
       <c r="E72">
-        <v>943.1600000000001</v>
+        <v>963.4080000000001</v>
       </c>
       <c r="F72">
-        <v>1417.36</v>
+        <v>1437.608</v>
       </c>
       <c r="G72">
         <v>36.1</v>
@@ -7313,37 +7313,37 @@
         <v>40.733</v>
       </c>
       <c r="M72">
-        <v>334.213488</v>
+        <v>338.9879664000001</v>
       </c>
       <c r="N72">
-        <v>-293.480488</v>
+        <v>-298.2549664000001</v>
       </c>
       <c r="O72">
-        <v>-93.91375616000002</v>
+        <v>-95.44158924800001</v>
       </c>
       <c r="P72">
-        <v>-199.56673184</v>
+        <v>-202.813377152</v>
       </c>
       <c r="Q72">
-        <v>-199.49973184</v>
+        <v>-202.746377152</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1566867679582004</v>
+        <v>0.1605104496119314</v>
       </c>
       <c r="T72">
-        <v>1.445226312369692</v>
+        <v>1.495061702451406</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03900070005552857</v>
+        <v>0.03845139442094366</v>
       </c>
       <c r="W72">
-        <v>0.2266036349269064</v>
+        <v>0.2267331611955415</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1218771876735268</v>
+        <v>0.120160607565449</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2075285748362946</v>
+        <v>0.2094285748362946</v>
       </c>
       <c r="C73">
-        <v>-982.6404637582657</v>
+        <v>-1007.752212768214</v>
       </c>
       <c r="D73">
-        <v>418.8675362417342</v>
+        <v>414.0037872317859</v>
       </c>
       <c r="E73">
-        <v>963.4079999999999</v>
+        <v>983.6559999999999</v>
       </c>
       <c r="F73">
-        <v>1437.608</v>
+        <v>1457.856</v>
       </c>
       <c r="G73">
         <v>36.1</v>
@@ -7395,37 +7395,37 @@
         <v>40.733</v>
       </c>
       <c r="M73">
-        <v>338.9879664</v>
+        <v>343.7624448</v>
       </c>
       <c r="N73">
-        <v>-298.2549664</v>
+        <v>-303.0294448</v>
       </c>
       <c r="O73">
-        <v>-95.441589248</v>
+        <v>-96.96942233600001</v>
       </c>
       <c r="P73">
-        <v>-202.813377152</v>
+        <v>-206.060022464</v>
       </c>
       <c r="Q73">
-        <v>-202.746377152</v>
+        <v>-205.993022464</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1605104496119314</v>
+        <v>0.1646072513837861</v>
       </c>
       <c r="T73">
-        <v>1.495061702451406</v>
+        <v>1.548456763253242</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03845139442094367</v>
+        <v>0.03791734727620833</v>
       </c>
       <c r="W73">
-        <v>0.2267331611955415</v>
+        <v>0.2268590895122701</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.120160607565449</v>
+        <v>0.1184917102381511</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2094285748362946</v>
+        <v>0.2113285748362946</v>
       </c>
       <c r="C74">
-        <v>-1007.752212768214</v>
+        <v>-1032.752305852555</v>
       </c>
       <c r="D74">
-        <v>414.0037872317859</v>
+        <v>409.2516941474447</v>
       </c>
       <c r="E74">
-        <v>983.6559999999999</v>
+        <v>1003.904</v>
       </c>
       <c r="F74">
-        <v>1457.856</v>
+        <v>1478.104</v>
       </c>
       <c r="G74">
         <v>36.1</v>
@@ -7477,37 +7477,37 @@
         <v>40.733</v>
       </c>
       <c r="M74">
-        <v>343.7624448</v>
+        <v>348.5369232</v>
       </c>
       <c r="N74">
-        <v>-303.0294448</v>
+        <v>-307.8039232</v>
       </c>
       <c r="O74">
-        <v>-96.96942233600001</v>
+        <v>-98.49725542400002</v>
       </c>
       <c r="P74">
-        <v>-206.060022464</v>
+        <v>-209.306667776</v>
       </c>
       <c r="Q74">
-        <v>-205.993022464</v>
+        <v>-209.239667776</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1646072513837861</v>
+        <v>0.169007519953556</v>
       </c>
       <c r="T74">
-        <v>1.548456763253242</v>
+        <v>1.605807013744102</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03791734727620833</v>
+        <v>0.03739793156009589</v>
       </c>
       <c r="W74">
-        <v>0.2268590895122701</v>
+        <v>0.2269815677381294</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1184917102381511</v>
+        <v>0.1168685361252997</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2113285748362946</v>
+        <v>0.2132285748362946</v>
       </c>
       <c r="C75">
-        <v>-1032.752305852555</v>
+        <v>-1057.644544266699</v>
       </c>
       <c r="D75">
-        <v>409.2516941474447</v>
+        <v>404.6074557333005</v>
       </c>
       <c r="E75">
-        <v>1003.904</v>
+        <v>1024.152</v>
       </c>
       <c r="F75">
-        <v>1478.104</v>
+        <v>1498.352</v>
       </c>
       <c r="G75">
         <v>36.1</v>
@@ -7559,37 +7559,37 @@
         <v>40.733</v>
       </c>
       <c r="M75">
-        <v>348.5369232</v>
+        <v>353.3114016</v>
       </c>
       <c r="N75">
-        <v>-307.8039232</v>
+        <v>-312.5784015999999</v>
       </c>
       <c r="O75">
-        <v>-98.49725542400002</v>
+        <v>-100.025088512</v>
       </c>
       <c r="P75">
-        <v>-209.306667776</v>
+        <v>-212.553313088</v>
       </c>
       <c r="Q75">
-        <v>-209.239667776</v>
+        <v>-212.486313088</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.169007519953556</v>
+        <v>0.1737462707210004</v>
       </c>
       <c r="T75">
-        <v>1.605807013744102</v>
+        <v>1.66756882196503</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03739793156009589</v>
+        <v>0.03689255410658109</v>
       </c>
       <c r="W75">
-        <v>0.2269815677381294</v>
+        <v>0.2271007357416682</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1168685361252997</v>
+        <v>0.1152892315830659</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2132285748362946</v>
+        <v>0.2151285748362946</v>
       </c>
       <c r="C76">
-        <v>-1057.644544266699</v>
+        <v>-1082.432558653736</v>
       </c>
       <c r="D76">
-        <v>404.6074557333005</v>
+        <v>400.0674413462636</v>
       </c>
       <c r="E76">
-        <v>1024.152</v>
+        <v>1044.4</v>
       </c>
       <c r="F76">
-        <v>1498.352</v>
+        <v>1518.6</v>
       </c>
       <c r="G76">
         <v>36.1</v>
@@ -7641,37 +7641,37 @@
         <v>40.733</v>
       </c>
       <c r="M76">
-        <v>353.3114016</v>
+        <v>358.08588</v>
       </c>
       <c r="N76">
-        <v>-312.5784015999999</v>
+        <v>-317.35288</v>
       </c>
       <c r="O76">
-        <v>-100.025088512</v>
+        <v>-101.5529216</v>
       </c>
       <c r="P76">
-        <v>-212.553313088</v>
+        <v>-215.7999584</v>
       </c>
       <c r="Q76">
-        <v>-212.486313088</v>
+        <v>-215.7329584</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1737462707210004</v>
+        <v>0.1788641215498405</v>
       </c>
       <c r="T76">
-        <v>1.66756882196503</v>
+        <v>1.734271574843631</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03689255410658109</v>
+        <v>0.03640065338516001</v>
       </c>
       <c r="W76">
-        <v>0.2271007357416682</v>
+        <v>0.2272167259317793</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1152892315830659</v>
+        <v>0.1137520418286251</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2151285748362946</v>
+        <v>0.2170285748362946</v>
       </c>
       <c r="C77">
-        <v>-1082.432558653736</v>
+        <v>-1107.119818510245</v>
       </c>
       <c r="D77">
-        <v>400.0674413462636</v>
+        <v>395.6281814897552</v>
       </c>
       <c r="E77">
-        <v>1044.4</v>
+        <v>1064.648</v>
       </c>
       <c r="F77">
-        <v>1518.6</v>
+        <v>1538.848</v>
       </c>
       <c r="G77">
         <v>36.1</v>
@@ -7723,37 +7723,37 @@
         <v>40.733</v>
       </c>
       <c r="M77">
-        <v>358.08588</v>
+        <v>362.8603584</v>
       </c>
       <c r="N77">
-        <v>-317.35288</v>
+        <v>-322.1273584</v>
       </c>
       <c r="O77">
-        <v>-101.5529216</v>
+        <v>-103.080754688</v>
       </c>
       <c r="P77">
-        <v>-215.7999584</v>
+        <v>-219.046603712</v>
       </c>
       <c r="Q77">
-        <v>-215.7329584</v>
+        <v>-218.979603712</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1788641215498405</v>
+        <v>0.1844084599477505</v>
       </c>
       <c r="T77">
-        <v>1.734271574843631</v>
+        <v>1.806532890462116</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03640065338516001</v>
+        <v>0.03592169741956579</v>
       </c>
       <c r="W77">
-        <v>0.2272167259317793</v>
+        <v>0.2273296637484664</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1137520418286251</v>
+        <v>0.1122553044361432</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2170285748362946</v>
+        <v>0.2189285748362946</v>
       </c>
       <c r="C78">
-        <v>-1107.119818510245</v>
+        <v>-1131.709641028806</v>
       </c>
       <c r="D78">
-        <v>395.6281814897552</v>
+        <v>391.2863589711943</v>
       </c>
       <c r="E78">
-        <v>1064.648</v>
+        <v>1084.896</v>
       </c>
       <c r="F78">
-        <v>1538.848</v>
+        <v>1559.096</v>
       </c>
       <c r="G78">
         <v>36.1</v>
@@ -7805,37 +7805,37 @@
         <v>40.733</v>
       </c>
       <c r="M78">
-        <v>362.8603584</v>
+        <v>367.6348368</v>
       </c>
       <c r="N78">
-        <v>-322.1273584</v>
+        <v>-326.9018368</v>
       </c>
       <c r="O78">
-        <v>-103.080754688</v>
+        <v>-104.608587776</v>
       </c>
       <c r="P78">
-        <v>-219.046603712</v>
+        <v>-222.293249024</v>
       </c>
       <c r="Q78">
-        <v>-218.979603712</v>
+        <v>-222.226249024</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1844084599477505</v>
+        <v>0.1904349147280875</v>
       </c>
       <c r="T78">
-        <v>1.806532890462116</v>
+        <v>1.885077798743077</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03592169741956579</v>
+        <v>0.03545518186866234</v>
       </c>
       <c r="W78">
-        <v>0.2273296637484664</v>
+        <v>0.2274396681153694</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1122553044361432</v>
+        <v>0.1107974433395699</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2189285748362946</v>
+        <v>0.2208285748362946</v>
       </c>
       <c r="C79">
-        <v>-1131.709641028806</v>
+        <v>-1156.205199364584</v>
       </c>
       <c r="D79">
-        <v>391.2863589711943</v>
+        <v>387.0388006354162</v>
       </c>
       <c r="E79">
-        <v>1084.896</v>
+        <v>1105.144</v>
       </c>
       <c r="F79">
-        <v>1559.096</v>
+        <v>1579.344</v>
       </c>
       <c r="G79">
         <v>36.1</v>
@@ -7887,37 +7887,37 @@
         <v>40.733</v>
       </c>
       <c r="M79">
-        <v>367.6348368</v>
+        <v>372.4093152</v>
       </c>
       <c r="N79">
-        <v>-326.9018368</v>
+        <v>-331.6763152</v>
       </c>
       <c r="O79">
-        <v>-104.608587776</v>
+        <v>-106.136420864</v>
       </c>
       <c r="P79">
-        <v>-222.293249024</v>
+        <v>-225.539894336</v>
       </c>
       <c r="Q79">
-        <v>-222.226249024</v>
+        <v>-225.472894336</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1904349147280875</v>
+        <v>0.1970092290339096</v>
       </c>
       <c r="T79">
-        <v>1.885077798743077</v>
+        <v>1.970763153231399</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03545518186866234</v>
+        <v>0.03500062825496154</v>
       </c>
       <c r="W79">
-        <v>0.2274396681153694</v>
+        <v>0.2275468518574801</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1107974433395699</v>
+        <v>0.1093769632967548</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2208285748362946</v>
+        <v>0.2227285748362946</v>
       </c>
       <c r="C80">
-        <v>-1156.205199364584</v>
+        <v>-1180.609530369271</v>
       </c>
       <c r="D80">
-        <v>387.0388006354162</v>
+        <v>382.8824696307289</v>
       </c>
       <c r="E80">
-        <v>1105.144</v>
+        <v>1125.392</v>
       </c>
       <c r="F80">
-        <v>1579.344</v>
+        <v>1599.592</v>
       </c>
       <c r="G80">
         <v>36.1</v>
@@ -7969,37 +7969,37 @@
         <v>40.733</v>
       </c>
       <c r="M80">
-        <v>372.4093152</v>
+        <v>377.1837936000001</v>
       </c>
       <c r="N80">
-        <v>-331.6763152</v>
+        <v>-336.4507936000001</v>
       </c>
       <c r="O80">
-        <v>-106.136420864</v>
+        <v>-107.664253952</v>
       </c>
       <c r="P80">
-        <v>-225.539894336</v>
+        <v>-228.786539648</v>
       </c>
       <c r="Q80">
-        <v>-225.472894336</v>
+        <v>-228.719539648</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1970092290339096</v>
+        <v>0.2042096685117149</v>
       </c>
       <c r="T80">
-        <v>1.970763153231399</v>
+        <v>2.064609017670989</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03500062825496154</v>
+        <v>0.03455758232768354</v>
       </c>
       <c r="W80">
-        <v>0.2275468518574801</v>
+        <v>0.2276513220871322</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1093769632967548</v>
+        <v>0.107992444774011</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2227285748362946</v>
+        <v>0.2246285748362946</v>
       </c>
       <c r="C81">
-        <v>-1180.609530369271</v>
+        <v>-1204.925541832005</v>
       </c>
       <c r="D81">
-        <v>382.8824696307289</v>
+        <v>378.8144581679948</v>
       </c>
       <c r="E81">
-        <v>1125.392</v>
+        <v>1145.64</v>
       </c>
       <c r="F81">
-        <v>1599.592</v>
+        <v>1619.84</v>
       </c>
       <c r="G81">
         <v>36.1</v>
@@ -8051,37 +8051,37 @@
         <v>40.733</v>
       </c>
       <c r="M81">
-        <v>377.1837936000001</v>
+        <v>381.958272</v>
       </c>
       <c r="N81">
-        <v>-336.4507936000001</v>
+        <v>-341.225272</v>
       </c>
       <c r="O81">
-        <v>-107.664253952</v>
+        <v>-109.19208704</v>
       </c>
       <c r="P81">
-        <v>-228.786539648</v>
+        <v>-232.03318496</v>
       </c>
       <c r="Q81">
-        <v>-228.719539648</v>
+        <v>-231.96618496</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2042096685117149</v>
+        <v>0.2121301519373006</v>
       </c>
       <c r="T81">
-        <v>2.064609017670989</v>
+        <v>2.167839468554539</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03455758232768354</v>
+        <v>0.0341256125485875</v>
       </c>
       <c r="W81">
-        <v>0.2276513220871322</v>
+        <v>0.2277531805610431</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.107992444774011</v>
+        <v>0.106642539214336</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2246285748362946</v>
+        <v>0.2265285748362946</v>
       </c>
       <c r="C82">
-        <v>-1204.925541832005</v>
+        <v>-1229.156019263541</v>
       </c>
       <c r="D82">
-        <v>378.8144581679948</v>
+        <v>374.8319807364591</v>
       </c>
       <c r="E82">
-        <v>1145.64</v>
+        <v>1165.888</v>
       </c>
       <c r="F82">
-        <v>1619.84</v>
+        <v>1640.088</v>
       </c>
       <c r="G82">
         <v>36.1</v>
@@ -8133,37 +8133,37 @@
         <v>40.733</v>
       </c>
       <c r="M82">
-        <v>381.958272</v>
+        <v>386.7327504</v>
       </c>
       <c r="N82">
-        <v>-341.225272</v>
+        <v>-345.9997504</v>
       </c>
       <c r="O82">
-        <v>-109.19208704</v>
+        <v>-110.719920128</v>
       </c>
       <c r="P82">
-        <v>-232.03318496</v>
+        <v>-235.279830272</v>
       </c>
       <c r="Q82">
-        <v>-231.96618496</v>
+        <v>-235.212830272</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2121301519373006</v>
+        <v>0.2208843704603164</v>
       </c>
       <c r="T82">
-        <v>2.167839468554539</v>
+        <v>2.281936282688989</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0341256125485875</v>
+        <v>0.03370430868996297</v>
       </c>
       <c r="W82">
-        <v>0.2277531805610431</v>
+        <v>0.2278525240109067</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.106642539214336</v>
+        <v>0.1053259646561343</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2265285748362946</v>
+        <v>0.2284285748362946</v>
       </c>
       <c r="C83">
-        <v>-1229.156019263541</v>
+        <v>-1253.303632256949</v>
       </c>
       <c r="D83">
-        <v>374.8319807364591</v>
+        <v>370.9323677430505</v>
       </c>
       <c r="E83">
-        <v>1165.888</v>
+        <v>1186.136</v>
       </c>
       <c r="F83">
-        <v>1640.088</v>
+        <v>1660.336</v>
       </c>
       <c r="G83">
         <v>36.1</v>
@@ -8215,37 +8215,37 @@
         <v>40.733</v>
       </c>
       <c r="M83">
-        <v>386.7327504</v>
+        <v>391.5072288</v>
       </c>
       <c r="N83">
-        <v>-345.9997504</v>
+        <v>-350.7742288</v>
       </c>
       <c r="O83">
-        <v>-110.719920128</v>
+        <v>-112.247753216</v>
       </c>
       <c r="P83">
-        <v>-235.279830272</v>
+        <v>-238.526475584</v>
       </c>
       <c r="Q83">
-        <v>-235.212830272</v>
+        <v>-238.459475584</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2208843704603164</v>
+        <v>0.230611279930334</v>
       </c>
       <c r="T83">
-        <v>2.281936282688989</v>
+        <v>2.408710520616154</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03370430868996297</v>
+        <v>0.03329328053520732</v>
       </c>
       <c r="W83">
-        <v>0.2278525240109067</v>
+        <v>0.2279494444497981</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1053259646561343</v>
+        <v>0.1040415016725229</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2284285748362946</v>
+        <v>0.2303285748362946</v>
       </c>
       <c r="C84">
-        <v>-1253.303632256949</v>
+        <v>-1277.370940455352</v>
       </c>
       <c r="D84">
-        <v>370.9323677430505</v>
+        <v>367.113059544648</v>
       </c>
       <c r="E84">
-        <v>1186.136</v>
+        <v>1206.384</v>
       </c>
       <c r="F84">
-        <v>1660.336</v>
+        <v>1680.584</v>
       </c>
       <c r="G84">
         <v>36.1</v>
@@ -8297,37 +8297,37 @@
         <v>40.733</v>
       </c>
       <c r="M84">
-        <v>391.5072288</v>
+        <v>396.2817072</v>
       </c>
       <c r="N84">
-        <v>-350.7742288</v>
+        <v>-355.5487072</v>
       </c>
       <c r="O84">
-        <v>-112.247753216</v>
+        <v>-113.775586304</v>
       </c>
       <c r="P84">
-        <v>-238.526475584</v>
+        <v>-241.773120896</v>
       </c>
       <c r="Q84">
-        <v>-238.459475584</v>
+        <v>-241.706120896</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.230611279930334</v>
+        <v>0.2414825316909419</v>
       </c>
       <c r="T84">
-        <v>2.408710520616154</v>
+        <v>2.550399374770046</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03329328053520732</v>
+        <v>0.03289215667333735</v>
       </c>
       <c r="W84">
-        <v>0.2279494444497981</v>
+        <v>0.2280440294564271</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1040415016725229</v>
+        <v>0.1027879896041792</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2303285748362946</v>
+        <v>0.2322285748362946</v>
       </c>
       <c r="C85">
-        <v>-1277.370940455352</v>
+        <v>-1301.360399154735</v>
       </c>
       <c r="D85">
-        <v>367.113059544648</v>
+        <v>363.3716008452649</v>
       </c>
       <c r="E85">
-        <v>1206.384</v>
+        <v>1226.632</v>
       </c>
       <c r="F85">
-        <v>1680.584</v>
+        <v>1700.832</v>
       </c>
       <c r="G85">
         <v>36.1</v>
@@ -8379,37 +8379,37 @@
         <v>40.733</v>
       </c>
       <c r="M85">
-        <v>396.2817072</v>
+        <v>401.0561856</v>
       </c>
       <c r="N85">
-        <v>-355.5487072</v>
+        <v>-360.3231856</v>
       </c>
       <c r="O85">
-        <v>-113.775586304</v>
+        <v>-115.303419392</v>
       </c>
       <c r="P85">
-        <v>-241.773120896</v>
+        <v>-245.019766208</v>
       </c>
       <c r="Q85">
-        <v>-241.706120896</v>
+        <v>-244.952766208</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2414825316909419</v>
+        <v>0.2537126899216258</v>
       </c>
       <c r="T85">
-        <v>2.550399374770046</v>
+        <v>2.709799335693174</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03289215667333735</v>
+        <v>0.03250058337960714</v>
       </c>
       <c r="W85">
-        <v>0.2280440294564271</v>
+        <v>0.2281363624390886</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1027879896041792</v>
+        <v>0.1015643230612724</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2322285748362946</v>
+        <v>0.2341285748362946</v>
       </c>
       <c r="C86">
-        <v>-1301.360399154735</v>
+        <v>-1325.274364567611</v>
       </c>
       <c r="D86">
-        <v>363.3716008452652</v>
+        <v>359.7056354323894</v>
       </c>
       <c r="E86">
-        <v>1226.632</v>
+        <v>1246.88</v>
       </c>
       <c r="F86">
-        <v>1700.832</v>
+        <v>1721.08</v>
       </c>
       <c r="G86">
         <v>36.1</v>
@@ -8461,37 +8461,37 @@
         <v>40.733</v>
       </c>
       <c r="M86">
-        <v>401.0561856</v>
+        <v>405.830664</v>
       </c>
       <c r="N86">
-        <v>-360.3231856</v>
+        <v>-365.097664</v>
       </c>
       <c r="O86">
-        <v>-115.303419392</v>
+        <v>-116.83125248</v>
       </c>
       <c r="P86">
-        <v>-245.019766208</v>
+        <v>-248.26641152</v>
       </c>
       <c r="Q86">
-        <v>-244.952766208</v>
+        <v>-248.19941152</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2537126899216257</v>
+        <v>0.2675735359164007</v>
       </c>
       <c r="T86">
-        <v>2.709799335693173</v>
+        <v>2.890452624739384</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03250058337960714</v>
+        <v>0.03211822357514118</v>
       </c>
       <c r="W86">
-        <v>0.2281363624390886</v>
+        <v>0.2282265228809817</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1015643230612724</v>
+        <v>0.1003694486723162</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2341285748362946</v>
+        <v>0.2360285748362946</v>
       </c>
       <c r="C87">
-        <v>-1325.274364567611</v>
+        <v>-1349.115098771237</v>
       </c>
       <c r="D87">
-        <v>359.7056354323894</v>
+        <v>356.1129012287626</v>
       </c>
       <c r="E87">
-        <v>1246.88</v>
+        <v>1267.128</v>
       </c>
       <c r="F87">
-        <v>1721.08</v>
+        <v>1741.328</v>
       </c>
       <c r="G87">
         <v>36.1</v>
@@ -8543,37 +8543,37 @@
         <v>40.733</v>
       </c>
       <c r="M87">
-        <v>405.830664</v>
+        <v>410.6051424</v>
       </c>
       <c r="N87">
-        <v>-365.097664</v>
+        <v>-369.8721424</v>
       </c>
       <c r="O87">
-        <v>-116.83125248</v>
+        <v>-118.359085568</v>
       </c>
       <c r="P87">
-        <v>-248.26641152</v>
+        <v>-251.513056832</v>
       </c>
       <c r="Q87">
-        <v>-248.19941152</v>
+        <v>-251.446056832</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2675735359164007</v>
+        <v>0.2834145027675722</v>
       </c>
       <c r="T87">
-        <v>2.890452624739384</v>
+        <v>3.096913526506483</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03211822357514118</v>
+        <v>0.03174475585915117</v>
       </c>
       <c r="W87">
-        <v>0.2282265228809817</v>
+        <v>0.2283145865684122</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1003694486723162</v>
+        <v>0.09920236205984745</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2360285748362946</v>
+        <v>0.2379285748362946</v>
       </c>
       <c r="C88">
-        <v>-1349.115098771237</v>
+        <v>-1372.884774362237</v>
       </c>
       <c r="D88">
-        <v>356.1129012287626</v>
+        <v>352.5912256377626</v>
       </c>
       <c r="E88">
-        <v>1267.128</v>
+        <v>1287.376</v>
       </c>
       <c r="F88">
-        <v>1741.328</v>
+        <v>1761.576</v>
       </c>
       <c r="G88">
         <v>36.1</v>
@@ -8625,37 +8625,37 @@
         <v>40.733</v>
       </c>
       <c r="M88">
-        <v>410.6051424</v>
+        <v>415.3796208</v>
       </c>
       <c r="N88">
-        <v>-369.8721424</v>
+        <v>-374.6466208</v>
       </c>
       <c r="O88">
-        <v>-118.359085568</v>
+        <v>-119.886918656</v>
       </c>
       <c r="P88">
-        <v>-251.513056832</v>
+        <v>-254.759702144</v>
       </c>
       <c r="Q88">
-        <v>-251.446056832</v>
+        <v>-254.692702144</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2834145027675722</v>
+        <v>0.3016925414420009</v>
       </c>
       <c r="T88">
-        <v>3.096913526506483</v>
+        <v>3.335137643930059</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03174475585915117</v>
+        <v>0.03137987360789656</v>
       </c>
       <c r="W88">
-        <v>0.2283145865684122</v>
+        <v>0.228400625803258</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09920236205984745</v>
+        <v>0.09806210502467672</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2379285748362946</v>
+        <v>0.2398285748362946</v>
       </c>
       <c r="C89">
-        <v>-1372.884774362237</v>
+        <v>-1396.585478837735</v>
       </c>
       <c r="D89">
-        <v>352.5912256377626</v>
+        <v>349.1385211622647</v>
       </c>
       <c r="E89">
-        <v>1287.376</v>
+        <v>1307.624</v>
       </c>
       <c r="F89">
-        <v>1761.576</v>
+        <v>1781.824</v>
       </c>
       <c r="G89">
         <v>36.1</v>
@@ -8707,37 +8707,37 @@
         <v>40.733</v>
       </c>
       <c r="M89">
-        <v>415.3796208</v>
+        <v>420.1540992</v>
       </c>
       <c r="N89">
-        <v>-374.6466208</v>
+        <v>-379.4210992</v>
       </c>
       <c r="O89">
-        <v>-119.886918656</v>
+        <v>-121.414751744</v>
       </c>
       <c r="P89">
-        <v>-254.759702144</v>
+        <v>-258.006347456</v>
       </c>
       <c r="Q89">
-        <v>-254.692702144</v>
+        <v>-257.939347456</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3016925414420009</v>
+        <v>0.323016919895501</v>
       </c>
       <c r="T89">
-        <v>3.335137643930059</v>
+        <v>3.613065780924231</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03137987360789656</v>
+        <v>0.03102328413507955</v>
       </c>
       <c r="W89">
-        <v>0.228400625803258</v>
+        <v>0.2284847096009482</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.09806210502467672</v>
+        <v>0.09694776292212359</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2398285748362946</v>
+        <v>0.2417285748362946</v>
       </c>
       <c r="C90">
-        <v>-1396.585478837735</v>
+        <v>-1420.219218721581</v>
       </c>
       <c r="D90">
-        <v>349.1385211622647</v>
+        <v>345.7527812784188</v>
       </c>
       <c r="E90">
-        <v>1307.624</v>
+        <v>1327.872</v>
       </c>
       <c r="F90">
-        <v>1781.824</v>
+        <v>1802.072</v>
       </c>
       <c r="G90">
         <v>36.1</v>
@@ -8789,37 +8789,37 @@
         <v>40.733</v>
       </c>
       <c r="M90">
-        <v>420.1540992</v>
+        <v>424.9285776</v>
       </c>
       <c r="N90">
-        <v>-379.4210992</v>
+        <v>-384.1955776</v>
       </c>
       <c r="O90">
-        <v>-121.414751744</v>
+        <v>-122.942584832</v>
       </c>
       <c r="P90">
-        <v>-258.006347456</v>
+        <v>-261.252992768</v>
       </c>
       <c r="Q90">
-        <v>-257.939347456</v>
+        <v>-261.185992768</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.323016919895501</v>
+        <v>0.3482184580678193</v>
       </c>
       <c r="T90">
-        <v>3.613065780924231</v>
+        <v>3.941526306462798</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03102328413507955</v>
+        <v>0.0306747079088427</v>
       </c>
       <c r="W90">
-        <v>0.2284847096009482</v>
+        <v>0.2285669038750949</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.09694776292212359</v>
+        <v>0.0958584622151335</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2417285748362946</v>
+        <v>0.2436285748362946</v>
       </c>
       <c r="C91">
-        <v>-1420.219218721581</v>
+        <v>-1443.787923452799</v>
       </c>
       <c r="D91">
-        <v>345.7527812784188</v>
+        <v>342.4320765472008</v>
       </c>
       <c r="E91">
-        <v>1327.872</v>
+        <v>1348.12</v>
       </c>
       <c r="F91">
-        <v>1802.072</v>
+        <v>1822.32</v>
       </c>
       <c r="G91">
         <v>36.1</v>
@@ -8871,37 +8871,37 @@
         <v>40.733</v>
       </c>
       <c r="M91">
-        <v>424.9285776</v>
+        <v>429.703056</v>
       </c>
       <c r="N91">
-        <v>-384.1955776</v>
+        <v>-388.970056</v>
       </c>
       <c r="O91">
-        <v>-122.942584832</v>
+        <v>-124.47041792</v>
       </c>
       <c r="P91">
-        <v>-261.252992768</v>
+        <v>-264.49963808</v>
       </c>
       <c r="Q91">
-        <v>-261.185992768</v>
+        <v>-264.43263808</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3482184580678193</v>
+        <v>0.3784603038746012</v>
       </c>
       <c r="T91">
-        <v>3.941526306462798</v>
+        <v>4.335678937109078</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0306747079088427</v>
+        <v>0.03033387782096667</v>
       </c>
       <c r="W91">
-        <v>0.2285669038750949</v>
+        <v>0.2286472716098161</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.0958584622151335</v>
+        <v>0.09479336819052087</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2436285748362946</v>
+        <v>0.2455285748362946</v>
       </c>
       <c r="C92">
-        <v>-1443.787923452799</v>
+        <v>-1467.293449052093</v>
       </c>
       <c r="D92">
-        <v>342.4320765472008</v>
+        <v>339.1745509479069</v>
       </c>
       <c r="E92">
-        <v>1348.12</v>
+        <v>1368.368</v>
       </c>
       <c r="F92">
-        <v>1822.32</v>
+        <v>1842.568</v>
       </c>
       <c r="G92">
         <v>36.1</v>
@@ -8953,37 +8953,37 @@
         <v>40.733</v>
       </c>
       <c r="M92">
-        <v>429.703056</v>
+        <v>434.4775344</v>
       </c>
       <c r="N92">
-        <v>-388.970056</v>
+        <v>-393.7445344</v>
       </c>
       <c r="O92">
-        <v>-124.47041792</v>
+        <v>-125.998251008</v>
       </c>
       <c r="P92">
-        <v>-264.49963808</v>
+        <v>-267.746283392</v>
       </c>
       <c r="Q92">
-        <v>-264.43263808</v>
+        <v>-267.679283392</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3784603038746012</v>
+        <v>0.415422559860668</v>
       </c>
       <c r="T92">
-        <v>4.335678937109078</v>
+        <v>4.817421041232309</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03033387782096667</v>
+        <v>0.03000053850425275</v>
       </c>
       <c r="W92">
-        <v>0.2286472716098161</v>
+        <v>0.2287258730206972</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.09479336819052087</v>
+        <v>0.09375168282578983</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2455285748362946</v>
+        <v>0.2474285748362946</v>
       </c>
       <c r="C93">
-        <v>-1467.293449052093</v>
+        <v>-1490.737581581048</v>
       </c>
       <c r="D93">
-        <v>339.1745509479069</v>
+        <v>335.9784184189523</v>
       </c>
       <c r="E93">
-        <v>1368.368</v>
+        <v>1388.616</v>
       </c>
       <c r="F93">
-        <v>1842.568</v>
+        <v>1862.816</v>
       </c>
       <c r="G93">
         <v>36.1</v>
@@ -9035,37 +9035,37 @@
         <v>40.733</v>
       </c>
       <c r="M93">
-        <v>434.4775344</v>
+        <v>439.2520128</v>
       </c>
       <c r="N93">
-        <v>-393.7445344</v>
+        <v>-398.5190128</v>
       </c>
       <c r="O93">
-        <v>-125.998251008</v>
+        <v>-127.526084096</v>
       </c>
       <c r="P93">
-        <v>-267.746283392</v>
+        <v>-270.992928704</v>
       </c>
       <c r="Q93">
-        <v>-267.679283392</v>
+        <v>-270.925928704</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.415422559860668</v>
+        <v>0.4616253798432516</v>
       </c>
       <c r="T93">
-        <v>4.817421041232309</v>
+        <v>5.419598671386349</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03000053850425275</v>
+        <v>0.02967444569442391</v>
       </c>
       <c r="W93">
-        <v>0.2287258730206972</v>
+        <v>0.2288027657052548</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.09375168282578983</v>
+        <v>0.09273264279507476</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2474285748362946</v>
+        <v>0.2493285748362946</v>
       </c>
       <c r="C94">
-        <v>-1490.737581581048</v>
+        <v>-1514.122040407576</v>
       </c>
       <c r="D94">
-        <v>335.9784184189523</v>
+        <v>332.8419595924245</v>
       </c>
       <c r="E94">
-        <v>1388.616</v>
+        <v>1408.864</v>
       </c>
       <c r="F94">
-        <v>1862.816</v>
+        <v>1883.064</v>
       </c>
       <c r="G94">
         <v>36.1</v>
@@ -9117,37 +9117,37 @@
         <v>40.733</v>
       </c>
       <c r="M94">
-        <v>439.2520128</v>
+        <v>444.0264912</v>
       </c>
       <c r="N94">
-        <v>-398.5190128</v>
+        <v>-403.2934912</v>
       </c>
       <c r="O94">
-        <v>-127.526084096</v>
+        <v>-129.053917184</v>
       </c>
       <c r="P94">
-        <v>-270.992928704</v>
+        <v>-274.239574016</v>
       </c>
       <c r="Q94">
-        <v>-270.925928704</v>
+        <v>-274.172574016</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4616253798432516</v>
+        <v>0.5210290055351448</v>
       </c>
       <c r="T94">
-        <v>5.419598671386349</v>
+        <v>6.193827053012971</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02967444569442391</v>
+        <v>0.02935536563319355</v>
       </c>
       <c r="W94">
-        <v>0.2288027657052548</v>
+        <v>0.228878004783693</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.09273264279507476</v>
+        <v>0.09173551760372989</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2493285748362946</v>
+        <v>0.2512285748362946</v>
       </c>
       <c r="C95">
-        <v>-1514.122040407576</v>
+        <v>-1537.448481290153</v>
       </c>
       <c r="D95">
-        <v>332.8419595924245</v>
+        <v>329.7635187098471</v>
       </c>
       <c r="E95">
-        <v>1408.864</v>
+        <v>1429.112</v>
       </c>
       <c r="F95">
-        <v>1883.064</v>
+        <v>1903.312</v>
       </c>
       <c r="G95">
         <v>36.1</v>
@@ -9199,37 +9199,37 @@
         <v>40.733</v>
       </c>
       <c r="M95">
-        <v>444.0264912</v>
+        <v>448.8009696</v>
       </c>
       <c r="N95">
-        <v>-403.2934912</v>
+        <v>-408.0679696</v>
       </c>
       <c r="O95">
-        <v>-129.053917184</v>
+        <v>-130.581750272</v>
       </c>
       <c r="P95">
-        <v>-274.239574016</v>
+        <v>-277.486219328</v>
       </c>
       <c r="Q95">
-        <v>-274.172574016</v>
+        <v>-277.419219328</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5210290055351448</v>
+        <v>0.6002338397910024</v>
       </c>
       <c r="T95">
-        <v>6.193827053012971</v>
+        <v>7.226131561848469</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02935536563319355</v>
+        <v>0.02904307450943617</v>
       </c>
       <c r="W95">
-        <v>0.228878004783693</v>
+        <v>0.2289516430306749</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.09173551760372989</v>
+        <v>0.090759607841988</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2512285748362946</v>
+        <v>0.2531285748362946</v>
       </c>
       <c r="C96">
-        <v>-1537.448481290153</v>
+        <v>-1560.718499292464</v>
       </c>
       <c r="D96">
-        <v>329.7635187098471</v>
+        <v>326.7415007075364</v>
       </c>
       <c r="E96">
-        <v>1429.112</v>
+        <v>1449.36</v>
       </c>
       <c r="F96">
-        <v>1903.312</v>
+        <v>1923.56</v>
       </c>
       <c r="G96">
         <v>36.1</v>
@@ -9281,37 +9281,37 @@
         <v>40.733</v>
       </c>
       <c r="M96">
-        <v>448.8009696</v>
+        <v>453.5754480000001</v>
       </c>
       <c r="N96">
-        <v>-408.0679696</v>
+        <v>-412.842448</v>
       </c>
       <c r="O96">
-        <v>-130.581750272</v>
+        <v>-132.10958336</v>
       </c>
       <c r="P96">
-        <v>-277.486219328</v>
+        <v>-280.73286464</v>
       </c>
       <c r="Q96">
-        <v>-277.419219328</v>
+        <v>-280.66586464</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6002338397910024</v>
+        <v>0.711120607749203</v>
       </c>
       <c r="T96">
-        <v>7.226131561848469</v>
+        <v>8.671357874218165</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02904307450943617</v>
+        <v>0.02873735793565263</v>
       </c>
       <c r="W96">
-        <v>0.2289516430306749</v>
+        <v>0.2290237309987731</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.090759607841988</v>
+        <v>0.08980424354891448</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2531285748362946</v>
+        <v>0.2550285748362946</v>
       </c>
       <c r="C97">
-        <v>-1560.718499292464</v>
+        <v>-1583.933631539242</v>
       </c>
       <c r="D97">
-        <v>326.7415007075364</v>
+        <v>323.7743684607576</v>
       </c>
       <c r="E97">
-        <v>1449.36</v>
+        <v>1469.608</v>
       </c>
       <c r="F97">
-        <v>1923.56</v>
+        <v>1943.808</v>
       </c>
       <c r="G97">
         <v>36.1</v>
@@ -9363,37 +9363,37 @@
         <v>40.733</v>
       </c>
       <c r="M97">
-        <v>453.5754480000001</v>
+        <v>458.3499264000001</v>
       </c>
       <c r="N97">
-        <v>-412.842448</v>
+        <v>-417.6169264000001</v>
       </c>
       <c r="O97">
-        <v>-132.10958336</v>
+        <v>-133.637416448</v>
       </c>
       <c r="P97">
-        <v>-280.73286464</v>
+        <v>-283.9795099520001</v>
       </c>
       <c r="Q97">
-        <v>-280.66586464</v>
+        <v>-283.9125099520001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.711120607749203</v>
+        <v>0.8774507596865042</v>
       </c>
       <c r="T97">
-        <v>8.671357874218165</v>
+        <v>10.83919734277271</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02873735793565263</v>
+        <v>0.02843801045715625</v>
       </c>
       <c r="W97">
-        <v>0.2290237309987731</v>
+        <v>0.2290943171342026</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08980424354891448</v>
+        <v>0.08886878267861331</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2550285748362946</v>
+        <v>0.2569285748362946</v>
       </c>
       <c r="C98">
-        <v>-1583.933631539242</v>
+        <v>-1607.09535982331</v>
       </c>
       <c r="D98">
-        <v>323.7743684607576</v>
+        <v>320.8606401766898</v>
       </c>
       <c r="E98">
-        <v>1469.608</v>
+        <v>1489.856</v>
       </c>
       <c r="F98">
-        <v>1943.808</v>
+        <v>1964.056</v>
       </c>
       <c r="G98">
         <v>36.1</v>
@@ -9445,37 +9445,37 @@
         <v>40.733</v>
       </c>
       <c r="M98">
-        <v>458.3499264</v>
+        <v>463.1244048</v>
       </c>
       <c r="N98">
-        <v>-417.6169264</v>
+        <v>-422.3914048</v>
       </c>
       <c r="O98">
-        <v>-133.637416448</v>
+        <v>-135.165249536</v>
       </c>
       <c r="P98">
-        <v>-283.979509952</v>
+        <v>-287.226155264</v>
       </c>
       <c r="Q98">
-        <v>-283.912509952</v>
+        <v>-287.159155264</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8774507596865021</v>
+        <v>1.154667679582003</v>
       </c>
       <c r="T98">
-        <v>10.83919734277268</v>
+        <v>14.45226312369691</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02843801045715625</v>
+        <v>0.02814483509161856</v>
       </c>
       <c r="W98">
-        <v>0.2290943171342026</v>
+        <v>0.2291634478853964</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08886878267861331</v>
+        <v>0.08795260966130802</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2569285748362946</v>
+        <v>0.2588285748362946</v>
       </c>
       <c r="C99">
-        <v>-1607.09535982331</v>
+        <v>-1630.205113073099</v>
       </c>
       <c r="D99">
-        <v>320.8606401766898</v>
+        <v>317.9988869269008</v>
       </c>
       <c r="E99">
-        <v>1489.856</v>
+        <v>1510.104</v>
       </c>
       <c r="F99">
-        <v>1964.056</v>
+        <v>1984.304</v>
       </c>
       <c r="G99">
         <v>36.1</v>
@@ -9527,37 +9527,37 @@
         <v>40.733</v>
       </c>
       <c r="M99">
-        <v>463.1244048</v>
+        <v>467.8988832</v>
       </c>
       <c r="N99">
-        <v>-422.3914048</v>
+        <v>-427.1658832</v>
       </c>
       <c r="O99">
-        <v>-135.165249536</v>
+        <v>-136.693082624</v>
       </c>
       <c r="P99">
-        <v>-287.226155264</v>
+        <v>-290.472800576</v>
       </c>
       <c r="Q99">
-        <v>-287.159155264</v>
+        <v>-290.405800576</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.154667679582003</v>
+        <v>1.709101519373004</v>
       </c>
       <c r="T99">
-        <v>14.45226312369691</v>
+        <v>21.67839468554536</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02814483509161856</v>
+        <v>0.02785764289680613</v>
       </c>
       <c r="W99">
-        <v>0.2291634478853964</v>
+        <v>0.2292311678049331</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.08795260966130802</v>
+        <v>0.08705513405251919</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2588285748362946</v>
+        <v>0.2607285748362946</v>
       </c>
       <c r="C100">
-        <v>-1630.205113073099</v>
+        <v>-1653.264269689297</v>
       </c>
       <c r="D100">
-        <v>317.9988869269008</v>
+        <v>315.1877303107024</v>
       </c>
       <c r="E100">
-        <v>1510.104</v>
+        <v>1530.352</v>
       </c>
       <c r="F100">
-        <v>1984.304</v>
+        <v>2004.552</v>
       </c>
       <c r="G100">
         <v>36.1</v>
@@ -9609,37 +9609,37 @@
         <v>40.733</v>
       </c>
       <c r="M100">
-        <v>467.8988832</v>
+        <v>472.6733616</v>
       </c>
       <c r="N100">
-        <v>-427.1658832</v>
+        <v>-431.9403616</v>
       </c>
       <c r="O100">
-        <v>-136.693082624</v>
+        <v>-138.220915712</v>
       </c>
       <c r="P100">
-        <v>-290.472800576</v>
+        <v>-293.719445888</v>
       </c>
       <c r="Q100">
-        <v>-290.405800576</v>
+        <v>-293.652445888</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.709101519373004</v>
+        <v>3.372403038746008</v>
       </c>
       <c r="T100">
-        <v>21.67839468554536</v>
+        <v>43.35678937109073</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02785764289680613</v>
+        <v>0.02757625256451515</v>
       </c>
       <c r="W100">
-        <v>0.2292311678049331</v>
+        <v>0.2292975196452874</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.08705513405251919</v>
+        <v>0.08617578926410985</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2607285748362946</v>
-      </c>
-      <c r="C101">
-        <v>-1653.264269689297</v>
-      </c>
-      <c r="D101">
-        <v>315.1877303107024</v>
-      </c>
-      <c r="E101">
-        <v>1530.352</v>
-      </c>
-      <c r="F101">
-        <v>2004.552</v>
-      </c>
-      <c r="G101">
-        <v>36.1</v>
-      </c>
-      <c r="H101">
-        <v>1550.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>40.8</v>
-      </c>
-      <c r="K101">
-        <v>0.067</v>
-      </c>
-      <c r="L101">
-        <v>40.733</v>
-      </c>
-      <c r="M101">
-        <v>472.6733616</v>
-      </c>
-      <c r="N101">
-        <v>-431.9403616</v>
-      </c>
-      <c r="O101">
-        <v>-138.220915712</v>
-      </c>
-      <c r="P101">
-        <v>-293.719445888</v>
-      </c>
-      <c r="Q101">
-        <v>-293.652445888</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.372403038746008</v>
-      </c>
-      <c r="T101">
-        <v>43.35678937109073</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02757625256451515</v>
-      </c>
-      <c r="W101">
-        <v>0.2292975196452874</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.08617578926410985</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
